--- a/StocksIC/sort.xlsx
+++ b/StocksIC/sort.xlsx
@@ -2754,7 +2754,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2765,13 +2765,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3245,28 +3238,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3275,118 +3271,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/StocksIC/sort.xlsx
+++ b/StocksIC/sort.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12255"/>
+    <workbookView windowWidth="20490" windowHeight="7695"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="911">
   <si>
     <t>Index</t>
   </si>
@@ -347,7 +347,7 @@
     <t>col276</t>
   </si>
   <si>
-    <t>近一年净利润(元)</t>
+    <t>近一年净利润</t>
   </si>
   <si>
     <t>col283</t>
@@ -428,7 +428,7 @@
     <t>col501</t>
   </si>
   <si>
-    <t>稀释每股收益(元)</t>
+    <t>稀释每股收益</t>
   </si>
   <si>
     <t>CB</t>
@@ -1052,7 +1052,7 @@
     <t>col219</t>
   </si>
   <si>
-    <t>每股经营性现金流(元)</t>
+    <t>每股经营性现金流</t>
   </si>
   <si>
     <t>col220</t>
@@ -1985,6 +1985,12 @@
     <t>非正常经营项目收益调整</t>
   </si>
   <si>
+    <t>ZJ</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
     <t>col72</t>
   </si>
   <si>
@@ -2003,6 +2009,12 @@
     <t>归属于母公司股东权益 合计</t>
   </si>
   <si>
+    <t>GMGS</t>
+  </si>
+  <si>
+    <t>归属于母公司</t>
+  </si>
+  <si>
     <t>col64</t>
   </si>
   <si>
@@ -2033,6 +2045,12 @@
     <t>未分配利润</t>
   </si>
   <si>
+    <t>SSGD</t>
+  </si>
+  <si>
+    <t>归少数股东</t>
+  </si>
+  <si>
     <t>col69</t>
   </si>
   <si>
@@ -2115,6 +2133,12 @@
   </si>
   <si>
     <t>负债合计</t>
+  </si>
+  <si>
+    <t>XJ</t>
+  </si>
+  <si>
+    <t>小计</t>
   </si>
   <si>
     <t>col295</t>
@@ -2751,7 +2775,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2771,13 +2795,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -3263,28 +3280,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3293,118 +3313,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4659,7 +4676,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:9">
+    <row r="31" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A31" s="5">
         <v>376</v>
       </c>
@@ -4688,7 +4705,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" ht="18.75" customHeight="1" spans="1:9">
+    <row r="32" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A32" s="5">
         <v>96</v>
       </c>
@@ -4717,7 +4734,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:9">
+    <row r="33" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A33" s="5">
         <v>97</v>
       </c>
@@ -4746,7 +4763,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" ht="18.75" customHeight="1" spans="1:9">
+    <row r="34" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A34" s="5">
         <v>205</v>
       </c>
@@ -4775,7 +4792,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" ht="18.75" customHeight="1" spans="1:9">
+    <row r="35" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A35" s="5">
         <v>301</v>
       </c>
@@ -4804,7 +4821,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" ht="18.75" customHeight="1" spans="1:9">
+    <row r="36" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A36" s="5">
         <v>302</v>
       </c>
@@ -4833,7 +4850,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" ht="18.75" customHeight="1" spans="1:9">
+    <row r="37" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A37" s="5">
         <v>93</v>
       </c>
@@ -4862,7 +4879,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" ht="18.75" customHeight="1" spans="1:9">
+    <row r="38" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A38" s="5">
         <v>92</v>
       </c>
@@ -4891,7 +4908,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" ht="18.75" customHeight="1" spans="1:9">
+    <row r="39" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A39" s="5">
         <v>95</v>
       </c>
@@ -4920,7 +4937,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" ht="18.75" customHeight="1" spans="1:9">
+    <row r="40" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A40" s="5">
         <v>275</v>
       </c>
@@ -4949,7 +4966,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" ht="18.75" customHeight="1" spans="1:9">
+    <row r="41" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A41" s="5">
         <v>282</v>
       </c>
@@ -4978,7 +4995,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" ht="18.75" customHeight="1" spans="1:9">
+    <row r="42" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A42" s="5">
         <v>307</v>
       </c>
@@ -5007,7 +5024,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43" ht="18.75" customHeight="1" spans="1:9">
+    <row r="43" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A43" s="5">
         <v>308</v>
       </c>
@@ -5036,7 +5053,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" ht="18.75" customHeight="1" spans="1:9">
+    <row r="44" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A44" s="5">
         <v>318</v>
       </c>
@@ -5065,7 +5082,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" ht="18.75" customHeight="1" spans="1:9">
+    <row r="45" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A45" s="5">
         <v>86</v>
       </c>
@@ -5094,7 +5111,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" ht="18.75" customHeight="1" spans="1:9">
+    <row r="46" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A46" s="5">
         <v>88</v>
       </c>
@@ -5123,7 +5140,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" ht="18.75" customHeight="1" spans="1:9">
+    <row r="47" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A47" s="5">
         <v>89</v>
       </c>
@@ -5152,7 +5169,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="48" ht="18.75" customHeight="1" spans="1:9">
+    <row r="48" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A48" s="5">
         <v>79</v>
       </c>
@@ -5181,7 +5198,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="49" ht="18.75" customHeight="1" spans="1:9">
+    <row r="49" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A49" s="5">
         <v>91</v>
       </c>
@@ -5210,7 +5227,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="50" ht="18.75" customHeight="1" spans="1:9">
+    <row r="50" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A50" s="5">
         <v>94</v>
       </c>
@@ -5239,7 +5256,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="51" ht="18.75" customHeight="1" spans="1:9">
+    <row r="51" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A51" s="5">
         <v>85</v>
       </c>
@@ -5255,8 +5272,6 @@
       <c r="E51" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
       <c r="H51" s="2" t="s">
         <v>127</v>
       </c>
@@ -5264,7 +5279,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="52" ht="18.75" customHeight="1" spans="1:9">
+    <row r="52" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A52" s="5">
         <v>87</v>
       </c>
@@ -5293,7 +5308,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="53" ht="18.75" customHeight="1" spans="1:9">
+    <row r="53" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A53" s="5">
         <v>361</v>
       </c>
@@ -5309,8 +5324,6 @@
       <c r="E53" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
       <c r="H53" s="2" t="s">
         <v>131</v>
       </c>
@@ -5318,7 +5331,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="54" ht="18.75" customHeight="1" spans="1:9">
+    <row r="54" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A54" s="5">
         <v>90</v>
       </c>
@@ -5347,7 +5360,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" ht="18.75" customHeight="1" spans="1:9">
+    <row r="55" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A55" s="5">
         <v>379</v>
       </c>
@@ -5376,7 +5389,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="56" ht="18.75" customHeight="1" spans="1:9">
+    <row r="56" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A56" s="5">
         <v>75</v>
       </c>
@@ -5405,7 +5418,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="57" ht="18.75" customHeight="1" spans="1:9">
+    <row r="57" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A57" s="5">
         <v>76</v>
       </c>
@@ -5434,7 +5447,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="58" ht="18.75" customHeight="1" spans="1:9">
+    <row r="58" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A58" s="5">
         <v>77</v>
       </c>
@@ -5463,7 +5476,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" ht="18.75" customHeight="1" spans="1:9">
+    <row r="59" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A59" s="5">
         <v>78</v>
       </c>
@@ -5492,7 +5505,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="60" ht="18.75" customHeight="1" spans="1:9">
+    <row r="60" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A60" s="5">
         <v>80</v>
       </c>
@@ -5521,7 +5534,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" ht="18.75" customHeight="1" spans="1:9">
+    <row r="61" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A61" s="5">
         <v>81</v>
       </c>
@@ -5550,7 +5563,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="62" ht="18.75" customHeight="1" spans="1:9">
+    <row r="62" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A62" s="5">
         <v>82</v>
       </c>
@@ -5579,7 +5592,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="63" ht="18.75" customHeight="1" spans="1:9">
+    <row r="63" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A63" s="5">
         <v>83</v>
       </c>
@@ -5608,7 +5621,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" ht="18.75" customHeight="1" spans="1:9">
+    <row r="64" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A64" s="5">
         <v>84</v>
       </c>
@@ -5637,7 +5650,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="65" ht="18.75" customHeight="1" spans="1:9">
+    <row r="65" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A65" s="5">
         <v>299</v>
       </c>
@@ -5666,7 +5679,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" ht="18.75" customHeight="1" spans="1:9">
+    <row r="66" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A66" s="5">
         <v>300</v>
       </c>
@@ -5695,7 +5708,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="67" ht="18.75" customHeight="1" spans="1:9">
+    <row r="67" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A67" s="5">
         <v>303</v>
       </c>
@@ -5724,7 +5737,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="68" ht="18.75" customHeight="1" spans="1:9">
+    <row r="68" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A68" s="5">
         <v>370</v>
       </c>
@@ -5753,7 +5766,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" ht="18.75" customHeight="1" spans="1:9">
+    <row r="69" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A69" s="5">
         <v>371</v>
       </c>
@@ -5782,7 +5795,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="70" ht="18.75" customHeight="1" spans="1:9">
+    <row r="70" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A70" s="5">
         <v>372</v>
       </c>
@@ -5811,7 +5824,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="71" ht="18.75" customHeight="1" spans="1:9">
+    <row r="71" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A71" s="5">
         <v>373</v>
       </c>
@@ -5840,7 +5853,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="72" ht="18.75" customHeight="1" spans="1:9">
+    <row r="72" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A72" s="5">
         <v>374</v>
       </c>
@@ -5869,7 +5882,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="73" ht="18.75" customHeight="1" spans="1:9">
+    <row r="73" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A73" s="5">
         <v>375</v>
       </c>
@@ -5898,7 +5911,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="74" ht="18.75" customHeight="1" spans="1:9">
+    <row r="74" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A74" s="5">
         <v>377</v>
       </c>
@@ -5927,7 +5940,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="75" ht="18.75" customHeight="1" spans="1:9">
+    <row r="75" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A75" s="5">
         <v>378</v>
       </c>
@@ -5956,7 +5969,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="76" ht="18.75" customHeight="1" spans="1:9">
+    <row r="76" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A76" s="5">
         <v>380</v>
       </c>
@@ -5985,7 +5998,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="77" ht="18.75" customHeight="1" spans="1:9">
+    <row r="77" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A77" s="5">
         <v>381</v>
       </c>
@@ -6014,7 +6027,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="78" ht="18.75" customHeight="1" spans="1:9">
+    <row r="78" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A78" s="5">
         <v>304</v>
       </c>
@@ -6043,7 +6056,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="79" ht="18.75" customHeight="1" spans="1:9">
+    <row r="79" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A79" s="5">
         <v>305</v>
       </c>
@@ -6072,7 +6085,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="80" ht="18.75" customHeight="1" spans="1:9">
+    <row r="80" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A80" s="5">
         <v>362</v>
       </c>
@@ -6101,7 +6114,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="81" ht="18.75" customHeight="1" spans="1:9">
+    <row r="81" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A81" s="5">
         <v>74</v>
       </c>
@@ -6130,7 +6143,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="82" ht="18.75" customHeight="1" spans="1:9">
+    <row r="82" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A82" s="5">
         <v>363</v>
       </c>
@@ -6159,7 +6172,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="83" ht="18.75" customHeight="1" spans="1:9">
+    <row r="83" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A83" s="5">
         <v>366</v>
       </c>
@@ -6188,7 +6201,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="84" ht="18.75" customHeight="1" spans="1:9">
+    <row r="84" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A84" s="5">
         <v>367</v>
       </c>
@@ -6217,7 +6230,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="85" ht="18.75" customHeight="1" spans="1:9">
+    <row r="85" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A85" s="5">
         <v>368</v>
       </c>
@@ -6246,7 +6259,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="86" ht="18.75" customHeight="1" spans="1:9">
+    <row r="86" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A86" s="5">
         <v>369</v>
       </c>
@@ -6275,7 +6288,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="87" ht="18.75" customHeight="1" spans="1:9">
+    <row r="87" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A87" s="5">
         <v>269</v>
       </c>
@@ -6304,7 +6317,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="88" ht="18.75" customHeight="1" spans="1:9">
+    <row r="88" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A88" s="5">
         <v>268</v>
       </c>
@@ -6333,7 +6346,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="89" ht="18.75" customHeight="1" spans="1:9">
+    <row r="89" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A89" s="5">
         <v>364</v>
       </c>
@@ -6362,7 +6375,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="90" ht="18.75" customHeight="1" spans="1:9">
+    <row r="90" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A90" s="5">
         <v>365</v>
       </c>
@@ -12063,16 +12076,16 @@
         <v>646</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>100</v>
+        <v>651</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>101</v>
+        <v>652</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="I286" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="287" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12092,19 +12105,19 @@
         <v>646</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>100</v>
+        <v>651</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>101</v>
+        <v>652</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I287" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="288" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="288" ht="18.75" customHeight="1" spans="1:9">
       <c r="A288" s="5">
         <v>270</v>
       </c>
@@ -12127,10 +12140,10 @@
         <v>101</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="I288" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="289" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12150,16 +12163,16 @@
         <v>646</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="I289" s="2" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="290" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12179,16 +12192,16 @@
         <v>646</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="I290" s="2" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="291" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12208,16 +12221,16 @@
         <v>646</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I291" s="2" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="292" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12237,16 +12250,16 @@
         <v>646</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="I292" s="2" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="293" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12266,19 +12279,19 @@
         <v>646</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="I293" s="2" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="294" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="294" ht="18.75" customHeight="1" spans="1:9">
       <c r="A294" s="5">
         <v>69</v>
       </c>
@@ -12295,16 +12308,16 @@
         <v>646</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>645</v>
+        <v>671</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>646</v>
+        <v>672</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="I294" s="2" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
     <row r="295" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12324,16 +12337,16 @@
         <v>646</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="I295" s="2" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
     </row>
     <row r="296" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12353,16 +12366,16 @@
         <v>646</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="I296" s="2" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="297" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12382,16 +12395,16 @@
         <v>646</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="I297" s="2" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="298" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12411,16 +12424,16 @@
         <v>646</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="I298" s="2" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="299" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12446,10 +12459,10 @@
         <v>39</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="I299" s="7" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="300" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12475,10 +12488,10 @@
         <v>39</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="I300" s="7" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="301" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12492,10 +12505,10 @@
         <v>644</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>39</v>
@@ -12504,10 +12517,10 @@
         <v>39</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="302" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12521,10 +12534,10 @@
         <v>644</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>39</v>
@@ -12533,10 +12546,10 @@
         <v>39</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="303" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12550,10 +12563,10 @@
         <v>644</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>39</v>
@@ -12562,13 +12575,13 @@
         <v>39</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="304" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="304" ht="18.75" customHeight="1" spans="1:9">
       <c r="A304" s="5">
         <v>54</v>
       </c>
@@ -12579,10 +12592,10 @@
         <v>644</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>100</v>
@@ -12591,13 +12604,13 @@
         <v>101</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="I304" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="305" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="305" ht="18.75" customHeight="1" spans="1:9">
       <c r="A305" s="5">
         <v>62</v>
       </c>
@@ -12608,10 +12621,10 @@
         <v>644</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>100</v>
@@ -12620,10 +12633,10 @@
         <v>101</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="I305" s="2" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="306" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12637,22 +12650,22 @@
         <v>644</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>100</v>
+        <v>651</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>101</v>
+        <v>652</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="I306" s="2" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
     </row>
     <row r="307" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12666,22 +12679,22 @@
         <v>644</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>100</v>
+        <v>701</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>101</v>
+        <v>702</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="I307" s="2" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
     </row>
     <row r="308" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12695,22 +12708,22 @@
         <v>644</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="I308" s="2" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
     </row>
     <row r="309" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12724,22 +12737,22 @@
         <v>644</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="I309" s="2" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
     </row>
     <row r="310" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12753,22 +12766,22 @@
         <v>644</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="I310" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
     </row>
     <row r="311" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12782,22 +12795,22 @@
         <v>644</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="I311" s="2" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
     </row>
     <row r="312" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12811,22 +12824,22 @@
         <v>644</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="I312" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
     </row>
     <row r="313" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12840,22 +12853,22 @@
         <v>644</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="I313" s="2" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
     </row>
     <row r="314" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12869,22 +12882,22 @@
         <v>644</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="I314" s="2" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
     </row>
     <row r="315" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12898,10 +12911,10 @@
         <v>644</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>39</v>
@@ -12910,10 +12923,10 @@
         <v>39</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="I315" s="7" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
     </row>
     <row r="316" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12927,10 +12940,10 @@
         <v>644</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>39</v>
@@ -12939,10 +12952,10 @@
         <v>39</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="I316" s="7" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
     </row>
     <row r="317" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12956,22 +12969,22 @@
         <v>644</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="I317" s="2" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
     </row>
     <row r="318" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12985,22 +12998,22 @@
         <v>644</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="I318" s="2" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
     </row>
     <row r="319" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13014,22 +13027,22 @@
         <v>644</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="I319" s="2" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
     </row>
     <row r="320" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13043,22 +13056,22 @@
         <v>644</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="I320" s="2" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
     </row>
     <row r="321" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13072,22 +13085,22 @@
         <v>644</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="I321" s="2" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
     </row>
     <row r="322" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13101,22 +13114,22 @@
         <v>644</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="I322" s="2" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
     </row>
     <row r="323" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13130,22 +13143,22 @@
         <v>644</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="I323" s="2" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
     </row>
     <row r="324" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13159,22 +13172,22 @@
         <v>644</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="I324" s="2" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
     </row>
     <row r="325" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13188,22 +13201,22 @@
         <v>644</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="I325" s="2" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
     </row>
     <row r="326" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13217,22 +13230,22 @@
         <v>644</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="I326" s="2" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
     </row>
     <row r="327" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13246,22 +13259,22 @@
         <v>644</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="I327" s="2" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
     </row>
     <row r="328" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13275,22 +13288,22 @@
         <v>644</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="I328" s="2" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="329" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13304,22 +13317,22 @@
         <v>644</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="I329" s="2" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
     </row>
     <row r="330" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13333,22 +13346,22 @@
         <v>644</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="I330" s="2" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
     </row>
     <row r="331" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13362,22 +13375,22 @@
         <v>644</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="I331" s="2" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
     </row>
     <row r="332" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13391,22 +13404,22 @@
         <v>644</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="I332" s="2" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
     </row>
     <row r="333" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13420,22 +13433,22 @@
         <v>644</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="I333" s="2" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
     </row>
     <row r="334" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13449,22 +13462,22 @@
         <v>644</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="I334" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
     </row>
     <row r="335" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13478,22 +13491,22 @@
         <v>644</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="I335" s="2" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
     </row>
     <row r="336" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13507,22 +13520,22 @@
         <v>644</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="I336" s="2" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
     </row>
     <row r="337" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13536,22 +13549,22 @@
         <v>644</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="I337" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
     </row>
     <row r="338" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13565,22 +13578,22 @@
         <v>644</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="I338" s="2" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
     </row>
     <row r="339" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13594,22 +13607,22 @@
         <v>644</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="I339" s="2" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
     </row>
     <row r="340" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13623,10 +13636,10 @@
         <v>644</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>39</v>
@@ -13635,10 +13648,10 @@
         <v>39</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="I340" s="7" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
     </row>
     <row r="341" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13652,10 +13665,10 @@
         <v>644</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>39</v>
@@ -13664,10 +13677,10 @@
         <v>39</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="I341" s="7" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
     </row>
     <row r="342" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13681,22 +13694,22 @@
         <v>644</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="I342" s="2" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
     </row>
     <row r="343" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13710,22 +13723,22 @@
         <v>644</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="I343" s="2" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
     </row>
     <row r="344" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13739,10 +13752,10 @@
         <v>644</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>39</v>
@@ -13751,10 +13764,10 @@
         <v>39</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="I344" s="6" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
     </row>
     <row r="345" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13768,10 +13781,10 @@
         <v>644</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>39</v>
@@ -13780,10 +13793,10 @@
         <v>39</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="I345" s="6" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
     </row>
     <row r="346" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13797,10 +13810,10 @@
         <v>644</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>39</v>
@@ -13809,10 +13822,10 @@
         <v>39</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="I346" s="6" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
     </row>
     <row r="347" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13826,10 +13839,10 @@
         <v>644</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>39</v>
@@ -13838,13 +13851,13 @@
         <v>39</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="I347" s="6" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="348" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="348" ht="18.75" customHeight="1" spans="1:9">
       <c r="A348" s="5">
         <v>21</v>
       </c>
@@ -13855,10 +13868,10 @@
         <v>644</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>100</v>
@@ -13867,13 +13880,13 @@
         <v>101</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="I348" s="2" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="349" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="349" ht="18.75" customHeight="1" spans="1:9">
       <c r="A349" s="5">
         <v>39</v>
       </c>
@@ -13884,10 +13897,10 @@
         <v>644</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F349" s="2" t="s">
         <v>100</v>
@@ -13896,10 +13909,10 @@
         <v>101</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="I349" s="2" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
     </row>
     <row r="350" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13913,22 +13926,22 @@
         <v>644</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>100</v>
+        <v>651</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>101</v>
+        <v>652</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="I350" s="2" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
     </row>
     <row r="351" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13942,22 +13955,22 @@
         <v>644</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>100</v>
+        <v>701</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>101</v>
+        <v>702</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="I351" s="2" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
     </row>
     <row r="352" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13971,22 +13984,22 @@
         <v>644</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="I352" s="2" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
     </row>
     <row r="353" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14000,22 +14013,22 @@
         <v>644</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="I353" s="2" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
     </row>
     <row r="354" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14029,22 +14042,22 @@
         <v>644</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="I354" s="2" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
     </row>
     <row r="355" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14058,22 +14071,22 @@
         <v>644</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="I355" s="2" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
     </row>
     <row r="356" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14087,22 +14100,22 @@
         <v>644</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="I356" s="2" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
     </row>
     <row r="357" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14116,22 +14129,22 @@
         <v>644</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="I357" s="2" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
     </row>
     <row r="358" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14145,10 +14158,10 @@
         <v>644</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>39</v>
@@ -14157,10 +14170,10 @@
         <v>39</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="I358" s="7" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
     </row>
     <row r="359" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14174,10 +14187,10 @@
         <v>644</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F359" s="2" t="s">
         <v>39</v>
@@ -14186,10 +14199,10 @@
         <v>39</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="I359" s="7" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="360" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14203,22 +14216,22 @@
         <v>644</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="I360" s="2" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
     </row>
     <row r="361" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14232,22 +14245,22 @@
         <v>644</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="I361" s="2" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
     </row>
     <row r="362" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14261,22 +14274,22 @@
         <v>644</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="I362" s="2" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
     </row>
     <row r="363" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14290,22 +14303,22 @@
         <v>644</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="I363" s="2" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
     </row>
     <row r="364" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14319,22 +14332,22 @@
         <v>644</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="I364" s="2" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
     </row>
     <row r="365" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14348,22 +14361,22 @@
         <v>644</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="I365" s="2" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
     </row>
     <row r="366" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14377,22 +14390,22 @@
         <v>644</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="I366" s="2" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
     </row>
     <row r="367" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14406,22 +14419,22 @@
         <v>644</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="I367" s="2" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
     </row>
     <row r="368" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14435,22 +14448,22 @@
         <v>644</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="I368" s="2" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
     </row>
     <row r="369" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14464,22 +14477,22 @@
         <v>644</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G369" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="I369" s="2" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
     </row>
     <row r="370" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14493,22 +14506,22 @@
         <v>644</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="I370" s="2" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
     </row>
     <row r="371" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14522,22 +14535,22 @@
         <v>644</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G371" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="I371" s="2" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
     </row>
     <row r="372" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14551,22 +14564,22 @@
         <v>644</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="I372" s="2" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
     </row>
     <row r="373" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14580,22 +14593,22 @@
         <v>644</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G373" s="2" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="I373" s="2" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
     </row>
     <row r="374" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14609,22 +14622,22 @@
         <v>644</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="I374" s="2" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
     </row>
     <row r="375" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14638,22 +14651,22 @@
         <v>644</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G375" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="I375" s="2" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
     </row>
     <row r="376" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14667,22 +14680,22 @@
         <v>644</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="I376" s="2" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
     </row>
     <row r="377" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14696,22 +14709,22 @@
         <v>644</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G377" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="I377" s="2" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
     </row>
     <row r="378" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14725,22 +14738,22 @@
         <v>644</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="I378" s="2" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
     </row>
     <row r="379" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14754,22 +14767,22 @@
         <v>644</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G379" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="I379" s="2" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
     </row>
     <row r="380" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14783,22 +14796,22 @@
         <v>644</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="I380" s="2" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
     </row>
     <row r="381" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14812,22 +14825,22 @@
         <v>644</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G381" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="I381" s="2" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
     </row>
     <row r="382" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14841,22 +14854,22 @@
         <v>644</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="I382" s="2" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
     </row>
     <row r="383" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14870,22 +14883,22 @@
         <v>644</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G383" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="I383" s="2" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
     </row>
     <row r="384" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14899,22 +14912,22 @@
         <v>644</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="I384" s="2" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
     </row>
     <row r="385" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14928,22 +14941,22 @@
         <v>644</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G385" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="I385" s="2" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
     </row>
     <row r="386" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14957,22 +14970,22 @@
         <v>644</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="I386" s="2" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
     </row>
     <row r="387" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14986,22 +14999,22 @@
         <v>644</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G387" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="I387" s="2" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
     </row>
     <row r="388" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15015,22 +15028,22 @@
         <v>644</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="I388" s="2" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
     </row>
     <row r="389" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15044,22 +15057,22 @@
         <v>644</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G389" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="I389" s="2" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
     </row>
     <row r="390" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15073,22 +15086,22 @@
         <v>644</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="I390" s="2" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
     </row>
     <row r="391" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15102,22 +15115,22 @@
         <v>644</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G391" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="I391" s="2" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
     </row>
     <row r="392" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15131,22 +15144,22 @@
         <v>644</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="I392" s="2" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
     </row>
     <row r="393" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15160,22 +15173,22 @@
         <v>644</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G393" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="I393" s="2" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="394" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15189,22 +15202,22 @@
         <v>644</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="I394" s="2" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
     </row>
     <row r="395" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15218,22 +15231,22 @@
         <v>644</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="G395" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="I395" s="2" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
     </row>
     <row r="396" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15241,28 +15254,28 @@
         <v>209</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="I396" s="2" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
     </row>
     <row r="397" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15270,28 +15283,28 @@
         <v>210</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G397" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="I397" s="2" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
     </row>
     <row r="398" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15299,28 +15312,28 @@
         <v>211</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="I398" s="2" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
     </row>
     <row r="399" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15328,28 +15341,28 @@
         <v>212</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G399" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="I399" s="2" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
     </row>
     <row r="400" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15357,28 +15370,28 @@
         <v>213</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="I400" s="2" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
     </row>
     <row r="401" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15386,28 +15399,28 @@
         <v>214</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G401" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="I401" s="2" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
     </row>
     <row r="402" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15415,28 +15428,28 @@
         <v>215</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G402" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="I402" s="2" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
     </row>
     <row r="403" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15444,28 +15457,28 @@
         <v>216</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G403" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="I403" s="2" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
     </row>
     <row r="404" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15473,35 +15486,41 @@
         <v>217</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G404" s="2" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="I404" s="2" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I404" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="利润表"/>
+        <filter val="资产负债表"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="合计"/>
+        <filter val="归少数股东"/>
       </filters>
     </filterColumn>
     <extLst/>

--- a/StocksIC/sort.xlsx
+++ b/StocksIC/sort.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="908">
   <si>
     <t>Index</t>
   </si>
@@ -1154,6 +1154,12 @@
     <t>投资活动现金流出小计</t>
   </si>
   <si>
+    <t>JE</t>
+  </si>
+  <si>
+    <t>净额</t>
+  </si>
+  <si>
     <t>col119</t>
   </si>
   <si>
@@ -1244,18 +1250,18 @@
     <t>现金及现金等价物</t>
   </si>
   <si>
+    <t>ZJE</t>
+  </si>
+  <si>
+    <t>总净额</t>
+  </si>
+  <si>
     <t>col131</t>
   </si>
   <si>
     <t>现金及现金等价物净增加额</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>时点</t>
-  </si>
-  <si>
     <t>col132</t>
   </si>
   <si>
@@ -1550,12 +1556,6 @@
     <t>现金及现金等价物净增加额（间接法）</t>
   </si>
   <si>
-    <t>ZJY</t>
-  </si>
-  <si>
-    <t>将净利润调节为经营活动现金流量</t>
-  </si>
-  <si>
     <t>col134</t>
   </si>
   <si>
@@ -1652,9 +1652,6 @@
     <t>其他</t>
   </si>
   <si>
-    <t>ZJYHD</t>
-  </si>
-  <si>
     <t>col580</t>
   </si>
   <si>
@@ -1665,12 +1662,6 @@
   </si>
   <si>
     <t>使用权资产折旧/摊销（万元）</t>
-  </si>
-  <si>
-    <t>DJWBD</t>
-  </si>
-  <si>
-    <t>现金及现金等价物净变动情况</t>
   </si>
   <si>
     <t>col154</t>
@@ -2775,7 +2766,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2795,6 +2786,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -3295,16 +3293,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3313,119 +3308,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3444,6 +3442,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -8480,16 +8479,16 @@
         <v>369</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>100</v>
+        <v>374</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>101</v>
+        <v>375</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="I162" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
+      </c>
+      <c r="I162" s="7" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="163" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -8515,13 +8514,13 @@
         <v>101</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="164" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="164" ht="18.75" customHeight="1" spans="1:9">
       <c r="A164" s="5">
         <v>108</v>
       </c>
@@ -8541,16 +8540,16 @@
         <v>82</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="165" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="165" ht="18.75" customHeight="1" spans="1:9">
       <c r="A165" s="5">
         <v>109</v>
       </c>
@@ -8570,16 +8569,16 @@
         <v>82</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="166" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="166" ht="18.75" customHeight="1" spans="1:9">
       <c r="A166" s="5">
         <v>110</v>
       </c>
@@ -8599,16 +8598,16 @@
         <v>82</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="167" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="167" ht="18.75" customHeight="1" spans="1:9">
       <c r="A167" s="5">
         <v>111</v>
       </c>
@@ -8628,16 +8627,16 @@
         <v>82</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="168" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="168" ht="18.75" customHeight="1" spans="1:9">
       <c r="A168" s="5">
         <v>112</v>
       </c>
@@ -8657,16 +8656,16 @@
         <v>82</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="169" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="169" ht="18.75" customHeight="1" spans="1:9">
       <c r="A169" s="5">
         <v>114</v>
       </c>
@@ -8683,19 +8682,19 @@
         <v>369</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="170" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="170" ht="18.75" customHeight="1" spans="1:9">
       <c r="A170" s="5">
         <v>115</v>
       </c>
@@ -8712,19 +8711,19 @@
         <v>369</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="171" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="171" ht="18.75" customHeight="1" spans="1:9">
       <c r="A171" s="5">
         <v>116</v>
       </c>
@@ -8741,19 +8740,19 @@
         <v>369</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="172" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="172" ht="18.75" customHeight="1" spans="1:9">
       <c r="A172" s="5">
         <v>117</v>
       </c>
@@ -8770,19 +8769,19 @@
         <v>369</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I172" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="173" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="173" ht="18.75" customHeight="1" spans="1:9">
       <c r="A173" s="5">
         <v>129</v>
       </c>
@@ -8796,19 +8795,19 @@
         <v>363</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="174" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -8822,25 +8821,25 @@
         <v>362</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>100</v>
+        <v>406</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>101</v>
+        <v>407</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="I174" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="175" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>408</v>
+      </c>
+      <c r="I174" s="8" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="175" ht="18.75" customHeight="1" spans="1:9">
       <c r="A175" s="5">
         <v>132</v>
       </c>
@@ -8851,25 +8850,25 @@
         <v>362</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="176" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="176" ht="18.75" customHeight="1" spans="1:9">
       <c r="A176" s="5">
         <v>133</v>
       </c>
@@ -8880,22 +8879,22 @@
         <v>362</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -8915,16 +8914,16 @@
         <v>362</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>100</v>
+        <v>406</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>101</v>
+        <v>407</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="I177" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
+      </c>
+      <c r="I177" s="8" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="178" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -8938,10 +8937,10 @@
         <v>362</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>100</v>
@@ -8950,10 +8949,10 @@
         <v>101</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I178" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -8967,10 +8966,10 @@
         <v>362</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>100</v>
@@ -8979,10 +8978,10 @@
         <v>101</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="180" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -8996,25 +8995,25 @@
         <v>362</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>100</v>
+        <v>374</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>101</v>
+        <v>375</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="I180" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="181" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>422</v>
+      </c>
+      <c r="I180" s="7" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="181" ht="18.75" customHeight="1" spans="1:9">
       <c r="A181" s="5">
         <v>120</v>
       </c>
@@ -9025,25 +9024,25 @@
         <v>362</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="182" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="182" ht="18.75" customHeight="1" spans="1:9">
       <c r="A182" s="5">
         <v>121</v>
       </c>
@@ -9054,25 +9053,25 @@
         <v>362</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="183" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="183" ht="18.75" customHeight="1" spans="1:9">
       <c r="A183" s="5">
         <v>122</v>
       </c>
@@ -9083,25 +9082,25 @@
         <v>362</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I183" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="184" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="184" ht="18.75" customHeight="1" spans="1:9">
       <c r="A184" s="5">
         <v>398</v>
       </c>
@@ -9112,25 +9111,25 @@
         <v>362</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I184" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="185" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="185" ht="18.75" customHeight="1" spans="1:9">
       <c r="A185" s="5">
         <v>124</v>
       </c>
@@ -9141,25 +9140,25 @@
         <v>362</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="186" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="186" ht="18.75" customHeight="1" spans="1:9">
       <c r="A186" s="5">
         <v>125</v>
       </c>
@@ -9170,25 +9169,25 @@
         <v>362</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I186" s="2" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="187" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="187" ht="18.75" customHeight="1" spans="1:9">
       <c r="A187" s="5">
         <v>126</v>
       </c>
@@ -9199,25 +9198,25 @@
         <v>362</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="188" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="188" ht="18.75" customHeight="1" spans="1:9">
       <c r="A188" s="5">
         <v>399</v>
       </c>
@@ -9228,22 +9227,22 @@
         <v>362</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="189" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -9257,10 +9256,10 @@
         <v>362</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>100</v>
@@ -9269,10 +9268,10 @@
         <v>101</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="190" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -9286,10 +9285,10 @@
         <v>362</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>100</v>
@@ -9298,10 +9297,10 @@
         <v>101</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="191" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -9315,22 +9314,22 @@
         <v>362</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>100</v>
+        <v>374</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>101</v>
+        <v>375</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="I191" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="192" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -9344,25 +9343,25 @@
         <v>362</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>100</v>
+        <v>374</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>101</v>
+        <v>375</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I192" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="193" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>448</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="193" ht="18.75" customHeight="1" spans="1:9">
       <c r="A193" s="5">
         <v>98</v>
       </c>
@@ -9373,25 +9372,25 @@
         <v>362</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I193" s="2" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="194" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="194" ht="18.75" customHeight="1" spans="1:9">
       <c r="A194" s="5">
         <v>99</v>
       </c>
@@ -9402,25 +9401,25 @@
         <v>362</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="195" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="195" ht="18.75" customHeight="1" spans="1:9">
       <c r="A195" s="5">
         <v>100</v>
       </c>
@@ -9431,25 +9430,25 @@
         <v>362</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I195" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="196" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="196" ht="18.75" customHeight="1" spans="1:9">
       <c r="A196" s="5">
         <v>383</v>
       </c>
@@ -9460,25 +9459,25 @@
         <v>362</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I196" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="197" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="197" ht="18.75" customHeight="1" spans="1:9">
       <c r="A197" s="5">
         <v>384</v>
       </c>
@@ -9489,25 +9488,25 @@
         <v>362</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I197" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="198" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="198" ht="18.75" customHeight="1" spans="1:9">
       <c r="A198" s="5">
         <v>385</v>
       </c>
@@ -9518,25 +9517,25 @@
         <v>362</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="199" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="199" ht="18.75" customHeight="1" spans="1:9">
       <c r="A199" s="5">
         <v>386</v>
       </c>
@@ -9547,25 +9546,25 @@
         <v>362</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="200" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="200" ht="18.75" customHeight="1" spans="1:9">
       <c r="A200" s="5">
         <v>387</v>
       </c>
@@ -9576,25 +9575,25 @@
         <v>362</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="201" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="201" ht="18.75" customHeight="1" spans="1:9">
       <c r="A201" s="5">
         <v>388</v>
       </c>
@@ -9605,25 +9604,25 @@
         <v>362</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I201" s="2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="202" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="202" ht="18.75" customHeight="1" spans="1:9">
       <c r="A202" s="5">
         <v>389</v>
       </c>
@@ -9634,25 +9633,25 @@
         <v>362</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I202" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="203" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="203" ht="18.75" customHeight="1" spans="1:9">
       <c r="A203" s="5">
         <v>390</v>
       </c>
@@ -9663,25 +9662,25 @@
         <v>362</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I203" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="204" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="204" ht="18.75" customHeight="1" spans="1:9">
       <c r="A204" s="5">
         <v>391</v>
       </c>
@@ -9692,25 +9691,25 @@
         <v>362</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="I204" s="2" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="205" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="205" ht="18.75" customHeight="1" spans="1:9">
       <c r="A205" s="5">
         <v>392</v>
       </c>
@@ -9721,25 +9720,25 @@
         <v>362</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I205" s="2" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="206" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="206" ht="18.75" customHeight="1" spans="1:9">
       <c r="A206" s="5">
         <v>102</v>
       </c>
@@ -9750,25 +9749,25 @@
         <v>362</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I206" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="207" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="207" ht="18.75" customHeight="1" spans="1:9">
       <c r="A207" s="5">
         <v>103</v>
       </c>
@@ -9779,25 +9778,25 @@
         <v>362</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="I207" s="2" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="208" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="208" ht="18.75" customHeight="1" spans="1:9">
       <c r="A208" s="5">
         <v>104</v>
       </c>
@@ -9808,25 +9807,25 @@
         <v>362</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I208" s="2" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="209" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="209" ht="18.75" customHeight="1" spans="1:9">
       <c r="A209" s="5">
         <v>105</v>
       </c>
@@ -9837,25 +9836,25 @@
         <v>362</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="I209" s="2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="210" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="210" ht="18.75" customHeight="1" spans="1:9">
       <c r="A210" s="5">
         <v>393</v>
       </c>
@@ -9866,25 +9865,25 @@
         <v>362</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I210" s="2" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="211" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="211" ht="18.75" customHeight="1" spans="1:9">
       <c r="A211" s="5">
         <v>394</v>
       </c>
@@ -9895,25 +9894,25 @@
         <v>362</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="I211" s="2" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="212" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="212" ht="18.75" customHeight="1" spans="1:9">
       <c r="A212" s="5">
         <v>395</v>
       </c>
@@ -9924,25 +9923,25 @@
         <v>362</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I212" s="2" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="213" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="213" ht="18.75" customHeight="1" spans="1:9">
       <c r="A213" s="5">
         <v>396</v>
       </c>
@@ -9953,25 +9952,25 @@
         <v>362</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="I213" s="2" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="214" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="214" ht="18.75" customHeight="1" spans="1:9">
       <c r="A214" s="5">
         <v>397</v>
       </c>
@@ -9982,22 +9981,22 @@
         <v>362</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I214" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="215" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10011,10 +10010,10 @@
         <v>362</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>39</v>
@@ -10023,10 +10022,10 @@
         <v>39</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="216" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10040,10 +10039,10 @@
         <v>362</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>39</v>
@@ -10052,10 +10051,10 @@
         <v>39</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="217" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10069,10 +10068,10 @@
         <v>362</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>39</v>
@@ -10081,10 +10080,10 @@
         <v>39</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="218" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10098,10 +10097,10 @@
         <v>362</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>39</v>
@@ -10110,10 +10109,10 @@
         <v>39</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="219" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10127,22 +10126,22 @@
         <v>362</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>100</v>
+        <v>374</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>101</v>
+        <v>375</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="I219" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
+      </c>
+      <c r="I219" s="7" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="220" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10156,25 +10155,25 @@
         <v>362</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>100</v>
+        <v>406</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>101</v>
+        <v>407</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="I220" s="2" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="221" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>506</v>
+      </c>
+      <c r="I220" s="8" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="221" ht="18.75" customHeight="1" spans="1:9">
       <c r="A221" s="5">
         <v>134</v>
       </c>
@@ -10185,16 +10184,16 @@
         <v>362</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>507</v>
+        <v>380</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>508</v>
@@ -10203,7 +10202,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="222" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="222" ht="18.75" customHeight="1" spans="1:9">
       <c r="A222" s="5">
         <v>135</v>
       </c>
@@ -10214,16 +10213,16 @@
         <v>362</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>510</v>
@@ -10232,7 +10231,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="223" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="223" ht="18.75" customHeight="1" spans="1:9">
       <c r="A223" s="5">
         <v>136</v>
       </c>
@@ -10243,16 +10242,16 @@
         <v>362</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>512</v>
@@ -10261,7 +10260,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="224" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="224" ht="18.75" customHeight="1" spans="1:9">
       <c r="A224" s="5">
         <v>137</v>
       </c>
@@ -10272,16 +10271,16 @@
         <v>362</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>514</v>
@@ -10290,7 +10289,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="225" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="225" ht="18.75" customHeight="1" spans="1:9">
       <c r="A225" s="5">
         <v>138</v>
       </c>
@@ -10301,16 +10300,16 @@
         <v>362</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>516</v>
@@ -10319,7 +10318,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="226" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="226" ht="18.75" customHeight="1" spans="1:9">
       <c r="A226" s="5">
         <v>139</v>
       </c>
@@ -10330,16 +10329,16 @@
         <v>362</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>518</v>
@@ -10348,7 +10347,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="227" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="227" ht="18.75" customHeight="1" spans="1:9">
       <c r="A227" s="5">
         <v>140</v>
       </c>
@@ -10359,16 +10358,16 @@
         <v>362</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>520</v>
@@ -10377,7 +10376,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="228" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="228" ht="18.75" customHeight="1" spans="1:9">
       <c r="A228" s="5">
         <v>141</v>
       </c>
@@ -10388,16 +10387,16 @@
         <v>362</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>522</v>
@@ -10406,7 +10405,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="229" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="229" ht="18.75" customHeight="1" spans="1:9">
       <c r="A229" s="5">
         <v>142</v>
       </c>
@@ -10417,16 +10416,16 @@
         <v>362</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>524</v>
@@ -10435,7 +10434,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="230" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="230" ht="18.75" customHeight="1" spans="1:9">
       <c r="A230" s="5">
         <v>143</v>
       </c>
@@ -10446,16 +10445,16 @@
         <v>362</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>526</v>
@@ -10464,7 +10463,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="231" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="231" ht="18.75" customHeight="1" spans="1:9">
       <c r="A231" s="5">
         <v>144</v>
       </c>
@@ -10475,16 +10474,16 @@
         <v>362</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>528</v>
@@ -10493,7 +10492,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="232" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="232" ht="18.75" customHeight="1" spans="1:9">
       <c r="A232" s="5">
         <v>145</v>
       </c>
@@ -10504,16 +10503,16 @@
         <v>362</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>530</v>
@@ -10522,7 +10521,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="233" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="233" ht="18.75" customHeight="1" spans="1:9">
       <c r="A233" s="5">
         <v>146</v>
       </c>
@@ -10533,16 +10532,16 @@
         <v>362</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>532</v>
@@ -10551,7 +10550,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="234" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="234" ht="18.75" customHeight="1" spans="1:9">
       <c r="A234" s="5">
         <v>147</v>
       </c>
@@ -10562,16 +10561,16 @@
         <v>362</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>534</v>
@@ -10580,7 +10579,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="235" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="235" ht="18.75" customHeight="1" spans="1:9">
       <c r="A235" s="5">
         <v>148</v>
       </c>
@@ -10591,16 +10590,16 @@
         <v>362</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>536</v>
@@ -10609,7 +10608,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="236" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="236" ht="18.75" customHeight="1" spans="1:9">
       <c r="A236" s="5">
         <v>149</v>
       </c>
@@ -10620,16 +10619,16 @@
         <v>362</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>506</v>
+        <v>391</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>538</v>
@@ -10638,7 +10637,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="237" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="237" ht="18.75" customHeight="1" spans="1:9">
       <c r="A237" s="5">
         <v>401</v>
       </c>
@@ -10649,25 +10648,25 @@
         <v>362</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F237" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H237" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="G237" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="H237" s="2" t="s">
+      <c r="I237" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="I237" s="2" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="238" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    </row>
+    <row r="238" ht="18.75" customHeight="1" spans="1:9">
       <c r="A238" s="5">
         <v>402</v>
       </c>
@@ -10678,25 +10677,25 @@
         <v>362</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>540</v>
+        <v>391</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="H238" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="I238" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="I238" s="2" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="239" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    </row>
+    <row r="239" ht="18.75" customHeight="1" spans="1:9">
       <c r="A239" s="5">
         <v>154</v>
       </c>
@@ -10707,25 +10706,25 @@
         <v>362</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F239" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I239" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="G239" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="I239" s="2" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="240" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    </row>
+    <row r="240" ht="18.75" customHeight="1" spans="1:9">
       <c r="A240" s="5">
         <v>155</v>
       </c>
@@ -10736,25 +10735,25 @@
         <v>362</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="G240" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H240" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="H240" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="I240" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="241" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="241" ht="18.75" customHeight="1" spans="1:9">
       <c r="A241" s="5">
         <v>156</v>
       </c>
@@ -10765,25 +10764,25 @@
         <v>362</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>546</v>
+        <v>380</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="I241" s="2" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="242" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="242" ht="18.75" customHeight="1" spans="1:9">
       <c r="A242" s="5">
         <v>157</v>
       </c>
@@ -10794,22 +10793,22 @@
         <v>362</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>546</v>
+        <v>380</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="I242" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="243" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10817,28 +10816,28 @@
         <v>172</v>
       </c>
       <c r="B243" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="H243" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="I243" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="G243" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="H243" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I243" s="2" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="244" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10846,28 +10845,28 @@
         <v>173</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C244" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="H244" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="D244" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="G244" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="H244" s="2" t="s">
-        <v>559</v>
-      </c>
       <c r="I244" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="245" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10875,28 +10874,28 @@
         <v>174</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I245" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="246" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10904,28 +10903,28 @@
         <v>175</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I246" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="247" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10933,28 +10932,28 @@
         <v>176</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="I247" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="248" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10962,28 +10961,28 @@
         <v>177</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="I248" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="249" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10991,28 +10990,28 @@
         <v>178</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="I249" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="250" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11020,28 +11019,28 @@
         <v>179</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="I250" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="251" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11049,28 +11048,28 @@
         <v>180</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="I251" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="252" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11078,28 +11077,28 @@
         <v>181</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="I252" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="253" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11107,28 +11106,28 @@
         <v>182</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I253" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="254" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11136,28 +11135,28 @@
         <v>237</v>
       </c>
       <c r="B254" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="H254" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="I254" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="G254" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="H254" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="I254" s="2" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="255" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11165,28 +11164,28 @@
         <v>238</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C255" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="H255" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="D255" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="G255" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="H255" s="2" t="s">
-        <v>583</v>
-      </c>
       <c r="I255" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="256" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11194,28 +11193,28 @@
         <v>239</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I256" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="257" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11223,28 +11222,28 @@
         <v>240</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="I257" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="258" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11252,28 +11251,28 @@
         <v>241</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="I258" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="259" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11281,28 +11280,28 @@
         <v>242</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="I259" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="260" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11310,28 +11309,28 @@
         <v>243</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="I260" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="261" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11339,28 +11338,28 @@
         <v>244</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="I261" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="262" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11368,28 +11367,28 @@
         <v>263</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="I262" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="263" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11397,28 +11396,28 @@
         <v>264</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="I263" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="264" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11426,28 +11425,28 @@
         <v>265</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="I264" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="265" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11455,28 +11454,28 @@
         <v>266</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="I265" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="266" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11484,28 +11483,28 @@
         <v>283</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="I266" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="267" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11513,28 +11512,28 @@
         <v>319</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="I267" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="268" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11542,28 +11541,28 @@
         <v>192</v>
       </c>
       <c r="B268" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="H268" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="I268" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="G268" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="H268" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="I268" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="269" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11571,28 +11570,28 @@
         <v>193</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C269" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F269" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="G269" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="H269" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="D269" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="G269" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="H269" s="2" t="s">
-        <v>613</v>
-      </c>
       <c r="I269" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="270" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11600,28 +11599,28 @@
         <v>194</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="I270" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="271" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11629,28 +11628,28 @@
         <v>195</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I271" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="272" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11658,28 +11657,28 @@
         <v>196</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="I272" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="273" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11687,28 +11686,28 @@
         <v>197</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I273" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="274" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11716,28 +11715,28 @@
         <v>198</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="I274" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="275" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11745,28 +11744,28 @@
         <v>199</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="I275" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="276" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11774,28 +11773,28 @@
         <v>200</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="I276" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="277" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11803,28 +11802,28 @@
         <v>201</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="I277" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="278" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11832,28 +11831,28 @@
         <v>202</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="I278" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="279" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11861,28 +11860,28 @@
         <v>203</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="I279" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="280" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11890,28 +11889,28 @@
         <v>204</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="I280" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="281" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11919,28 +11918,28 @@
         <v>206</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="I281" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="282" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11948,28 +11947,28 @@
         <v>207</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="I282" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="283" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11977,28 +11976,28 @@
         <v>208</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="I283" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="284" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12006,16 +12005,16 @@
         <v>70</v>
       </c>
       <c r="B284" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E284" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E284" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>39</v>
@@ -12024,10 +12023,10 @@
         <v>39</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="285" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12035,16 +12034,16 @@
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E285" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>39</v>
@@ -12053,10 +12052,10 @@
         <v>39</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="286" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12064,28 +12063,28 @@
         <v>72</v>
       </c>
       <c r="B286" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E286" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C286" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F286" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="G286" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="H286" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="I286" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="G286" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="H286" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="I286" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="287" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12093,45 +12092,45 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E287" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C287" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D287" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F287" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G287" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="H287" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="H287" s="2" t="s">
-        <v>655</v>
-      </c>
       <c r="I287" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="288" ht="18.75" customHeight="1" spans="1:9">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="288" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A288" s="5">
         <v>270</v>
       </c>
       <c r="B288" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E288" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>100</v>
@@ -12140,10 +12139,10 @@
         <v>101</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="I288" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="289" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12151,28 +12150,28 @@
         <v>64</v>
       </c>
       <c r="B289" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E289" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C289" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D289" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F289" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H289" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="I289" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="G289" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="H289" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="I289" s="2" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="290" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12180,28 +12179,28 @@
         <v>65</v>
       </c>
       <c r="B290" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E290" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C290" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D290" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F290" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G290" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H290" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="H290" s="2" t="s">
-        <v>663</v>
-      </c>
       <c r="I290" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="291" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12209,28 +12208,28 @@
         <v>66</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E291" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C291" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F291" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="I291" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="292" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12238,28 +12237,28 @@
         <v>67</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E292" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C292" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D292" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F292" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="I292" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="293" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12267,57 +12266,57 @@
         <v>68</v>
       </c>
       <c r="B293" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E293" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C293" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D293" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F293" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="I293" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="294" ht="18.75" customHeight="1" spans="1:9">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="294" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A294" s="5">
         <v>69</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E294" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C294" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F294" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="G294" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="H294" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="I294" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="G294" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="H294" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="I294" s="2" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="295" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12325,28 +12324,28 @@
         <v>267</v>
       </c>
       <c r="B295" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E295" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C295" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E295" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F295" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I295" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="296" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12354,28 +12353,28 @@
         <v>297</v>
       </c>
       <c r="B296" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E296" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C296" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F296" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="I296" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="297" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12383,28 +12382,28 @@
         <v>298</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E297" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C297" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D297" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E297" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F297" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="I297" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="298" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12412,28 +12411,28 @@
         <v>322</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E298" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C298" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F298" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="I298" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="299" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12441,16 +12440,16 @@
         <v>349</v>
       </c>
       <c r="B299" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E299" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D299" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E299" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>39</v>
@@ -12459,10 +12458,10 @@
         <v>39</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="I299" s="7" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="300" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12470,16 +12469,16 @@
         <v>350</v>
       </c>
       <c r="B300" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E300" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>39</v>
@@ -12488,10 +12487,10 @@
         <v>39</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="I300" s="7" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="301" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12499,16 +12498,16 @@
         <v>51</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>39</v>
@@ -12517,10 +12516,10 @@
         <v>39</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="302" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12528,16 +12527,16 @@
         <v>58</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>39</v>
@@ -12546,10 +12545,10 @@
         <v>39</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="303" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12557,16 +12556,16 @@
         <v>345</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>39</v>
@@ -12575,27 +12574,27 @@
         <v>39</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="304" ht="18.75" customHeight="1" spans="1:9">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="304" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A304" s="5">
         <v>54</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>100</v>
@@ -12604,27 +12603,27 @@
         <v>101</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="I304" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="305" ht="18.75" customHeight="1" spans="1:9">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="305" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A305" s="5">
         <v>62</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>100</v>
@@ -12633,10 +12632,10 @@
         <v>101</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="I305" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="306" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12644,28 +12643,28 @@
         <v>63</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="I306" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="307" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12673,28 +12672,28 @@
         <v>294</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F307" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G307" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="H307" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="I307" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="G307" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="H307" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="I307" s="2" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="308" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12702,28 +12701,28 @@
         <v>41</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F308" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="G308" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="H308" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="I308" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="G308" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="H308" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="I308" s="2" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="309" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12731,28 +12730,28 @@
         <v>42</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G309" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="H309" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="H309" s="2" t="s">
-        <v>709</v>
-      </c>
       <c r="I309" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="310" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12760,28 +12759,28 @@
         <v>43</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I310" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="311" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12789,28 +12788,28 @@
         <v>44</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="I311" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="312" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12818,28 +12817,28 @@
         <v>45</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="I312" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="313" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12847,28 +12846,28 @@
         <v>46</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="I313" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="314" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12876,28 +12875,28 @@
         <v>47</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="I314" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="315" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12905,16 +12904,16 @@
         <v>48</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>39</v>
@@ -12923,10 +12922,10 @@
         <v>39</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="I315" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="316" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12934,16 +12933,16 @@
         <v>49</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>39</v>
@@ -12952,10 +12951,10 @@
         <v>39</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="I316" s="7" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="317" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12963,28 +12962,28 @@
         <v>50</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="I317" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="318" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12992,28 +12991,28 @@
         <v>52</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="I318" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="319" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13021,28 +13020,28 @@
         <v>53</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="I319" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="320" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13050,28 +13049,28 @@
         <v>333</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="I320" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="321" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13079,28 +13078,28 @@
         <v>334</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="I321" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="322" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13108,28 +13107,28 @@
         <v>335</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="I322" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="323" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13137,28 +13136,28 @@
         <v>336</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="I323" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="324" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13166,28 +13165,28 @@
         <v>337</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="I324" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="325" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13195,28 +13194,28 @@
         <v>338</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="I325" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="326" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13224,28 +13223,28 @@
         <v>339</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="I326" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="327" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13253,28 +13252,28 @@
         <v>341</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="I327" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="328" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13282,28 +13281,28 @@
         <v>342</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="I328" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="329" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13311,28 +13310,28 @@
         <v>343</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="I329" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="330" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13340,28 +13339,28 @@
         <v>355</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="I330" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="331" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13369,28 +13368,28 @@
         <v>55</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F331" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="G331" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="H331" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="I331" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="G331" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="H331" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="I331" s="2" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="332" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13398,28 +13397,28 @@
         <v>56</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G332" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="H332" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="H332" s="2" t="s">
-        <v>757</v>
-      </c>
       <c r="I332" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="333" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13427,28 +13426,28 @@
         <v>57</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="I333" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="334" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13456,28 +13455,28 @@
         <v>59</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="I334" s="2" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="335" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13485,28 +13484,28 @@
         <v>60</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="I335" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="336" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13514,28 +13513,28 @@
         <v>61</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="I336" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="337" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13543,28 +13542,28 @@
         <v>296</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="I337" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="338" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13572,28 +13571,28 @@
         <v>340</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="I338" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="339" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13601,28 +13600,28 @@
         <v>344</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="I339" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="340" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13630,16 +13629,16 @@
         <v>346</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>39</v>
@@ -13648,10 +13647,10 @@
         <v>39</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="I340" s="7" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="341" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13659,16 +13658,16 @@
         <v>347</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>39</v>
@@ -13677,10 +13676,10 @@
         <v>39</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="I341" s="7" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="342" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13688,28 +13687,28 @@
         <v>348</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="I342" s="2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="343" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13717,28 +13716,28 @@
         <v>360</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="I343" s="2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="344" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13746,16 +13745,16 @@
         <v>14</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>39</v>
@@ -13764,10 +13763,10 @@
         <v>39</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="I344" s="6" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="345" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13775,16 +13774,16 @@
         <v>18</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>39</v>
@@ -13793,10 +13792,10 @@
         <v>39</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="I345" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="346" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13804,16 +13803,16 @@
         <v>29</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>39</v>
@@ -13822,10 +13821,10 @@
         <v>39</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="I346" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="347" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13833,16 +13832,16 @@
         <v>30</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>39</v>
@@ -13851,27 +13850,27 @@
         <v>39</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="I347" s="6" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="348" ht="18.75" customHeight="1" spans="1:9">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="348" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A348" s="5">
         <v>21</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>100</v>
@@ -13880,27 +13879,27 @@
         <v>101</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="I348" s="2" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="349" ht="18.75" customHeight="1" spans="1:9">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="349" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A349" s="5">
         <v>39</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F349" s="2" t="s">
         <v>100</v>
@@ -13909,10 +13908,10 @@
         <v>101</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="I349" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="350" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13920,28 +13919,28 @@
         <v>40</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="I350" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="351" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13949,28 +13948,28 @@
         <v>295</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="I351" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
     </row>
     <row r="352" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13978,28 +13977,28 @@
         <v>8</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F352" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="G352" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="H352" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="I352" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="G352" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="H352" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="I352" s="2" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="353" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14007,28 +14006,28 @@
         <v>9</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G353" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="H353" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="H353" s="2" t="s">
-        <v>803</v>
-      </c>
       <c r="I353" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="354" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14036,28 +14035,28 @@
         <v>10</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="I354" s="2" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
     </row>
     <row r="355" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14065,28 +14064,28 @@
         <v>11</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="I355" s="2" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="356" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14094,28 +14093,28 @@
         <v>12</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I356" s="2" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="357" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14123,28 +14122,28 @@
         <v>13</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="I357" s="2" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
     </row>
     <row r="358" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14152,16 +14151,16 @@
         <v>15</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>39</v>
@@ -14170,10 +14169,10 @@
         <v>39</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="I358" s="7" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
     </row>
     <row r="359" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14181,16 +14180,16 @@
         <v>16</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F359" s="2" t="s">
         <v>39</v>
@@ -14199,10 +14198,10 @@
         <v>39</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="I359" s="7" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="360" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14210,28 +14209,28 @@
         <v>17</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="I360" s="2" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="361" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14239,28 +14238,28 @@
         <v>19</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="I361" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="362" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14268,28 +14267,28 @@
         <v>20</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="I362" s="2" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="363" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14297,28 +14296,28 @@
         <v>323</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="I363" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="364" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14326,28 +14325,28 @@
         <v>324</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="I364" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="365" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14355,28 +14354,28 @@
         <v>325</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="I365" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="366" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14384,28 +14383,28 @@
         <v>326</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="I366" s="2" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="367" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14413,28 +14412,28 @@
         <v>327</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="I367" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="368" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14442,28 +14441,28 @@
         <v>328</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="I368" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="369" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14471,28 +14470,28 @@
         <v>329</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G369" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="I369" s="2" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="370" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14500,28 +14499,28 @@
         <v>330</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="I370" s="2" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
     </row>
     <row r="371" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14529,28 +14528,28 @@
         <v>331</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G371" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="I371" s="2" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="372" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14558,28 +14557,28 @@
         <v>356</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="I372" s="2" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
     </row>
     <row r="373" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14587,28 +14586,28 @@
         <v>358</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G373" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="I373" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="374" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14616,28 +14615,28 @@
         <v>357</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F374" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="G374" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="H374" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="I374" s="2" t="s">
         <v>845</v>
-      </c>
-      <c r="G374" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="H374" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="I374" s="2" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="375" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14645,28 +14644,28 @@
         <v>22</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G375" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="H375" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="H375" s="2" t="s">
-        <v>849</v>
-      </c>
       <c r="I375" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="376" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14674,28 +14673,28 @@
         <v>23</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="I376" s="2" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="377" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14703,28 +14702,28 @@
         <v>24</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G377" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="I377" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
     </row>
     <row r="378" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14732,28 +14731,28 @@
         <v>25</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="I378" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="379" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14761,28 +14760,28 @@
         <v>26</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G379" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="I379" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
     </row>
     <row r="380" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14790,28 +14789,28 @@
         <v>27</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="I380" s="2" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="381" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14819,28 +14818,28 @@
         <v>28</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G381" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="I381" s="2" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
     </row>
     <row r="382" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14848,28 +14847,28 @@
         <v>31</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="I382" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="383" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14877,28 +14876,28 @@
         <v>32</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G383" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="I383" s="2" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
     </row>
     <row r="384" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14906,28 +14905,28 @@
         <v>33</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="I384" s="2" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
     </row>
     <row r="385" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14935,28 +14934,28 @@
         <v>34</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G385" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="I385" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
     <row r="386" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14964,28 +14963,28 @@
         <v>35</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="I386" s="2" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="387" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14993,28 +14992,28 @@
         <v>36</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G387" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="I387" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
     </row>
     <row r="388" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15022,28 +15021,28 @@
         <v>37</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="I388" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="389" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15051,28 +15050,28 @@
         <v>38</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G389" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="I389" s="2" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="390" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15080,28 +15079,28 @@
         <v>332</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="I390" s="2" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="391" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15109,28 +15108,28 @@
         <v>351</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G391" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="I391" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
     </row>
     <row r="392" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15138,28 +15137,28 @@
         <v>352</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="I392" s="2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="393" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15167,28 +15166,28 @@
         <v>353</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G393" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="I393" s="2" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
     </row>
     <row r="394" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15196,28 +15195,28 @@
         <v>354</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="I394" s="2" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
     </row>
     <row r="395" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15225,28 +15224,28 @@
         <v>359</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G395" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="I395" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
     </row>
     <row r="396" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15254,28 +15253,28 @@
         <v>209</v>
       </c>
       <c r="B396" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="E396" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="F396" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="G396" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="H396" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="I396" s="2" t="s">
         <v>891</v>
-      </c>
-      <c r="C396" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="D396" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="E396" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="F396" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="G396" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="H396" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="I396" s="2" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="397" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15283,28 +15282,28 @@
         <v>210</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C397" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="E397" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="F397" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="G397" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="H397" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="D397" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="E397" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="F397" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="G397" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="H397" s="2" t="s">
-        <v>895</v>
-      </c>
       <c r="I397" s="2" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
     </row>
     <row r="398" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15312,28 +15311,28 @@
         <v>211</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="I398" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="399" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15341,28 +15340,28 @@
         <v>212</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G399" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="I399" s="2" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
     </row>
     <row r="400" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15370,28 +15369,28 @@
         <v>213</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="I400" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="401" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15399,28 +15398,28 @@
         <v>214</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G401" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="I401" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
     </row>
     <row r="402" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15428,28 +15427,28 @@
         <v>215</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G402" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="I402" s="2" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="403" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15457,28 +15456,28 @@
         <v>216</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G403" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="I403" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="404" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15486,41 +15485,45 @@
         <v>217</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G404" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="I404" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I404" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="资产负债表"/>
+        <filter val="现金流量表"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="合计"/>
-        <filter val="归少数股东"/>
+        <filter val="流入"/>
+        <filter val="现金及现金等价物净变动情况"/>
+        <filter val="汇率变动"/>
+        <filter val="时点"/>
+        <filter val="流出"/>
+        <filter val="将净利润调节为经营活动现金流量"/>
       </filters>
     </filterColumn>
     <extLst/>

--- a/StocksIC/sort.xlsx
+++ b/StocksIC/sort.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7695"/>
+    <workbookView windowWidth="21600" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="911">
   <si>
     <t>Index</t>
   </si>
@@ -1142,12 +1142,18 @@
     <t>投资活动</t>
   </si>
   <si>
+    <t>LRHJ</t>
+  </si>
+  <si>
     <t>col113</t>
   </si>
   <si>
     <t>投资活动现金流入小计</t>
   </si>
   <si>
+    <t>LCHJ</t>
+  </si>
+  <si>
     <t>col118</t>
   </si>
   <si>
@@ -1164,6 +1170,9 @@
   </si>
   <si>
     <t>投资活动产生的现金流量净额</t>
+  </si>
+  <si>
+    <t>JEY</t>
   </si>
   <si>
     <t>col316</t>
@@ -8404,7 +8413,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="160" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="160" ht="18.75" customHeight="1" spans="1:9">
       <c r="A160" s="5">
         <v>113</v>
       </c>
@@ -8421,19 +8430,19 @@
         <v>369</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>101</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I160" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="161" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="161" ht="18.75" customHeight="1" spans="1:9">
       <c r="A161" s="5">
         <v>118</v>
       </c>
@@ -8450,19 +8459,19 @@
         <v>369</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>100</v>
+        <v>373</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>101</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="162" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="162" ht="18.75" customHeight="1" spans="1:9">
       <c r="A162" s="5">
         <v>119</v>
       </c>
@@ -8479,19 +8488,19 @@
         <v>369</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="163" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="163" ht="18.75" customHeight="1" spans="1:9">
       <c r="A163" s="5">
         <v>315</v>
       </c>
@@ -8508,16 +8517,16 @@
         <v>369</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>101</v>
+        <v>377</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="I163" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
+      </c>
+      <c r="I163" s="7" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="164" ht="18.75" customHeight="1" spans="1:9">
@@ -8540,13 +8549,13 @@
         <v>82</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="165" ht="18.75" customHeight="1" spans="1:9">
@@ -8569,13 +8578,13 @@
         <v>82</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="166" ht="18.75" customHeight="1" spans="1:9">
@@ -8598,13 +8607,13 @@
         <v>82</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="167" ht="18.75" customHeight="1" spans="1:9">
@@ -8627,13 +8636,13 @@
         <v>82</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="168" ht="18.75" customHeight="1" spans="1:9">
@@ -8656,13 +8665,13 @@
         <v>82</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="169" ht="18.75" customHeight="1" spans="1:9">
@@ -8682,16 +8691,16 @@
         <v>369</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="170" ht="18.75" customHeight="1" spans="1:9">
@@ -8711,16 +8720,16 @@
         <v>369</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="171" ht="18.75" customHeight="1" spans="1:9">
@@ -8740,16 +8749,16 @@
         <v>369</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="172" ht="18.75" customHeight="1" spans="1:9">
@@ -8769,16 +8778,16 @@
         <v>369</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="I172" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="173" ht="18.75" customHeight="1" spans="1:9">
@@ -8795,22 +8804,22 @@
         <v>363</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="174" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="174" ht="18.75" customHeight="1" spans="1:9">
       <c r="A174" s="5">
         <v>131</v>
       </c>
@@ -8821,22 +8830,22 @@
         <v>362</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="I174" s="8" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="175" ht="18.75" customHeight="1" spans="1:9">
@@ -8850,22 +8859,22 @@
         <v>362</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="176" ht="18.75" customHeight="1" spans="1:9">
@@ -8879,25 +8888,25 @@
         <v>362</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="177" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="177" ht="18.75" customHeight="1" spans="1:9">
       <c r="A177" s="5">
         <v>309</v>
       </c>
@@ -8914,19 +8923,19 @@
         <v>362</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="I177" s="8" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="178" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="178" ht="18.75" customHeight="1" spans="1:9">
       <c r="A178" s="5">
         <v>123</v>
       </c>
@@ -8937,25 +8946,25 @@
         <v>362</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>101</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="I178" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="179" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="179" ht="18.75" customHeight="1" spans="1:9">
       <c r="A179" s="5">
         <v>127</v>
       </c>
@@ -8966,25 +8975,25 @@
         <v>362</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>100</v>
+        <v>373</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>101</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="180" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="180" ht="18.75" customHeight="1" spans="1:9">
       <c r="A180" s="5">
         <v>128</v>
       </c>
@@ -8995,22 +9004,22 @@
         <v>362</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" ht="18.75" customHeight="1" spans="1:9">
@@ -9024,22 +9033,22 @@
         <v>362</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" ht="18.75" customHeight="1" spans="1:9">
@@ -9053,22 +9062,22 @@
         <v>362</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="183" ht="18.75" customHeight="1" spans="1:9">
@@ -9082,22 +9091,22 @@
         <v>362</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="I183" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="184" ht="18.75" customHeight="1" spans="1:9">
@@ -9111,22 +9120,22 @@
         <v>362</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="I184" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="185" ht="18.75" customHeight="1" spans="1:9">
@@ -9140,22 +9149,22 @@
         <v>362</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" ht="18.75" customHeight="1" spans="1:9">
@@ -9169,22 +9178,22 @@
         <v>362</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="I186" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" ht="18.75" customHeight="1" spans="1:9">
@@ -9198,22 +9207,22 @@
         <v>362</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="188" ht="18.75" customHeight="1" spans="1:9">
@@ -9227,25 +9236,25 @@
         <v>362</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="189" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="189" ht="18.75" customHeight="1" spans="1:9">
       <c r="A189" s="5">
         <v>101</v>
       </c>
@@ -9256,25 +9265,25 @@
         <v>362</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>101</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="190" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="190" ht="18.75" customHeight="1" spans="1:9">
       <c r="A190" s="5">
         <v>106</v>
       </c>
@@ -9285,25 +9294,25 @@
         <v>362</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>100</v>
+        <v>373</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>101</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="191" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="191" ht="18.75" customHeight="1" spans="1:9">
       <c r="A191" s="5">
         <v>107</v>
       </c>
@@ -9314,25 +9323,25 @@
         <v>362</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="192" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="192" ht="18.75" customHeight="1" spans="1:9">
       <c r="A192" s="5">
         <v>306</v>
       </c>
@@ -9343,22 +9352,22 @@
         <v>362</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" ht="18.75" customHeight="1" spans="1:9">
@@ -9372,22 +9381,22 @@
         <v>362</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="I193" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="194" ht="18.75" customHeight="1" spans="1:9">
@@ -9401,22 +9410,22 @@
         <v>362</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="195" ht="18.75" customHeight="1" spans="1:9">
@@ -9430,22 +9439,22 @@
         <v>362</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="I195" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" ht="18.75" customHeight="1" spans="1:9">
@@ -9459,22 +9468,22 @@
         <v>362</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="I196" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" ht="18.75" customHeight="1" spans="1:9">
@@ -9488,22 +9497,22 @@
         <v>362</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="I197" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" ht="18.75" customHeight="1" spans="1:9">
@@ -9517,22 +9526,22 @@
         <v>362</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" ht="18.75" customHeight="1" spans="1:9">
@@ -9546,22 +9555,22 @@
         <v>362</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" ht="18.75" customHeight="1" spans="1:9">
@@ -9575,22 +9584,22 @@
         <v>362</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="201" ht="18.75" customHeight="1" spans="1:9">
@@ -9604,22 +9613,22 @@
         <v>362</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="I201" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" ht="18.75" customHeight="1" spans="1:9">
@@ -9633,22 +9642,22 @@
         <v>362</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I202" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" ht="18.75" customHeight="1" spans="1:9">
@@ -9662,22 +9671,22 @@
         <v>362</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I203" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="204" ht="18.75" customHeight="1" spans="1:9">
@@ -9691,22 +9700,22 @@
         <v>362</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="I204" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="205" ht="18.75" customHeight="1" spans="1:9">
@@ -9720,22 +9729,22 @@
         <v>362</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I205" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="206" ht="18.75" customHeight="1" spans="1:9">
@@ -9749,22 +9758,22 @@
         <v>362</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="I206" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="207" ht="18.75" customHeight="1" spans="1:9">
@@ -9778,22 +9787,22 @@
         <v>362</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="I207" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="208" ht="18.75" customHeight="1" spans="1:9">
@@ -9807,22 +9816,22 @@
         <v>362</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="I208" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" ht="18.75" customHeight="1" spans="1:9">
@@ -9836,22 +9845,22 @@
         <v>362</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="I209" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="210" ht="18.75" customHeight="1" spans="1:9">
@@ -9865,22 +9874,22 @@
         <v>362</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="I210" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="211" ht="18.75" customHeight="1" spans="1:9">
@@ -9894,22 +9903,22 @@
         <v>362</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="I211" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="212" ht="18.75" customHeight="1" spans="1:9">
@@ -9923,22 +9932,22 @@
         <v>362</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="I212" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="213" ht="18.75" customHeight="1" spans="1:9">
@@ -9952,22 +9961,22 @@
         <v>362</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="I213" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="214" ht="18.75" customHeight="1" spans="1:9">
@@ -9981,22 +9990,22 @@
         <v>362</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="I214" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="215" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10010,10 +10019,10 @@
         <v>362</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>39</v>
@@ -10022,10 +10031,10 @@
         <v>39</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="216" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10039,10 +10048,10 @@
         <v>362</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>39</v>
@@ -10051,10 +10060,10 @@
         <v>39</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="217" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10068,10 +10077,10 @@
         <v>362</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>39</v>
@@ -10080,10 +10089,10 @@
         <v>39</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="218" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10097,10 +10106,10 @@
         <v>362</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>39</v>
@@ -10109,13 +10118,13 @@
         <v>39</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="219" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="219" ht="18.75" customHeight="1" spans="1:9">
       <c r="A219" s="5">
         <v>150</v>
       </c>
@@ -10126,25 +10135,25 @@
         <v>362</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="220" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="220" ht="18.75" customHeight="1" spans="1:9">
       <c r="A220" s="5">
         <v>158</v>
       </c>
@@ -10155,22 +10164,22 @@
         <v>362</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="I220" s="8" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="221" ht="18.75" customHeight="1" spans="1:9">
@@ -10184,22 +10193,22 @@
         <v>362</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="I221" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="222" ht="18.75" customHeight="1" spans="1:9">
@@ -10213,22 +10222,22 @@
         <v>362</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="I222" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="223" ht="18.75" customHeight="1" spans="1:9">
@@ -10242,22 +10251,22 @@
         <v>362</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="I223" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="224" ht="18.75" customHeight="1" spans="1:9">
@@ -10271,22 +10280,22 @@
         <v>362</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="I224" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="225" ht="18.75" customHeight="1" spans="1:9">
@@ -10300,22 +10309,22 @@
         <v>362</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I225" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="226" ht="18.75" customHeight="1" spans="1:9">
@@ -10329,22 +10338,22 @@
         <v>362</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="I226" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="227" ht="18.75" customHeight="1" spans="1:9">
@@ -10358,22 +10367,22 @@
         <v>362</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="I227" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="228" ht="18.75" customHeight="1" spans="1:9">
@@ -10387,22 +10396,22 @@
         <v>362</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="I228" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="229" ht="18.75" customHeight="1" spans="1:9">
@@ -10416,22 +10425,22 @@
         <v>362</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="I229" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="230" ht="18.75" customHeight="1" spans="1:9">
@@ -10445,22 +10454,22 @@
         <v>362</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="I230" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="231" ht="18.75" customHeight="1" spans="1:9">
@@ -10474,22 +10483,22 @@
         <v>362</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="I231" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="232" ht="18.75" customHeight="1" spans="1:9">
@@ -10503,22 +10512,22 @@
         <v>362</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="I232" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="233" ht="18.75" customHeight="1" spans="1:9">
@@ -10532,22 +10541,22 @@
         <v>362</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I233" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="234" ht="18.75" customHeight="1" spans="1:9">
@@ -10561,22 +10570,22 @@
         <v>362</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="I234" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="235" ht="18.75" customHeight="1" spans="1:9">
@@ -10590,22 +10599,22 @@
         <v>362</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="I235" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="236" ht="18.75" customHeight="1" spans="1:9">
@@ -10619,22 +10628,22 @@
         <v>362</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I236" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="237" ht="18.75" customHeight="1" spans="1:9">
@@ -10648,22 +10657,22 @@
         <v>362</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I237" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="238" ht="18.75" customHeight="1" spans="1:9">
@@ -10677,22 +10686,22 @@
         <v>362</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I238" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="239" ht="18.75" customHeight="1" spans="1:9">
@@ -10706,22 +10715,22 @@
         <v>362</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I239" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="240" ht="18.75" customHeight="1" spans="1:9">
@@ -10735,22 +10744,22 @@
         <v>362</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="I240" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="241" ht="18.75" customHeight="1" spans="1:9">
@@ -10764,22 +10773,22 @@
         <v>362</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="I241" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="242" ht="18.75" customHeight="1" spans="1:9">
@@ -10793,22 +10802,22 @@
         <v>362</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="I242" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="243" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10816,28 +10825,28 @@
         <v>172</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="I243" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="244" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10845,28 +10854,28 @@
         <v>173</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="I244" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="245" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10874,28 +10883,28 @@
         <v>174</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I245" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="246" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10903,28 +10912,28 @@
         <v>175</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="I246" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="247" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10932,28 +10941,28 @@
         <v>176</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="I247" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="248" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10961,28 +10970,28 @@
         <v>177</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="I248" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="249" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10990,28 +10999,28 @@
         <v>178</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="I249" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="250" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11019,28 +11028,28 @@
         <v>179</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="I250" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="251" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11048,28 +11057,28 @@
         <v>180</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="I251" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="252" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11077,28 +11086,28 @@
         <v>181</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="I252" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="253" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11106,28 +11115,28 @@
         <v>182</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="I253" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="254" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11135,28 +11144,28 @@
         <v>237</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="I254" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="255" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11164,28 +11173,28 @@
         <v>238</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="I255" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="256" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11193,28 +11202,28 @@
         <v>239</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="I256" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="257" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11222,28 +11231,28 @@
         <v>240</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="I257" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="258" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11251,28 +11260,28 @@
         <v>241</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="I258" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="259" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11280,28 +11289,28 @@
         <v>242</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="I259" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="260" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11309,28 +11318,28 @@
         <v>243</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="I260" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="261" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11338,28 +11347,28 @@
         <v>244</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="I261" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="262" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11367,28 +11376,28 @@
         <v>263</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="I262" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="263" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11396,28 +11405,28 @@
         <v>264</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="I263" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="264" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11425,28 +11434,28 @@
         <v>265</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="I264" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="265" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11454,28 +11463,28 @@
         <v>266</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="I265" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="266" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11483,28 +11492,28 @@
         <v>283</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="I266" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="267" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11512,28 +11521,28 @@
         <v>319</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="I267" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="268" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11541,28 +11550,28 @@
         <v>192</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I268" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="269" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11570,28 +11579,28 @@
         <v>193</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="I269" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="270" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11599,28 +11608,28 @@
         <v>194</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="I270" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="271" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11628,28 +11637,28 @@
         <v>195</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="I271" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="272" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11657,28 +11666,28 @@
         <v>196</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="I272" s="2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="273" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11686,28 +11695,28 @@
         <v>197</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="I273" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="274" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11715,28 +11724,28 @@
         <v>198</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="I274" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="275" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11744,28 +11753,28 @@
         <v>199</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="I275" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="276" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11773,28 +11782,28 @@
         <v>200</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="I276" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="277" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11802,28 +11811,28 @@
         <v>201</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="I277" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="278" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11831,28 +11840,28 @@
         <v>202</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I278" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="279" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11860,28 +11869,28 @@
         <v>203</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="I279" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="280" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11889,28 +11898,28 @@
         <v>204</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="I280" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="281" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11918,28 +11927,28 @@
         <v>206</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="I281" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="282" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11947,28 +11956,28 @@
         <v>207</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="I282" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="283" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11976,28 +11985,28 @@
         <v>208</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="I283" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="284" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12005,16 +12014,16 @@
         <v>70</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>39</v>
@@ -12023,10 +12032,10 @@
         <v>39</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="285" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12034,16 +12043,16 @@
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>39</v>
@@ -12052,10 +12061,10 @@
         <v>39</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="286" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12063,28 +12072,28 @@
         <v>72</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="I286" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="287" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12092,28 +12101,28 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="I287" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="288" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12121,16 +12130,16 @@
         <v>270</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>100</v>
@@ -12139,10 +12148,10 @@
         <v>101</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="I288" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="289" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12150,28 +12159,28 @@
         <v>64</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="I289" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="290" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12179,28 +12188,28 @@
         <v>65</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="I290" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="291" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12208,28 +12217,28 @@
         <v>66</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I291" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="292" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12237,28 +12246,28 @@
         <v>67</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="I292" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="293" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12266,28 +12275,28 @@
         <v>68</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="I293" s="2" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="294" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12295,28 +12304,28 @@
         <v>69</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="I294" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="295" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12324,28 +12333,28 @@
         <v>267</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="I295" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="296" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12353,28 +12362,28 @@
         <v>297</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="I296" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="297" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12382,28 +12391,28 @@
         <v>298</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="I297" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="298" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12411,28 +12420,28 @@
         <v>322</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="I298" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="299" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12440,16 +12449,16 @@
         <v>349</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>39</v>
@@ -12458,10 +12467,10 @@
         <v>39</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="I299" s="7" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="300" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12469,16 +12478,16 @@
         <v>350</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>39</v>
@@ -12487,10 +12496,10 @@
         <v>39</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="I300" s="7" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="301" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12498,16 +12507,16 @@
         <v>51</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>39</v>
@@ -12516,10 +12525,10 @@
         <v>39</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="302" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12527,16 +12536,16 @@
         <v>58</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>39</v>
@@ -12545,10 +12554,10 @@
         <v>39</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="303" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12556,16 +12565,16 @@
         <v>345</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>39</v>
@@ -12574,10 +12583,10 @@
         <v>39</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="304" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12585,16 +12594,16 @@
         <v>54</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>100</v>
@@ -12603,10 +12612,10 @@
         <v>101</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="I304" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="305" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12614,16 +12623,16 @@
         <v>62</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>100</v>
@@ -12632,10 +12641,10 @@
         <v>101</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="I305" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="306" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12643,28 +12652,28 @@
         <v>63</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I306" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="307" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12672,28 +12681,28 @@
         <v>294</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="I307" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="308" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12701,28 +12710,28 @@
         <v>41</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="I308" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="309" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12730,28 +12739,28 @@
         <v>42</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="I309" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="310" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12759,28 +12768,28 @@
         <v>43</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="I310" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
     <row r="311" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12788,28 +12797,28 @@
         <v>44</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="I311" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="312" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12817,28 +12826,28 @@
         <v>45</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="I312" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="313" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12846,28 +12855,28 @@
         <v>46</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="I313" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="314" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12875,28 +12884,28 @@
         <v>47</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="I314" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="315" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12904,16 +12913,16 @@
         <v>48</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>39</v>
@@ -12922,10 +12931,10 @@
         <v>39</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="I315" s="7" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="316" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12933,16 +12942,16 @@
         <v>49</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>39</v>
@@ -12951,10 +12960,10 @@
         <v>39</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="I316" s="7" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="317" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12962,28 +12971,28 @@
         <v>50</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="I317" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="318" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12991,28 +13000,28 @@
         <v>52</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="I318" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="319" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13020,28 +13029,28 @@
         <v>53</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="I319" s="2" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="320" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13049,28 +13058,28 @@
         <v>333</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="I320" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="321" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13078,28 +13087,28 @@
         <v>334</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="I321" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="322" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13107,28 +13116,28 @@
         <v>335</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="I322" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="323" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13136,28 +13145,28 @@
         <v>336</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="I323" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="324" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13165,28 +13174,28 @@
         <v>337</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="I324" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="325" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13194,28 +13203,28 @@
         <v>338</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="I325" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="326" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13223,28 +13232,28 @@
         <v>339</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="I326" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="327" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13252,28 +13261,28 @@
         <v>341</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="I327" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="328" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13281,28 +13290,28 @@
         <v>342</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="I328" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="329" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13310,28 +13319,28 @@
         <v>343</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="I329" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="330" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13339,28 +13348,28 @@
         <v>355</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="I330" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="331" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13368,28 +13377,28 @@
         <v>55</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="I331" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="332" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13397,28 +13406,28 @@
         <v>56</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="I332" s="2" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="333" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13426,28 +13435,28 @@
         <v>57</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="I333" s="2" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="334" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13455,28 +13464,28 @@
         <v>59</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="I334" s="2" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="335" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13484,28 +13493,28 @@
         <v>60</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="I335" s="2" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="336" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13513,28 +13522,28 @@
         <v>61</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="I336" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="337" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13542,28 +13551,28 @@
         <v>296</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="I337" s="2" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="338" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13571,28 +13580,28 @@
         <v>340</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="I338" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="339" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13600,28 +13609,28 @@
         <v>344</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="I339" s="2" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="340" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13629,16 +13638,16 @@
         <v>346</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>39</v>
@@ -13647,10 +13656,10 @@
         <v>39</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="I340" s="7" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="341" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13658,16 +13667,16 @@
         <v>347</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>39</v>
@@ -13676,10 +13685,10 @@
         <v>39</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="I341" s="7" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="342" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13687,28 +13696,28 @@
         <v>348</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="I342" s="2" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="343" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13716,28 +13725,28 @@
         <v>360</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="I343" s="2" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="344" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13745,16 +13754,16 @@
         <v>14</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>39</v>
@@ -13763,10 +13772,10 @@
         <v>39</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="I344" s="6" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="345" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13774,16 +13783,16 @@
         <v>18</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>39</v>
@@ -13792,10 +13801,10 @@
         <v>39</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="I345" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="346" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13803,16 +13812,16 @@
         <v>29</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>39</v>
@@ -13821,10 +13830,10 @@
         <v>39</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="I346" s="6" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="347" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13832,16 +13841,16 @@
         <v>30</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>39</v>
@@ -13850,10 +13859,10 @@
         <v>39</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="I347" s="6" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
     </row>
     <row r="348" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13861,16 +13870,16 @@
         <v>21</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>100</v>
@@ -13879,10 +13888,10 @@
         <v>101</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="I348" s="2" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="349" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13890,16 +13899,16 @@
         <v>39</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F349" s="2" t="s">
         <v>100</v>
@@ -13908,10 +13917,10 @@
         <v>101</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="I349" s="2" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="350" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13919,28 +13928,28 @@
         <v>40</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="I350" s="2" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="351" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13948,28 +13957,28 @@
         <v>295</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="I351" s="2" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="352" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13977,28 +13986,28 @@
         <v>8</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="I352" s="2" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="353" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14006,28 +14015,28 @@
         <v>9</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="I353" s="2" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="354" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14035,28 +14044,28 @@
         <v>10</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="I354" s="2" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="355" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14064,28 +14073,28 @@
         <v>11</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="I355" s="2" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="356" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14093,28 +14102,28 @@
         <v>12</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="I356" s="2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="357" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14122,28 +14131,28 @@
         <v>13</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="I357" s="2" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="358" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14151,16 +14160,16 @@
         <v>15</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>39</v>
@@ -14169,10 +14178,10 @@
         <v>39</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="I358" s="7" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="359" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14180,16 +14189,16 @@
         <v>16</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F359" s="2" t="s">
         <v>39</v>
@@ -14198,10 +14207,10 @@
         <v>39</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="I359" s="7" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="360" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14209,28 +14218,28 @@
         <v>17</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="I360" s="2" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="361" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14238,28 +14247,28 @@
         <v>19</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="I361" s="2" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="362" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14267,28 +14276,28 @@
         <v>20</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="I362" s="2" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="363" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14296,28 +14305,28 @@
         <v>323</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="I363" s="2" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="364" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14325,28 +14334,28 @@
         <v>324</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="I364" s="2" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="365" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14354,28 +14363,28 @@
         <v>325</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="I365" s="2" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="366" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14383,28 +14392,28 @@
         <v>326</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="I366" s="2" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="367" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14412,28 +14421,28 @@
         <v>327</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="I367" s="2" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="368" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14441,28 +14450,28 @@
         <v>328</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="I368" s="2" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="369" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14470,28 +14479,28 @@
         <v>329</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G369" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="I369" s="2" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="370" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14499,28 +14508,28 @@
         <v>330</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="I370" s="2" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="371" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14528,28 +14537,28 @@
         <v>331</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G371" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="I371" s="2" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="372" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14557,28 +14566,28 @@
         <v>356</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="I372" s="2" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="373" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14586,28 +14595,28 @@
         <v>358</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G373" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="I373" s="2" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="374" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14615,28 +14624,28 @@
         <v>357</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="I374" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="375" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14644,28 +14653,28 @@
         <v>22</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G375" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="I375" s="2" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="376" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14673,28 +14682,28 @@
         <v>23</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="I376" s="2" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="377" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14702,28 +14711,28 @@
         <v>24</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G377" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="I377" s="2" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="378" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14731,28 +14740,28 @@
         <v>25</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="I378" s="2" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="379" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14760,28 +14769,28 @@
         <v>26</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G379" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="I379" s="2" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
     </row>
     <row r="380" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14789,28 +14798,28 @@
         <v>27</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="I380" s="2" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="381" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14818,28 +14827,28 @@
         <v>28</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G381" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="I381" s="2" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="382" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14847,28 +14856,28 @@
         <v>31</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="I382" s="2" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="383" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14876,28 +14885,28 @@
         <v>32</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G383" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="I383" s="2" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="384" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14905,28 +14914,28 @@
         <v>33</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="I384" s="2" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="385" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14934,28 +14943,28 @@
         <v>34</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G385" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="I385" s="2" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="386" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14963,28 +14972,28 @@
         <v>35</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="I386" s="2" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="387" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14992,28 +15001,28 @@
         <v>36</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G387" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="I387" s="2" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="388" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15021,28 +15030,28 @@
         <v>37</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="I388" s="2" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="389" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15050,28 +15059,28 @@
         <v>38</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G389" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="I389" s="2" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="390" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15079,28 +15088,28 @@
         <v>332</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="I390" s="2" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="391" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15108,28 +15117,28 @@
         <v>351</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G391" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="I391" s="2" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="392" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15137,28 +15146,28 @@
         <v>352</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="I392" s="2" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="393" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15166,28 +15175,28 @@
         <v>353</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G393" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="I393" s="2" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="394" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15195,28 +15204,28 @@
         <v>354</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="I394" s="2" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="395" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15224,28 +15233,28 @@
         <v>359</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G395" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="I395" s="2" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
     </row>
     <row r="396" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15253,28 +15262,28 @@
         <v>209</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="I396" s="2" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="397" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15282,28 +15291,28 @@
         <v>210</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G397" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="I397" s="2" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
     </row>
     <row r="398" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15311,28 +15320,28 @@
         <v>211</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="I398" s="2" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="399" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15340,28 +15349,28 @@
         <v>212</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G399" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="I399" s="2" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="400" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15369,28 +15378,28 @@
         <v>213</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="I400" s="2" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="401" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15398,28 +15407,28 @@
         <v>214</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G401" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="I401" s="2" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="402" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15427,28 +15436,28 @@
         <v>215</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G402" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="I402" s="2" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="403" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15456,28 +15465,28 @@
         <v>216</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G403" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="I403" s="2" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="404" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15485,28 +15494,28 @@
         <v>217</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G404" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="I404" s="2" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
   </sheetData>
@@ -15518,12 +15527,11 @@
     </filterColumn>
     <filterColumn colId="6">
       <filters>
+        <filter val="合计"/>
         <filter val="流入"/>
-        <filter val="现金及现金等价物净变动情况"/>
-        <filter val="汇率变动"/>
-        <filter val="时点"/>
         <filter val="流出"/>
-        <filter val="将净利润调节为经营活动现金流量"/>
+        <filter val="净额"/>
+        <filter val="总净额"/>
       </filters>
     </filterColumn>
     <extLst/>

--- a/StocksIC/sort.xlsx
+++ b/StocksIC/sort.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9675"/>
+    <workbookView windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3231" uniqueCount="911">
   <si>
     <t>Index</t>
   </si>
@@ -425,6 +425,12 @@
     <t>加：补贴收入</t>
   </si>
   <si>
+    <t>MGZB</t>
+  </si>
+  <si>
+    <t>每股指标</t>
+  </si>
+  <si>
     <t>col501</t>
   </si>
   <si>
@@ -975,12 +981,6 @@
   </si>
   <si>
     <t>特殊法人持股量(股)(机构持股)</t>
-  </si>
-  <si>
-    <t>MGZB</t>
-  </si>
-  <si>
-    <t>每股指标</t>
   </si>
   <si>
     <t>col1</t>
@@ -3447,10 +3447,10 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4216,7 +4216,7 @@
       <c r="H14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="7" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4709,11 +4709,11 @@
       <c r="H31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="32" ht="18.75" customHeight="1" spans="1:9">
       <c r="A32" s="5">
         <v>96</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="33" ht="18.75" customHeight="1" spans="1:9">
       <c r="A33" s="5">
         <v>97</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="34" ht="18.75" customHeight="1" spans="1:9">
       <c r="A34" s="5">
         <v>205</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="35" ht="18.75" customHeight="1" spans="1:9">
       <c r="A35" s="5">
         <v>301</v>
       </c>
@@ -4817,10 +4817,10 @@
         <v>83</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>92</v>
@@ -4829,7 +4829,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="36" ht="18.75" customHeight="1" spans="1:9">
       <c r="A36" s="5">
         <v>302</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="37" ht="18.75" customHeight="1" spans="1:9">
       <c r="A37" s="5">
         <v>93</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="38" ht="18.75" customHeight="1" spans="1:9">
       <c r="A38" s="5">
         <v>92</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="39" ht="18.75" customHeight="1" spans="1:9">
       <c r="A39" s="5">
         <v>95</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="40" ht="18.75" customHeight="1" spans="1:9">
       <c r="A40" s="5">
         <v>275</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="41" ht="18.75" customHeight="1" spans="1:9">
       <c r="A41" s="5">
         <v>282</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="42" ht="18.75" customHeight="1" spans="1:9">
       <c r="A42" s="5">
         <v>307</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="43" ht="18.75" customHeight="1" spans="1:9">
       <c r="A43" s="5">
         <v>308</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="44" ht="18.75" customHeight="1" spans="1:9">
       <c r="A44" s="5">
         <v>318</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="45" ht="18.75" customHeight="1" spans="1:9">
       <c r="A45" s="5">
         <v>86</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="46" ht="18.75" customHeight="1" spans="1:9">
       <c r="A46" s="5">
         <v>88</v>
       </c>
@@ -5148,7 +5148,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="47" ht="18.75" customHeight="1" spans="1:9">
       <c r="A47" s="5">
         <v>89</v>
       </c>
@@ -5202,7 +5202,7 @@
       <c r="H48" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="I48" s="7" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       <c r="H49" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="I49" s="6" t="s">
+      <c r="I49" s="7" t="s">
         <v>124</v>
       </c>
     </row>
@@ -5260,11 +5260,11 @@
       <c r="H50" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="I50" s="6" t="s">
+      <c r="I50" s="7" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="51" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="51" ht="18.75" customHeight="1" spans="1:9">
       <c r="A51" s="5">
         <v>85</v>
       </c>
@@ -5274,16 +5274,18 @@
       <c r="C51" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="I51" s="6" t="s">
         <v>128</v>
       </c>
     </row>
@@ -5312,7 +5314,7 @@
       <c r="H52" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I52" s="7" t="s">
         <v>130</v>
       </c>
     </row>
@@ -5321,22 +5323,28 @@
         <v>361</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>77</v>
+        <v>132</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -5350,10 +5358,10 @@
         <v>77</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>39</v>
@@ -5362,13 +5370,13 @@
         <v>39</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="55" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>137</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55" ht="18.75" customHeight="1" spans="1:9">
       <c r="A55" s="5">
         <v>379</v>
       </c>
@@ -5379,10 +5387,10 @@
         <v>77</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>100</v>
@@ -5391,13 +5399,13 @@
         <v>101</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="56" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="56" ht="18.75" customHeight="1" spans="1:9">
       <c r="A56" s="5">
         <v>75</v>
       </c>
@@ -5408,25 +5416,25 @@
         <v>77</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="57" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="57" ht="18.75" customHeight="1" spans="1:9">
       <c r="A57" s="5">
         <v>76</v>
       </c>
@@ -5437,25 +5445,25 @@
         <v>77</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="58" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" ht="18.75" customHeight="1" spans="1:9">
       <c r="A58" s="5">
         <v>77</v>
       </c>
@@ -5466,25 +5474,25 @@
         <v>77</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="59" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" ht="18.75" customHeight="1" spans="1:9">
       <c r="A59" s="5">
         <v>78</v>
       </c>
@@ -5495,25 +5503,25 @@
         <v>77</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="60" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" ht="18.75" customHeight="1" spans="1:9">
       <c r="A60" s="5">
         <v>80</v>
       </c>
@@ -5524,25 +5532,25 @@
         <v>77</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" ht="18.75" customHeight="1" spans="1:9">
       <c r="A61" s="5">
         <v>81</v>
       </c>
@@ -5553,25 +5561,25 @@
         <v>77</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="62" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="62" ht="18.75" customHeight="1" spans="1:9">
       <c r="A62" s="5">
         <v>82</v>
       </c>
@@ -5582,25 +5590,25 @@
         <v>77</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="63" ht="18.75" customHeight="1" spans="1:9">
       <c r="A63" s="5">
         <v>83</v>
       </c>
@@ -5611,25 +5619,25 @@
         <v>77</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="64" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="64" ht="18.75" customHeight="1" spans="1:9">
       <c r="A64" s="5">
         <v>84</v>
       </c>
@@ -5640,25 +5648,25 @@
         <v>77</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="65" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="65" ht="18.75" customHeight="1" spans="1:9">
       <c r="A65" s="5">
         <v>299</v>
       </c>
@@ -5669,25 +5677,25 @@
         <v>77</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="66" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="66" ht="18.75" customHeight="1" spans="1:9">
       <c r="A66" s="5">
         <v>300</v>
       </c>
@@ -5698,25 +5706,25 @@
         <v>77</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="67" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" ht="18.75" customHeight="1" spans="1:9">
       <c r="A67" s="5">
         <v>303</v>
       </c>
@@ -5727,25 +5735,25 @@
         <v>77</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="68" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" ht="18.75" customHeight="1" spans="1:9">
       <c r="A68" s="5">
         <v>370</v>
       </c>
@@ -5756,25 +5764,25 @@
         <v>77</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="69" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="69" ht="18.75" customHeight="1" spans="1:9">
       <c r="A69" s="5">
         <v>371</v>
       </c>
@@ -5785,25 +5793,25 @@
         <v>77</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="70" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="70" ht="18.75" customHeight="1" spans="1:9">
       <c r="A70" s="5">
         <v>372</v>
       </c>
@@ -5814,25 +5822,25 @@
         <v>77</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="71" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" ht="18.75" customHeight="1" spans="1:9">
       <c r="A71" s="5">
         <v>373</v>
       </c>
@@ -5843,25 +5851,25 @@
         <v>77</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="72" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72" ht="18.75" customHeight="1" spans="1:9">
       <c r="A72" s="5">
         <v>374</v>
       </c>
@@ -5872,25 +5880,25 @@
         <v>77</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="73" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="73" ht="18.75" customHeight="1" spans="1:9">
       <c r="A73" s="5">
         <v>375</v>
       </c>
@@ -5901,25 +5909,25 @@
         <v>77</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="74" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74" ht="18.75" customHeight="1" spans="1:9">
       <c r="A74" s="5">
         <v>377</v>
       </c>
@@ -5930,25 +5938,25 @@
         <v>77</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="75" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" ht="18.75" customHeight="1" spans="1:9">
       <c r="A75" s="5">
         <v>378</v>
       </c>
@@ -5959,25 +5967,25 @@
         <v>77</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="76" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="76" ht="18.75" customHeight="1" spans="1:9">
       <c r="A76" s="5">
         <v>380</v>
       </c>
@@ -5988,25 +5996,25 @@
         <v>77</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="77" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" ht="18.75" customHeight="1" spans="1:9">
       <c r="A77" s="5">
         <v>381</v>
       </c>
@@ -6017,25 +6025,25 @@
         <v>77</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="78" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="78" ht="18.75" customHeight="1" spans="1:9">
       <c r="A78" s="5">
         <v>304</v>
       </c>
@@ -6046,25 +6054,25 @@
         <v>77</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="79" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="79" ht="18.75" customHeight="1" spans="1:9">
       <c r="A79" s="5">
         <v>305</v>
       </c>
@@ -6075,25 +6083,25 @@
         <v>77</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="80" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="80" ht="18.75" customHeight="1" spans="1:9">
       <c r="A80" s="5">
         <v>362</v>
       </c>
@@ -6104,10 +6112,10 @@
         <v>77</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>100</v>
@@ -6116,13 +6124,13 @@
         <v>101</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="81" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="81" ht="18.75" customHeight="1" spans="1:9">
       <c r="A81" s="5">
         <v>74</v>
       </c>
@@ -6133,25 +6141,25 @@
         <v>77</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="82" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="82" ht="18.75" customHeight="1" spans="1:9">
       <c r="A82" s="5">
         <v>363</v>
       </c>
@@ -6162,25 +6170,25 @@
         <v>77</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="83" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83" ht="18.75" customHeight="1" spans="1:9">
       <c r="A83" s="5">
         <v>366</v>
       </c>
@@ -6191,25 +6199,25 @@
         <v>77</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="84" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" ht="18.75" customHeight="1" spans="1:9">
       <c r="A84" s="5">
         <v>367</v>
       </c>
@@ -6220,25 +6228,25 @@
         <v>77</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="85" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="85" ht="18.75" customHeight="1" spans="1:9">
       <c r="A85" s="5">
         <v>368</v>
       </c>
@@ -6249,25 +6257,25 @@
         <v>77</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="86" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="86" ht="18.75" customHeight="1" spans="1:9">
       <c r="A86" s="5">
         <v>369</v>
       </c>
@@ -6278,25 +6286,25 @@
         <v>77</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="87" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="87" ht="18.75" customHeight="1" spans="1:9">
       <c r="A87" s="5">
         <v>269</v>
       </c>
@@ -6307,10 +6315,10 @@
         <v>77</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>100</v>
@@ -6319,13 +6327,13 @@
         <v>101</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="88" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" ht="18.75" customHeight="1" spans="1:9">
       <c r="A88" s="5">
         <v>268</v>
       </c>
@@ -6336,25 +6344,25 @@
         <v>77</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="89" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="89" ht="18.75" customHeight="1" spans="1:9">
       <c r="A89" s="5">
         <v>364</v>
       </c>
@@ -6365,25 +6373,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="90" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="90" ht="18.75" customHeight="1" spans="1:9">
       <c r="A90" s="5">
         <v>365</v>
       </c>
@@ -6394,22 +6402,22 @@
         <v>77</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="91" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6417,28 +6425,28 @@
         <v>229</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="92" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6446,28 +6454,28 @@
         <v>230</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="93" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6475,28 +6483,28 @@
         <v>231</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="94" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6504,28 +6512,28 @@
         <v>232</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6533,28 +6541,28 @@
         <v>233</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="96" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6562,28 +6570,28 @@
         <v>234</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6591,28 +6599,28 @@
         <v>235</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6620,28 +6628,28 @@
         <v>236</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="99" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6649,28 +6657,28 @@
         <v>281</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="100" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6678,28 +6686,28 @@
         <v>310</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="101" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6707,28 +6715,28 @@
         <v>311</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="102" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6736,28 +6744,28 @@
         <v>183</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="103" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6765,28 +6773,28 @@
         <v>184</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6794,28 +6802,28 @@
         <v>185</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="105" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6823,28 +6831,28 @@
         <v>186</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6852,28 +6860,28 @@
         <v>187</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="107" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6881,28 +6889,28 @@
         <v>188</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6910,28 +6918,28 @@
         <v>189</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="109" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6939,28 +6947,28 @@
         <v>190</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="110" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6968,28 +6976,28 @@
         <v>191</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -6997,28 +7005,28 @@
         <v>245</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7026,28 +7034,28 @@
         <v>246</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="113" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7055,28 +7063,28 @@
         <v>247</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="114" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7084,28 +7092,28 @@
         <v>248</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7113,28 +7121,28 @@
         <v>249</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="116" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7142,28 +7150,28 @@
         <v>250</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7171,28 +7179,28 @@
         <v>251</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7200,28 +7208,28 @@
         <v>252</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="119" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7229,28 +7237,28 @@
         <v>253</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="120" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7258,28 +7266,28 @@
         <v>254</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="121" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7287,28 +7295,28 @@
         <v>255</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="122" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7316,28 +7324,28 @@
         <v>256</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="123" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7345,28 +7353,28 @@
         <v>257</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="124" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7374,28 +7382,28 @@
         <v>258</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="125" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7403,28 +7411,28 @@
         <v>259</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7432,28 +7440,28 @@
         <v>260</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="127" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7461,28 +7469,28 @@
         <v>261</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="128" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7490,28 +7498,28 @@
         <v>262</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="129" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7519,28 +7527,28 @@
         <v>271</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="130" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7548,28 +7556,28 @@
         <v>272</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="131" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7577,28 +7585,28 @@
         <v>273</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="132" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7606,28 +7614,28 @@
         <v>274</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="133" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7635,28 +7643,28 @@
         <v>276</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="134" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7664,28 +7672,28 @@
         <v>277</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="135" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7693,28 +7701,28 @@
         <v>278</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="136" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7722,28 +7730,28 @@
         <v>279</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="137" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -7751,22 +7759,22 @@
         <v>1</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>317</v>
@@ -7780,22 +7788,22 @@
         <v>2</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>319</v>
@@ -7809,22 +7817,22 @@
         <v>3</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>321</v>
@@ -7838,22 +7846,22 @@
         <v>4</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>323</v>
@@ -7867,22 +7875,22 @@
         <v>5</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>325</v>
@@ -7896,22 +7904,22 @@
         <v>6</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>327</v>
@@ -7925,22 +7933,22 @@
         <v>7</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>329</v>
@@ -7954,22 +7962,22 @@
         <v>280</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>331</v>
@@ -7983,22 +7991,22 @@
         <v>320</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>333</v>
@@ -8012,22 +8020,22 @@
         <v>321</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>335</v>
@@ -8380,7 +8388,7 @@
       <c r="H158" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="I158" s="6" t="s">
+      <c r="I158" s="7" t="s">
         <v>365</v>
       </c>
     </row>
@@ -8409,11 +8417,11 @@
       <c r="H159" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="I159" s="6" t="s">
+      <c r="I159" s="7" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="160" ht="18.75" customHeight="1" spans="1:9">
+    <row r="160" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A160" s="5">
         <v>113</v>
       </c>
@@ -8442,7 +8450,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="161" ht="18.75" customHeight="1" spans="1:9">
+    <row r="161" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A161" s="5">
         <v>118</v>
       </c>
@@ -8471,7 +8479,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="162" ht="18.75" customHeight="1" spans="1:9">
+    <row r="162" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A162" s="5">
         <v>119</v>
       </c>
@@ -8496,11 +8504,11 @@
       <c r="H162" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="I162" s="7" t="s">
+      <c r="I162" s="6" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="163" ht="18.75" customHeight="1" spans="1:9">
+    <row r="163" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A163" s="5">
         <v>315</v>
       </c>
@@ -8525,11 +8533,11 @@
       <c r="H163" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="I163" s="7" t="s">
+      <c r="I163" s="6" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="164" ht="18.75" customHeight="1" spans="1:9">
+    <row r="164" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A164" s="5">
         <v>108</v>
       </c>
@@ -8558,7 +8566,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="165" ht="18.75" customHeight="1" spans="1:9">
+    <row r="165" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A165" s="5">
         <v>109</v>
       </c>
@@ -8587,7 +8595,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="166" ht="18.75" customHeight="1" spans="1:9">
+    <row r="166" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A166" s="5">
         <v>110</v>
       </c>
@@ -8616,7 +8624,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="167" ht="18.75" customHeight="1" spans="1:9">
+    <row r="167" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A167" s="5">
         <v>111</v>
       </c>
@@ -8645,7 +8653,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="168" ht="18.75" customHeight="1" spans="1:9">
+    <row r="168" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A168" s="5">
         <v>112</v>
       </c>
@@ -8674,7 +8682,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="169" ht="18.75" customHeight="1" spans="1:9">
+    <row r="169" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A169" s="5">
         <v>114</v>
       </c>
@@ -8703,7 +8711,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="170" ht="18.75" customHeight="1" spans="1:9">
+    <row r="170" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A170" s="5">
         <v>115</v>
       </c>
@@ -8732,7 +8740,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="171" ht="18.75" customHeight="1" spans="1:9">
+    <row r="171" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A171" s="5">
         <v>116</v>
       </c>
@@ -8761,7 +8769,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="172" ht="18.75" customHeight="1" spans="1:9">
+    <row r="172" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A172" s="5">
         <v>117</v>
       </c>
@@ -8790,7 +8798,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="173" ht="18.75" customHeight="1" spans="1:9">
+    <row r="173" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A173" s="5">
         <v>129</v>
       </c>
@@ -8819,7 +8827,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="174" ht="18.75" customHeight="1" spans="1:9">
+    <row r="174" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A174" s="5">
         <v>131</v>
       </c>
@@ -8848,7 +8856,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="175" ht="18.75" customHeight="1" spans="1:9">
+    <row r="175" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A175" s="5">
         <v>132</v>
       </c>
@@ -8877,7 +8885,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="176" ht="18.75" customHeight="1" spans="1:9">
+    <row r="176" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A176" s="5">
         <v>133</v>
       </c>
@@ -8906,7 +8914,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="177" ht="18.75" customHeight="1" spans="1:9">
+    <row r="177" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A177" s="5">
         <v>309</v>
       </c>
@@ -8935,7 +8943,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="178" ht="18.75" customHeight="1" spans="1:9">
+    <row r="178" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A178" s="5">
         <v>123</v>
       </c>
@@ -8964,7 +8972,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="179" ht="18.75" customHeight="1" spans="1:9">
+    <row r="179" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A179" s="5">
         <v>127</v>
       </c>
@@ -8993,7 +9001,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="180" ht="18.75" customHeight="1" spans="1:9">
+    <row r="180" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A180" s="5">
         <v>128</v>
       </c>
@@ -9018,11 +9026,11 @@
       <c r="H180" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="I180" s="7" t="s">
+      <c r="I180" s="6" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="181" ht="18.75" customHeight="1" spans="1:9">
+    <row r="181" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A181" s="5">
         <v>120</v>
       </c>
@@ -9051,7 +9059,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="182" ht="18.75" customHeight="1" spans="1:9">
+    <row r="182" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A182" s="5">
         <v>121</v>
       </c>
@@ -9080,7 +9088,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="183" ht="18.75" customHeight="1" spans="1:9">
+    <row r="183" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A183" s="5">
         <v>122</v>
       </c>
@@ -9109,7 +9117,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="184" ht="18.75" customHeight="1" spans="1:9">
+    <row r="184" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A184" s="5">
         <v>398</v>
       </c>
@@ -9138,7 +9146,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="185" ht="18.75" customHeight="1" spans="1:9">
+    <row r="185" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A185" s="5">
         <v>124</v>
       </c>
@@ -9167,7 +9175,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="186" ht="18.75" customHeight="1" spans="1:9">
+    <row r="186" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A186" s="5">
         <v>125</v>
       </c>
@@ -9196,7 +9204,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="187" ht="18.75" customHeight="1" spans="1:9">
+    <row r="187" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A187" s="5">
         <v>126</v>
       </c>
@@ -9225,7 +9233,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="188" ht="18.75" customHeight="1" spans="1:9">
+    <row r="188" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A188" s="5">
         <v>399</v>
       </c>
@@ -9254,7 +9262,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="189" ht="18.75" customHeight="1" spans="1:9">
+    <row r="189" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A189" s="5">
         <v>101</v>
       </c>
@@ -9283,7 +9291,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="190" ht="18.75" customHeight="1" spans="1:9">
+    <row r="190" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A190" s="5">
         <v>106</v>
       </c>
@@ -9312,7 +9320,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="191" ht="18.75" customHeight="1" spans="1:9">
+    <row r="191" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A191" s="5">
         <v>107</v>
       </c>
@@ -9337,11 +9345,11 @@
       <c r="H191" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="I191" s="7" t="s">
+      <c r="I191" s="6" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="192" ht="18.75" customHeight="1" spans="1:9">
+    <row r="192" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A192" s="5">
         <v>306</v>
       </c>
@@ -9366,11 +9374,11 @@
       <c r="H192" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="I192" s="7" t="s">
+      <c r="I192" s="6" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="193" ht="18.75" customHeight="1" spans="1:9">
+    <row r="193" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A193" s="5">
         <v>98</v>
       </c>
@@ -9399,7 +9407,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="194" ht="18.75" customHeight="1" spans="1:9">
+    <row r="194" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A194" s="5">
         <v>99</v>
       </c>
@@ -9428,7 +9436,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="195" ht="18.75" customHeight="1" spans="1:9">
+    <row r="195" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A195" s="5">
         <v>100</v>
       </c>
@@ -9457,7 +9465,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="196" ht="18.75" customHeight="1" spans="1:9">
+    <row r="196" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A196" s="5">
         <v>383</v>
       </c>
@@ -9486,7 +9494,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="197" ht="18.75" customHeight="1" spans="1:9">
+    <row r="197" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A197" s="5">
         <v>384</v>
       </c>
@@ -9515,7 +9523,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="198" ht="18.75" customHeight="1" spans="1:9">
+    <row r="198" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A198" s="5">
         <v>385</v>
       </c>
@@ -9544,7 +9552,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="199" ht="18.75" customHeight="1" spans="1:9">
+    <row r="199" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A199" s="5">
         <v>386</v>
       </c>
@@ -9573,7 +9581,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="200" ht="18.75" customHeight="1" spans="1:9">
+    <row r="200" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A200" s="5">
         <v>387</v>
       </c>
@@ -9602,7 +9610,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="201" ht="18.75" customHeight="1" spans="1:9">
+    <row r="201" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A201" s="5">
         <v>388</v>
       </c>
@@ -9631,7 +9639,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="202" ht="18.75" customHeight="1" spans="1:9">
+    <row r="202" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A202" s="5">
         <v>389</v>
       </c>
@@ -9660,7 +9668,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="203" ht="18.75" customHeight="1" spans="1:9">
+    <row r="203" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A203" s="5">
         <v>390</v>
       </c>
@@ -9689,7 +9697,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="204" ht="18.75" customHeight="1" spans="1:9">
+    <row r="204" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A204" s="5">
         <v>391</v>
       </c>
@@ -9718,7 +9726,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="205" ht="18.75" customHeight="1" spans="1:9">
+    <row r="205" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A205" s="5">
         <v>392</v>
       </c>
@@ -9747,7 +9755,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="206" ht="18.75" customHeight="1" spans="1:9">
+    <row r="206" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A206" s="5">
         <v>102</v>
       </c>
@@ -9776,7 +9784,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="207" ht="18.75" customHeight="1" spans="1:9">
+    <row r="207" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A207" s="5">
         <v>103</v>
       </c>
@@ -9805,7 +9813,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="208" ht="18.75" customHeight="1" spans="1:9">
+    <row r="208" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A208" s="5">
         <v>104</v>
       </c>
@@ -9834,7 +9842,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="209" ht="18.75" customHeight="1" spans="1:9">
+    <row r="209" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A209" s="5">
         <v>105</v>
       </c>
@@ -9863,7 +9871,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="210" ht="18.75" customHeight="1" spans="1:9">
+    <row r="210" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A210" s="5">
         <v>393</v>
       </c>
@@ -9892,7 +9900,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="211" ht="18.75" customHeight="1" spans="1:9">
+    <row r="211" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A211" s="5">
         <v>394</v>
       </c>
@@ -9921,7 +9929,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="212" ht="18.75" customHeight="1" spans="1:9">
+    <row r="212" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A212" s="5">
         <v>395</v>
       </c>
@@ -9950,7 +9958,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="213" ht="18.75" customHeight="1" spans="1:9">
+    <row r="213" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A213" s="5">
         <v>396</v>
       </c>
@@ -9979,7 +9987,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="214" ht="18.75" customHeight="1" spans="1:9">
+    <row r="214" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A214" s="5">
         <v>397</v>
       </c>
@@ -10033,7 +10041,7 @@
       <c r="H215" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="I215" s="6" t="s">
+      <c r="I215" s="7" t="s">
         <v>500</v>
       </c>
     </row>
@@ -10062,7 +10070,7 @@
       <c r="H216" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="I216" s="6" t="s">
+      <c r="I216" s="7" t="s">
         <v>502</v>
       </c>
     </row>
@@ -10091,7 +10099,7 @@
       <c r="H217" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="I217" s="6" t="s">
+      <c r="I217" s="7" t="s">
         <v>504</v>
       </c>
     </row>
@@ -10120,11 +10128,11 @@
       <c r="H218" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="I218" s="6" t="s">
+      <c r="I218" s="7" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="219" ht="18.75" customHeight="1" spans="1:9">
+    <row r="219" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A219" s="5">
         <v>150</v>
       </c>
@@ -10149,11 +10157,11 @@
       <c r="H219" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="I219" s="7" t="s">
+      <c r="I219" s="6" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="220" ht="18.75" customHeight="1" spans="1:9">
+    <row r="220" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A220" s="5">
         <v>158</v>
       </c>
@@ -10182,7 +10190,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="221" ht="18.75" customHeight="1" spans="1:9">
+    <row r="221" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A221" s="5">
         <v>134</v>
       </c>
@@ -10211,7 +10219,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="222" ht="18.75" customHeight="1" spans="1:9">
+    <row r="222" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A222" s="5">
         <v>135</v>
       </c>
@@ -10240,7 +10248,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="223" ht="18.75" customHeight="1" spans="1:9">
+    <row r="223" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A223" s="5">
         <v>136</v>
       </c>
@@ -10269,7 +10277,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="224" ht="18.75" customHeight="1" spans="1:9">
+    <row r="224" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A224" s="5">
         <v>137</v>
       </c>
@@ -10298,7 +10306,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="225" ht="18.75" customHeight="1" spans="1:9">
+    <row r="225" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A225" s="5">
         <v>138</v>
       </c>
@@ -10327,7 +10335,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="226" ht="18.75" customHeight="1" spans="1:9">
+    <row r="226" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A226" s="5">
         <v>139</v>
       </c>
@@ -10356,7 +10364,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="227" ht="18.75" customHeight="1" spans="1:9">
+    <row r="227" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A227" s="5">
         <v>140</v>
       </c>
@@ -10385,7 +10393,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="228" ht="18.75" customHeight="1" spans="1:9">
+    <row r="228" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A228" s="5">
         <v>141</v>
       </c>
@@ -10414,7 +10422,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="229" ht="18.75" customHeight="1" spans="1:9">
+    <row r="229" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A229" s="5">
         <v>142</v>
       </c>
@@ -10443,7 +10451,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="230" ht="18.75" customHeight="1" spans="1:9">
+    <row r="230" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A230" s="5">
         <v>143</v>
       </c>
@@ -10472,7 +10480,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="231" ht="18.75" customHeight="1" spans="1:9">
+    <row r="231" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A231" s="5">
         <v>144</v>
       </c>
@@ -10501,7 +10509,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="232" ht="18.75" customHeight="1" spans="1:9">
+    <row r="232" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A232" s="5">
         <v>145</v>
       </c>
@@ -10530,7 +10538,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="233" ht="18.75" customHeight="1" spans="1:9">
+    <row r="233" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A233" s="5">
         <v>146</v>
       </c>
@@ -10559,7 +10567,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="234" ht="18.75" customHeight="1" spans="1:9">
+    <row r="234" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A234" s="5">
         <v>147</v>
       </c>
@@ -10588,7 +10596,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="235" ht="18.75" customHeight="1" spans="1:9">
+    <row r="235" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A235" s="5">
         <v>148</v>
       </c>
@@ -10617,7 +10625,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="236" ht="18.75" customHeight="1" spans="1:9">
+    <row r="236" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A236" s="5">
         <v>149</v>
       </c>
@@ -10646,7 +10654,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="237" ht="18.75" customHeight="1" spans="1:9">
+    <row r="237" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A237" s="5">
         <v>401</v>
       </c>
@@ -10675,7 +10683,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="238" ht="18.75" customHeight="1" spans="1:9">
+    <row r="238" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A238" s="5">
         <v>402</v>
       </c>
@@ -10704,7 +10712,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="239" ht="18.75" customHeight="1" spans="1:9">
+    <row r="239" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A239" s="5">
         <v>154</v>
       </c>
@@ -10733,7 +10741,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="240" ht="18.75" customHeight="1" spans="1:9">
+    <row r="240" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A240" s="5">
         <v>155</v>
       </c>
@@ -10762,7 +10770,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="241" ht="18.75" customHeight="1" spans="1:9">
+    <row r="241" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A241" s="5">
         <v>156</v>
       </c>
@@ -10791,7 +10799,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="242" ht="18.75" customHeight="1" spans="1:9">
+    <row r="242" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A242" s="5">
         <v>157</v>
       </c>
@@ -12034,7 +12042,7 @@
       <c r="H284" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="I284" s="6" t="s">
+      <c r="I284" s="7" t="s">
         <v>648</v>
       </c>
     </row>
@@ -12063,7 +12071,7 @@
       <c r="H285" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="I285" s="6" t="s">
+      <c r="I285" s="7" t="s">
         <v>650</v>
       </c>
     </row>
@@ -12469,7 +12477,7 @@
       <c r="H299" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="I299" s="7" t="s">
+      <c r="I299" s="6" t="s">
         <v>684</v>
       </c>
     </row>
@@ -12498,7 +12506,7 @@
       <c r="H300" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="I300" s="7" t="s">
+      <c r="I300" s="6" t="s">
         <v>686</v>
       </c>
     </row>
@@ -12527,7 +12535,7 @@
       <c r="H301" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="I301" s="6" t="s">
+      <c r="I301" s="7" t="s">
         <v>690</v>
       </c>
     </row>
@@ -12556,7 +12564,7 @@
       <c r="H302" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="I302" s="6" t="s">
+      <c r="I302" s="7" t="s">
         <v>692</v>
       </c>
     </row>
@@ -12585,7 +12593,7 @@
       <c r="H303" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="I303" s="6" t="s">
+      <c r="I303" s="7" t="s">
         <v>694</v>
       </c>
     </row>
@@ -12933,7 +12941,7 @@
       <c r="H315" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="I315" s="7" t="s">
+      <c r="I315" s="6" t="s">
         <v>722</v>
       </c>
     </row>
@@ -12962,7 +12970,7 @@
       <c r="H316" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="I316" s="7" t="s">
+      <c r="I316" s="6" t="s">
         <v>724</v>
       </c>
     </row>
@@ -13658,7 +13666,7 @@
       <c r="H340" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="I340" s="7" t="s">
+      <c r="I340" s="6" t="s">
         <v>774</v>
       </c>
     </row>
@@ -13687,7 +13695,7 @@
       <c r="H341" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="I341" s="7" t="s">
+      <c r="I341" s="6" t="s">
         <v>776</v>
       </c>
     </row>
@@ -13774,7 +13782,7 @@
       <c r="H344" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="I344" s="6" t="s">
+      <c r="I344" s="7" t="s">
         <v>784</v>
       </c>
     </row>
@@ -13803,7 +13811,7 @@
       <c r="H345" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="I345" s="6" t="s">
+      <c r="I345" s="7" t="s">
         <v>786</v>
       </c>
     </row>
@@ -13832,7 +13840,7 @@
       <c r="H346" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="I346" s="6" t="s">
+      <c r="I346" s="7" t="s">
         <v>788</v>
       </c>
     </row>
@@ -13861,7 +13869,7 @@
       <c r="H347" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="I347" s="6" t="s">
+      <c r="I347" s="7" t="s">
         <v>790</v>
       </c>
     </row>
@@ -14180,7 +14188,7 @@
       <c r="H358" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="I358" s="7" t="s">
+      <c r="I358" s="6" t="s">
         <v>814</v>
       </c>
     </row>
@@ -14209,7 +14217,7 @@
       <c r="H359" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="I359" s="7" t="s">
+      <c r="I359" s="6" t="s">
         <v>816</v>
       </c>
     </row>
@@ -15522,16 +15530,19 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I404" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="现金流量表"/>
+        <filter val="利润表"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="合计"/>
-        <filter val="流入"/>
-        <filter val="流出"/>
-        <filter val="净额"/>
-        <filter val="总净额"/>
+    <filterColumn colId="5">
+      <filters blank="1">
+        <filter val="SR"/>
+        <filter val="JLR"/>
+        <filter val="YYLR"/>
+        <filter val="GS"/>
+        <filter val="LRZE"/>
+        <filter val="CBFY"/>
+        <filter val="CWFY"/>
+        <filter val="HJ"/>
       </filters>
     </filterColumn>
     <extLst/>

--- a/StocksIC/sort.xlsx
+++ b/StocksIC/sort.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7695"/>
+    <workbookView windowWidth="21600" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3858,7 +3858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:I404"/>
@@ -3904,7 +3904,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:9">
+    <row r="2" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A2" s="5">
         <v>286</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:9">
+    <row r="3" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A3" s="5">
         <v>287</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:9">
+    <row r="4" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A4" s="5">
         <v>288</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:9">
+    <row r="5" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A5" s="5">
         <v>289</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:9">
+    <row r="6" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A6" s="5">
         <v>290</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:9">
+    <row r="7" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A7" s="5">
         <v>291</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:9">
+    <row r="8" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A8" s="5">
         <v>292</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:9">
+    <row r="9" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A9" s="5">
         <v>293</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:9">
+    <row r="10" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A10" s="5">
         <v>284</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:9">
+    <row r="11" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A11" s="5">
         <v>285</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:9">
+    <row r="12" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A12" s="5">
         <v>316</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:9">
+    <row r="13" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A13" s="5">
         <v>317</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:9">
+    <row r="14" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A14" s="5">
         <v>165</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:9">
+    <row r="15" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A15" s="5">
         <v>159</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:9">
+    <row r="16" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A16" s="5">
         <v>160</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:9">
+    <row r="17" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A17" s="5">
         <v>161</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" ht="18.75" customHeight="1" spans="1:9">
+    <row r="18" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A18" s="5">
         <v>162</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:9">
+    <row r="19" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A19" s="5">
         <v>163</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:9">
+    <row r="20" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A20" s="5">
         <v>164</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" ht="18.75" customHeight="1" spans="1:9">
+    <row r="21" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A21" s="5">
         <v>166</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" ht="18.75" customHeight="1" spans="1:9">
+    <row r="22" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A22" s="5">
         <v>167</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" ht="18.75" customHeight="1" spans="1:9">
+    <row r="23" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A23" s="5">
         <v>168</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:9">
+    <row r="24" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A24" s="5">
         <v>169</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:9">
+    <row r="25" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A25" s="5">
         <v>170</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:9">
+    <row r="26" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A26" s="5">
         <v>171</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" ht="18.75" customHeight="1" spans="1:9">
+    <row r="27" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A27" s="5">
         <v>0</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:9">
+    <row r="28" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A28" s="5">
         <v>312</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:9">
+    <row r="29" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A29" s="5">
         <v>313</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:9">
+    <row r="30" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A30" s="5">
         <v>314</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="53" ht="18.75" customHeight="1" spans="1:9">
+    <row r="53" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A53" s="5">
         <v>361</v>
       </c>
@@ -5777,10 +5777,10 @@
         <v>132</v>
       </c>
       <c r="F66" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G66" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>178</v>
@@ -6485,7 +6485,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="91" ht="18.75" customHeight="1" spans="1:9">
+    <row r="91" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A91" s="5">
         <v>229</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="92" ht="18.75" customHeight="1" spans="1:9">
+    <row r="92" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A92" s="5">
         <v>230</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="93" ht="18.75" customHeight="1" spans="1:9">
+    <row r="93" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A93" s="5">
         <v>231</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="94" ht="18.75" customHeight="1" spans="1:9">
+    <row r="94" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A94" s="5">
         <v>232</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="95" ht="18.75" customHeight="1" spans="1:9">
+    <row r="95" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A95" s="5">
         <v>233</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="96" ht="18.75" customHeight="1" spans="1:9">
+    <row r="96" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A96" s="5">
         <v>234</v>
       </c>
@@ -6659,7 +6659,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="97" ht="18.75" customHeight="1" spans="1:9">
+    <row r="97" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A97" s="5">
         <v>235</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="98" ht="18.75" customHeight="1" spans="1:9">
+    <row r="98" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A98" s="5">
         <v>236</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="99" ht="18.75" customHeight="1" spans="1:9">
+    <row r="99" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A99" s="5">
         <v>281</v>
       </c>
@@ -6746,7 +6746,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="100" ht="18.75" customHeight="1" spans="1:9">
+    <row r="100" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A100" s="5">
         <v>310</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="101" ht="18.75" customHeight="1" spans="1:9">
+    <row r="101" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A101" s="5">
         <v>311</v>
       </c>
@@ -6804,7 +6804,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="102" ht="18.75" customHeight="1" spans="1:9">
+    <row r="102" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A102" s="5">
         <v>183</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="103" ht="18.75" customHeight="1" spans="1:9">
+    <row r="103" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A103" s="5">
         <v>184</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="104" ht="18.75" customHeight="1" spans="1:9">
+    <row r="104" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A104" s="5">
         <v>185</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="105" ht="18.75" customHeight="1" spans="1:9">
+    <row r="105" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A105" s="5">
         <v>186</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="106" ht="18.75" customHeight="1" spans="1:9">
+    <row r="106" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A106" s="5">
         <v>187</v>
       </c>
@@ -6949,7 +6949,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="107" ht="18.75" customHeight="1" spans="1:9">
+    <row r="107" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A107" s="5">
         <v>188</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="108" ht="18.75" customHeight="1" spans="1:9">
+    <row r="108" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A108" s="5">
         <v>189</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="109" ht="18.75" customHeight="1" spans="1:9">
+    <row r="109" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A109" s="5">
         <v>190</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="110" ht="18.75" customHeight="1" spans="1:9">
+    <row r="110" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A110" s="5">
         <v>191</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="111" ht="18.75" customHeight="1" spans="1:9">
+    <row r="111" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A111" s="5">
         <v>245</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="112" ht="18.75" customHeight="1" spans="1:9">
+    <row r="112" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A112" s="5">
         <v>246</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="113" ht="18.75" customHeight="1" spans="1:9">
+    <row r="113" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A113" s="5">
         <v>247</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="114" ht="18.75" customHeight="1" spans="1:9">
+    <row r="114" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A114" s="5">
         <v>248</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="115" ht="18.75" customHeight="1" spans="1:9">
+    <row r="115" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A115" s="5">
         <v>249</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="116" ht="18.75" customHeight="1" spans="1:9">
+    <row r="116" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A116" s="5">
         <v>250</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="117" ht="18.75" customHeight="1" spans="1:9">
+    <row r="117" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A117" s="5">
         <v>251</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="118" ht="18.75" customHeight="1" spans="1:9">
+    <row r="118" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A118" s="5">
         <v>252</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="119" ht="18.75" customHeight="1" spans="1:9">
+    <row r="119" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A119" s="5">
         <v>253</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="120" ht="18.75" customHeight="1" spans="1:9">
+    <row r="120" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A120" s="5">
         <v>254</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="121" ht="18.75" customHeight="1" spans="1:9">
+    <row r="121" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A121" s="5">
         <v>255</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="122" ht="18.75" customHeight="1" spans="1:9">
+    <row r="122" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A122" s="5">
         <v>256</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="123" ht="18.75" customHeight="1" spans="1:9">
+    <row r="123" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A123" s="5">
         <v>257</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="124" ht="18.75" customHeight="1" spans="1:9">
+    <row r="124" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A124" s="5">
         <v>258</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="125" ht="18.75" customHeight="1" spans="1:9">
+    <row r="125" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A125" s="5">
         <v>259</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="126" ht="18.75" customHeight="1" spans="1:9">
+    <row r="126" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A126" s="5">
         <v>260</v>
       </c>
@@ -7529,7 +7529,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="127" ht="18.75" customHeight="1" spans="1:9">
+    <row r="127" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A127" s="5">
         <v>261</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="128" ht="18.75" customHeight="1" spans="1:9">
+    <row r="128" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A128" s="5">
         <v>262</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="129" ht="18.75" customHeight="1" spans="1:9">
+    <row r="129" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A129" s="5">
         <v>271</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="130" ht="18.75" customHeight="1" spans="1:9">
+    <row r="130" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A130" s="5">
         <v>272</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="131" ht="18.75" customHeight="1" spans="1:9">
+    <row r="131" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A131" s="5">
         <v>273</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="132" ht="18.75" customHeight="1" spans="1:9">
+    <row r="132" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A132" s="5">
         <v>274</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="133" ht="18.75" customHeight="1" spans="1:9">
+    <row r="133" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A133" s="5">
         <v>276</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="134" ht="18.75" customHeight="1" spans="1:9">
+    <row r="134" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A134" s="5">
         <v>277</v>
       </c>
@@ -7761,7 +7761,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="135" ht="18.75" customHeight="1" spans="1:9">
+    <row r="135" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A135" s="5">
         <v>278</v>
       </c>
@@ -7790,7 +7790,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="136" ht="18.75" customHeight="1" spans="1:9">
+    <row r="136" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A136" s="5">
         <v>279</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="137" ht="18.75" customHeight="1" spans="1:9">
+    <row r="137" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A137" s="5">
         <v>1</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="138" ht="18.75" customHeight="1" spans="1:9">
+    <row r="138" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A138" s="5">
         <v>2</v>
       </c>
@@ -7877,7 +7877,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="139" ht="18.75" customHeight="1" spans="1:9">
+    <row r="139" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A139" s="5">
         <v>3</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="140" ht="18.75" customHeight="1" spans="1:9">
+    <row r="140" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A140" s="5">
         <v>4</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="141" ht="18.75" customHeight="1" spans="1:9">
+    <row r="141" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A141" s="5">
         <v>5</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="142" ht="18.75" customHeight="1" spans="1:9">
+    <row r="142" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A142" s="5">
         <v>6</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="143" ht="18.75" customHeight="1" spans="1:9">
+    <row r="143" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A143" s="5">
         <v>7</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="144" ht="18.75" customHeight="1" spans="1:9">
+    <row r="144" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A144" s="5">
         <v>280</v>
       </c>
@@ -8051,7 +8051,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="145" ht="18.75" customHeight="1" spans="1:9">
+    <row r="145" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A145" s="5">
         <v>320</v>
       </c>
@@ -8080,7 +8080,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="146" ht="18.75" customHeight="1" spans="1:9">
+    <row r="146" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A146" s="5">
         <v>321</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="147" ht="18.75" customHeight="1" spans="1:9">
+    <row r="147" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A147" s="5">
         <v>218</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="148" ht="18.75" customHeight="1" spans="1:9">
+    <row r="148" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A148" s="5">
         <v>219</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="149" ht="18.75" customHeight="1" spans="1:9">
+    <row r="149" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A149" s="5">
         <v>220</v>
       </c>
@@ -8196,7 +8196,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="150" ht="18.75" customHeight="1" spans="1:9">
+    <row r="150" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A150" s="5">
         <v>221</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="151" ht="18.75" customHeight="1" spans="1:9">
+    <row r="151" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A151" s="5">
         <v>222</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="152" ht="18.75" customHeight="1" spans="1:9">
+    <row r="152" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A152" s="5">
         <v>223</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="153" ht="18.75" customHeight="1" spans="1:9">
+    <row r="153" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A153" s="5">
         <v>224</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="154" ht="18.75" customHeight="1" spans="1:9">
+    <row r="154" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A154" s="5">
         <v>225</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="155" ht="18.75" customHeight="1" spans="1:9">
+    <row r="155" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A155" s="5">
         <v>226</v>
       </c>
@@ -8370,7 +8370,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="156" ht="18.75" customHeight="1" spans="1:9">
+    <row r="156" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A156" s="5">
         <v>227</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="157" ht="18.75" customHeight="1" spans="1:9">
+    <row r="157" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A157" s="5">
         <v>228</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="158" ht="18.75" customHeight="1" spans="1:9">
+    <row r="158" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A158" s="5">
         <v>130</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="159" ht="18.75" customHeight="1" spans="1:9">
+    <row r="159" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A159" s="5">
         <v>400</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="160" ht="18.75" customHeight="1" spans="1:9">
+    <row r="160" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A160" s="5">
         <v>113</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="161" ht="18.75" customHeight="1" spans="1:9">
+    <row r="161" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A161" s="5">
         <v>118</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="162" ht="18.75" customHeight="1" spans="1:9">
+    <row r="162" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A162" s="5">
         <v>119</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="163" ht="18.75" customHeight="1" spans="1:9">
+    <row r="163" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A163" s="5">
         <v>315</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="164" ht="18.75" customHeight="1" spans="1:9">
+    <row r="164" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A164" s="5">
         <v>108</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="165" ht="18.75" customHeight="1" spans="1:9">
+    <row r="165" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A165" s="5">
         <v>109</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="166" ht="18.75" customHeight="1" spans="1:9">
+    <row r="166" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A166" s="5">
         <v>110</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="167" ht="18.75" customHeight="1" spans="1:9">
+    <row r="167" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A167" s="5">
         <v>111</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="168" ht="18.75" customHeight="1" spans="1:9">
+    <row r="168" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A168" s="5">
         <v>112</v>
       </c>
@@ -8747,7 +8747,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="169" ht="18.75" customHeight="1" spans="1:9">
+    <row r="169" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A169" s="5">
         <v>114</v>
       </c>
@@ -8776,7 +8776,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="170" ht="18.75" customHeight="1" spans="1:9">
+    <row r="170" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A170" s="5">
         <v>115</v>
       </c>
@@ -8805,7 +8805,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="171" ht="18.75" customHeight="1" spans="1:9">
+    <row r="171" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A171" s="5">
         <v>116</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="172" ht="18.75" customHeight="1" spans="1:9">
+    <row r="172" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A172" s="5">
         <v>117</v>
       </c>
@@ -8863,7 +8863,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="173" ht="18.75" customHeight="1" spans="1:9">
+    <row r="173" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A173" s="5">
         <v>129</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="174" ht="18.75" customHeight="1" spans="1:9">
+    <row r="174" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A174" s="5">
         <v>131</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="175" ht="18.75" customHeight="1" spans="1:9">
+    <row r="175" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A175" s="5">
         <v>132</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="176" ht="18.75" customHeight="1" spans="1:9">
+    <row r="176" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A176" s="5">
         <v>133</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="177" ht="18.75" customHeight="1" spans="1:9">
+    <row r="177" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A177" s="5">
         <v>309</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="178" ht="18.75" customHeight="1" spans="1:9">
+    <row r="178" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A178" s="5">
         <v>123</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="179" ht="18.75" customHeight="1" spans="1:9">
+    <row r="179" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A179" s="5">
         <v>127</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="180" ht="18.75" customHeight="1" spans="1:9">
+    <row r="180" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A180" s="5">
         <v>128</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="181" ht="18.75" customHeight="1" spans="1:9">
+    <row r="181" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A181" s="5">
         <v>120</v>
       </c>
@@ -9124,7 +9124,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="182" ht="18.75" customHeight="1" spans="1:9">
+    <row r="182" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A182" s="5">
         <v>121</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="183" ht="18.75" customHeight="1" spans="1:9">
+    <row r="183" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A183" s="5">
         <v>122</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="184" ht="18.75" customHeight="1" spans="1:9">
+    <row r="184" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A184" s="5">
         <v>398</v>
       </c>
@@ -9211,7 +9211,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="185" ht="18.75" customHeight="1" spans="1:9">
+    <row r="185" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A185" s="5">
         <v>124</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="186" ht="18.75" customHeight="1" spans="1:9">
+    <row r="186" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A186" s="5">
         <v>125</v>
       </c>
@@ -9269,7 +9269,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="187" ht="18.75" customHeight="1" spans="1:9">
+    <row r="187" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A187" s="5">
         <v>126</v>
       </c>
@@ -9298,7 +9298,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="188" ht="18.75" customHeight="1" spans="1:9">
+    <row r="188" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A188" s="5">
         <v>399</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="189" ht="18.75" customHeight="1" spans="1:9">
+    <row r="189" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A189" s="5">
         <v>101</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="190" ht="18.75" customHeight="1" spans="1:9">
+    <row r="190" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A190" s="5">
         <v>106</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="191" ht="18.75" customHeight="1" spans="1:9">
+    <row r="191" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A191" s="5">
         <v>107</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="192" ht="18.75" customHeight="1" spans="1:9">
+    <row r="192" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A192" s="5">
         <v>306</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="193" ht="18.75" customHeight="1" spans="1:9">
+    <row r="193" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A193" s="5">
         <v>98</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="194" ht="18.75" customHeight="1" spans="1:9">
+    <row r="194" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A194" s="5">
         <v>99</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="195" ht="18.75" customHeight="1" spans="1:9">
+    <row r="195" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A195" s="5">
         <v>100</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="196" ht="18.75" customHeight="1" spans="1:9">
+    <row r="196" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A196" s="5">
         <v>383</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="197" ht="18.75" customHeight="1" spans="1:9">
+    <row r="197" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A197" s="5">
         <v>384</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="198" ht="18.75" customHeight="1" spans="1:9">
+    <row r="198" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A198" s="5">
         <v>385</v>
       </c>
@@ -9617,7 +9617,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="199" ht="18.75" customHeight="1" spans="1:9">
+    <row r="199" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A199" s="5">
         <v>386</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="200" ht="18.75" customHeight="1" spans="1:9">
+    <row r="200" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A200" s="5">
         <v>387</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="201" ht="18.75" customHeight="1" spans="1:9">
+    <row r="201" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A201" s="5">
         <v>388</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="202" ht="18.75" customHeight="1" spans="1:9">
+    <row r="202" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A202" s="5">
         <v>389</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="203" ht="18.75" customHeight="1" spans="1:9">
+    <row r="203" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A203" s="5">
         <v>390</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="204" ht="18.75" customHeight="1" spans="1:9">
+    <row r="204" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A204" s="5">
         <v>391</v>
       </c>
@@ -9791,7 +9791,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="205" ht="18.75" customHeight="1" spans="1:9">
+    <row r="205" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A205" s="5">
         <v>392</v>
       </c>
@@ -9820,7 +9820,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="206" ht="18.75" customHeight="1" spans="1:9">
+    <row r="206" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A206" s="5">
         <v>102</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="207" ht="18.75" customHeight="1" spans="1:9">
+    <row r="207" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A207" s="5">
         <v>103</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="208" ht="18.75" customHeight="1" spans="1:9">
+    <row r="208" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A208" s="5">
         <v>104</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="209" ht="18.75" customHeight="1" spans="1:9">
+    <row r="209" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A209" s="5">
         <v>105</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="210" ht="18.75" customHeight="1" spans="1:9">
+    <row r="210" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A210" s="5">
         <v>393</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="211" ht="18.75" customHeight="1" spans="1:9">
+    <row r="211" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A211" s="5">
         <v>394</v>
       </c>
@@ -9994,7 +9994,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="212" ht="18.75" customHeight="1" spans="1:9">
+    <row r="212" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A212" s="5">
         <v>395</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="213" ht="18.75" customHeight="1" spans="1:9">
+    <row r="213" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A213" s="5">
         <v>396</v>
       </c>
@@ -10052,7 +10052,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="214" ht="18.75" customHeight="1" spans="1:9">
+    <row r="214" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A214" s="5">
         <v>397</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="215" ht="18.75" customHeight="1" spans="1:9">
+    <row r="215" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A215" s="5">
         <v>151</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="216" ht="18.75" customHeight="1" spans="1:9">
+    <row r="216" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A216" s="5">
         <v>152</v>
       </c>
@@ -10139,7 +10139,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="217" ht="18.75" customHeight="1" spans="1:9">
+    <row r="217" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A217" s="5">
         <v>153</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="218" ht="18.75" customHeight="1" spans="1:9">
+    <row r="218" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A218" s="5">
         <v>382</v>
       </c>
@@ -10197,7 +10197,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="219" ht="18.75" customHeight="1" spans="1:9">
+    <row r="219" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A219" s="5">
         <v>150</v>
       </c>
@@ -10226,7 +10226,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="220" ht="18.75" customHeight="1" spans="1:9">
+    <row r="220" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A220" s="5">
         <v>158</v>
       </c>
@@ -10255,7 +10255,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="221" ht="18.75" customHeight="1" spans="1:9">
+    <row r="221" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A221" s="5">
         <v>134</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="222" ht="18.75" customHeight="1" spans="1:9">
+    <row r="222" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A222" s="5">
         <v>135</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="223" ht="18.75" customHeight="1" spans="1:9">
+    <row r="223" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A223" s="5">
         <v>136</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="224" ht="18.75" customHeight="1" spans="1:9">
+    <row r="224" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A224" s="5">
         <v>137</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="225" ht="18.75" customHeight="1" spans="1:9">
+    <row r="225" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A225" s="5">
         <v>138</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="226" ht="18.75" customHeight="1" spans="1:9">
+    <row r="226" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A226" s="5">
         <v>139</v>
       </c>
@@ -10429,7 +10429,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="227" ht="18.75" customHeight="1" spans="1:9">
+    <row r="227" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A227" s="5">
         <v>140</v>
       </c>
@@ -10458,7 +10458,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="228" ht="18.75" customHeight="1" spans="1:9">
+    <row r="228" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A228" s="5">
         <v>141</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="229" ht="18.75" customHeight="1" spans="1:9">
+    <row r="229" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A229" s="5">
         <v>142</v>
       </c>
@@ -10516,7 +10516,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="230" ht="18.75" customHeight="1" spans="1:9">
+    <row r="230" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A230" s="5">
         <v>143</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="231" ht="18.75" customHeight="1" spans="1:9">
+    <row r="231" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A231" s="5">
         <v>144</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="232" ht="18.75" customHeight="1" spans="1:9">
+    <row r="232" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A232" s="5">
         <v>145</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="233" ht="18.75" customHeight="1" spans="1:9">
+    <row r="233" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A233" s="5">
         <v>146</v>
       </c>
@@ -10632,7 +10632,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="234" ht="18.75" customHeight="1" spans="1:9">
+    <row r="234" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A234" s="5">
         <v>147</v>
       </c>
@@ -10661,7 +10661,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="235" ht="18.75" customHeight="1" spans="1:9">
+    <row r="235" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A235" s="5">
         <v>148</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="236" ht="18.75" customHeight="1" spans="1:9">
+    <row r="236" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A236" s="5">
         <v>149</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="237" ht="18.75" customHeight="1" spans="1:9">
+    <row r="237" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A237" s="5">
         <v>401</v>
       </c>
@@ -10748,7 +10748,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="238" ht="18.75" customHeight="1" spans="1:9">
+    <row r="238" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A238" s="5">
         <v>402</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="239" ht="18.75" customHeight="1" spans="1:9">
+    <row r="239" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A239" s="5">
         <v>154</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="240" ht="18.75" customHeight="1" spans="1:9">
+    <row r="240" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A240" s="5">
         <v>155</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="241" ht="18.75" customHeight="1" spans="1:9">
+    <row r="241" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A241" s="5">
         <v>156</v>
       </c>
@@ -10864,7 +10864,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="242" ht="18.75" customHeight="1" spans="1:9">
+    <row r="242" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A242" s="5">
         <v>157</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="243" ht="18.75" customHeight="1" spans="1:9">
+    <row r="243" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A243" s="5">
         <v>172</v>
       </c>
@@ -10922,7 +10922,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="244" ht="18.75" customHeight="1" spans="1:9">
+    <row r="244" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A244" s="5">
         <v>173</v>
       </c>
@@ -10951,7 +10951,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="245" ht="18.75" customHeight="1" spans="1:9">
+    <row r="245" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A245" s="5">
         <v>174</v>
       </c>
@@ -10980,7 +10980,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="246" ht="18.75" customHeight="1" spans="1:9">
+    <row r="246" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A246" s="5">
         <v>175</v>
       </c>
@@ -11009,7 +11009,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="247" ht="18.75" customHeight="1" spans="1:9">
+    <row r="247" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A247" s="5">
         <v>176</v>
       </c>
@@ -11038,7 +11038,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="248" ht="18.75" customHeight="1" spans="1:9">
+    <row r="248" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A248" s="5">
         <v>177</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="249" ht="18.75" customHeight="1" spans="1:9">
+    <row r="249" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A249" s="5">
         <v>178</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="250" ht="18.75" customHeight="1" spans="1:9">
+    <row r="250" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A250" s="5">
         <v>179</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="251" ht="18.75" customHeight="1" spans="1:9">
+    <row r="251" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A251" s="5">
         <v>180</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="252" ht="18.75" customHeight="1" spans="1:9">
+    <row r="252" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A252" s="5">
         <v>181</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="253" ht="18.75" customHeight="1" spans="1:9">
+    <row r="253" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A253" s="5">
         <v>182</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="254" ht="18.75" customHeight="1" spans="1:9">
+    <row r="254" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A254" s="5">
         <v>237</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="255" ht="18.75" customHeight="1" spans="1:9">
+    <row r="255" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A255" s="5">
         <v>238</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="256" ht="18.75" customHeight="1" spans="1:9">
+    <row r="256" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A256" s="5">
         <v>239</v>
       </c>
@@ -11299,7 +11299,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="257" ht="18.75" customHeight="1" spans="1:9">
+    <row r="257" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A257" s="5">
         <v>240</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="258" ht="18.75" customHeight="1" spans="1:9">
+    <row r="258" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A258" s="5">
         <v>241</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="259" ht="18.75" customHeight="1" spans="1:9">
+    <row r="259" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A259" s="5">
         <v>242</v>
       </c>
@@ -11386,7 +11386,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="260" ht="18.75" customHeight="1" spans="1:9">
+    <row r="260" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A260" s="5">
         <v>243</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="261" ht="18.75" customHeight="1" spans="1:9">
+    <row r="261" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A261" s="5">
         <v>244</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="262" ht="18.75" customHeight="1" spans="1:9">
+    <row r="262" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A262" s="5">
         <v>263</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="263" ht="18.75" customHeight="1" spans="1:9">
+    <row r="263" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A263" s="5">
         <v>264</v>
       </c>
@@ -11502,7 +11502,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="264" ht="18.75" customHeight="1" spans="1:9">
+    <row r="264" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A264" s="5">
         <v>265</v>
       </c>
@@ -11531,7 +11531,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="265" ht="18.75" customHeight="1" spans="1:9">
+    <row r="265" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A265" s="5">
         <v>266</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="266" ht="18.75" customHeight="1" spans="1:9">
+    <row r="266" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A266" s="5">
         <v>283</v>
       </c>
@@ -11589,7 +11589,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="267" ht="18.75" customHeight="1" spans="1:9">
+    <row r="267" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A267" s="5">
         <v>319</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="268" ht="18.75" customHeight="1" spans="1:9">
+    <row r="268" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A268" s="5">
         <v>192</v>
       </c>
@@ -11647,7 +11647,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="269" ht="18.75" customHeight="1" spans="1:9">
+    <row r="269" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A269" s="5">
         <v>193</v>
       </c>
@@ -11676,7 +11676,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="270" ht="18.75" customHeight="1" spans="1:9">
+    <row r="270" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A270" s="5">
         <v>194</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="271" ht="18.75" customHeight="1" spans="1:9">
+    <row r="271" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A271" s="5">
         <v>195</v>
       </c>
@@ -11734,7 +11734,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="272" ht="18.75" customHeight="1" spans="1:9">
+    <row r="272" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A272" s="5">
         <v>196</v>
       </c>
@@ -11763,7 +11763,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="273" ht="18.75" customHeight="1" spans="1:9">
+    <row r="273" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A273" s="5">
         <v>197</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="274" ht="18.75" customHeight="1" spans="1:9">
+    <row r="274" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A274" s="5">
         <v>198</v>
       </c>
@@ -11821,7 +11821,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="275" ht="18.75" customHeight="1" spans="1:9">
+    <row r="275" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A275" s="5">
         <v>199</v>
       </c>
@@ -11850,7 +11850,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="276" ht="18.75" customHeight="1" spans="1:9">
+    <row r="276" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A276" s="5">
         <v>200</v>
       </c>
@@ -11879,7 +11879,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="277" ht="18.75" customHeight="1" spans="1:9">
+    <row r="277" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A277" s="5">
         <v>201</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="278" ht="18.75" customHeight="1" spans="1:9">
+    <row r="278" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A278" s="5">
         <v>202</v>
       </c>
@@ -11937,7 +11937,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="279" ht="18.75" customHeight="1" spans="1:9">
+    <row r="279" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A279" s="5">
         <v>203</v>
       </c>
@@ -11966,7 +11966,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="280" ht="18.75" customHeight="1" spans="1:9">
+    <row r="280" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A280" s="5">
         <v>204</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="281" ht="18.75" customHeight="1" spans="1:9">
+    <row r="281" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A281" s="5">
         <v>206</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="282" ht="18.75" customHeight="1" spans="1:9">
+    <row r="282" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A282" s="5">
         <v>207</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="283" ht="18.75" customHeight="1" spans="1:9">
+    <row r="283" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A283" s="5">
         <v>208</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="284" ht="18.75" customHeight="1" spans="1:9">
+    <row r="284" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A284" s="5">
         <v>70</v>
       </c>
@@ -12111,7 +12111,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="285" ht="18.75" customHeight="1" spans="1:9">
+    <row r="285" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A285" s="5">
         <v>71</v>
       </c>
@@ -12140,7 +12140,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="286" ht="18.75" customHeight="1" spans="1:9">
+    <row r="286" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A286" s="5">
         <v>72</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="287" ht="18.75" customHeight="1" spans="1:9">
+    <row r="287" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A287" s="5">
         <v>73</v>
       </c>
@@ -12198,7 +12198,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="288" ht="18.75" customHeight="1" spans="1:9">
+    <row r="288" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A288" s="5">
         <v>270</v>
       </c>
@@ -12227,7 +12227,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="289" ht="18.75" customHeight="1" spans="1:9">
+    <row r="289" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A289" s="5">
         <v>64</v>
       </c>
@@ -12256,7 +12256,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="290" ht="18.75" customHeight="1" spans="1:9">
+    <row r="290" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A290" s="5">
         <v>65</v>
       </c>
@@ -12285,7 +12285,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="291" ht="18.75" customHeight="1" spans="1:9">
+    <row r="291" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A291" s="5">
         <v>66</v>
       </c>
@@ -12314,7 +12314,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="292" ht="18.75" customHeight="1" spans="1:9">
+    <row r="292" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A292" s="5">
         <v>67</v>
       </c>
@@ -12343,7 +12343,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="293" ht="18.75" customHeight="1" spans="1:9">
+    <row r="293" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A293" s="5">
         <v>68</v>
       </c>
@@ -12372,7 +12372,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="294" ht="18.75" customHeight="1" spans="1:9">
+    <row r="294" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A294" s="5">
         <v>69</v>
       </c>
@@ -12401,7 +12401,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="295" ht="18.75" customHeight="1" spans="1:9">
+    <row r="295" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A295" s="5">
         <v>267</v>
       </c>
@@ -12430,7 +12430,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="296" ht="18.75" customHeight="1" spans="1:9">
+    <row r="296" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A296" s="5">
         <v>297</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="297" ht="18.75" customHeight="1" spans="1:9">
+    <row r="297" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A297" s="5">
         <v>298</v>
       </c>
@@ -12488,7 +12488,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="298" ht="18.75" customHeight="1" spans="1:9">
+    <row r="298" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A298" s="5">
         <v>322</v>
       </c>
@@ -12517,7 +12517,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="299" ht="18.75" customHeight="1" spans="1:9">
+    <row r="299" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A299" s="5">
         <v>349</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="300" ht="18.75" customHeight="1" spans="1:9">
+    <row r="300" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A300" s="5">
         <v>350</v>
       </c>
@@ -12575,7 +12575,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="301" ht="18.75" customHeight="1" spans="1:9">
+    <row r="301" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A301" s="5">
         <v>51</v>
       </c>
@@ -12604,7 +12604,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="302" ht="18.75" customHeight="1" spans="1:9">
+    <row r="302" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A302" s="5">
         <v>58</v>
       </c>
@@ -12633,7 +12633,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="303" ht="18.75" customHeight="1" spans="1:9">
+    <row r="303" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A303" s="5">
         <v>345</v>
       </c>
@@ -12662,7 +12662,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="304" ht="18.75" customHeight="1" spans="1:9">
+    <row r="304" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A304" s="5">
         <v>54</v>
       </c>
@@ -12691,7 +12691,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="305" ht="18.75" customHeight="1" spans="1:9">
+    <row r="305" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A305" s="5">
         <v>62</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="306" ht="18.75" customHeight="1" spans="1:9">
+    <row r="306" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A306" s="5">
         <v>63</v>
       </c>
@@ -12749,7 +12749,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="307" ht="18.75" customHeight="1" spans="1:9">
+    <row r="307" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A307" s="5">
         <v>294</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="308" ht="18.75" customHeight="1" spans="1:9">
+    <row r="308" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A308" s="5">
         <v>41</v>
       </c>
@@ -12807,7 +12807,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="309" ht="18.75" customHeight="1" spans="1:9">
+    <row r="309" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A309" s="5">
         <v>42</v>
       </c>
@@ -12836,7 +12836,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="310" ht="18.75" customHeight="1" spans="1:9">
+    <row r="310" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A310" s="5">
         <v>43</v>
       </c>
@@ -12865,7 +12865,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="311" ht="18.75" customHeight="1" spans="1:9">
+    <row r="311" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A311" s="5">
         <v>44</v>
       </c>
@@ -12894,7 +12894,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="312" ht="18.75" customHeight="1" spans="1:9">
+    <row r="312" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A312" s="5">
         <v>45</v>
       </c>
@@ -12923,7 +12923,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="313" ht="18.75" customHeight="1" spans="1:9">
+    <row r="313" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A313" s="5">
         <v>46</v>
       </c>
@@ -12952,7 +12952,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="314" ht="18.75" customHeight="1" spans="1:9">
+    <row r="314" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A314" s="5">
         <v>47</v>
       </c>
@@ -12981,7 +12981,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="315" ht="18.75" customHeight="1" spans="1:9">
+    <row r="315" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A315" s="5">
         <v>48</v>
       </c>
@@ -13010,7 +13010,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="316" ht="18.75" customHeight="1" spans="1:9">
+    <row r="316" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A316" s="5">
         <v>49</v>
       </c>
@@ -13039,7 +13039,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="317" ht="18.75" customHeight="1" spans="1:9">
+    <row r="317" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A317" s="5">
         <v>50</v>
       </c>
@@ -13068,7 +13068,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="318" ht="18.75" customHeight="1" spans="1:9">
+    <row r="318" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A318" s="5">
         <v>52</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="319" ht="18.75" customHeight="1" spans="1:9">
+    <row r="319" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A319" s="5">
         <v>53</v>
       </c>
@@ -13126,7 +13126,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="320" ht="18.75" customHeight="1" spans="1:9">
+    <row r="320" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A320" s="5">
         <v>333</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="321" ht="18.75" customHeight="1" spans="1:9">
+    <row r="321" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A321" s="5">
         <v>334</v>
       </c>
@@ -13184,7 +13184,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="322" ht="18.75" customHeight="1" spans="1:9">
+    <row r="322" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A322" s="5">
         <v>335</v>
       </c>
@@ -13213,7 +13213,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="323" ht="18.75" customHeight="1" spans="1:9">
+    <row r="323" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A323" s="5">
         <v>336</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="324" ht="18.75" customHeight="1" spans="1:9">
+    <row r="324" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A324" s="5">
         <v>337</v>
       </c>
@@ -13271,7 +13271,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="325" ht="18.75" customHeight="1" spans="1:9">
+    <row r="325" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A325" s="5">
         <v>338</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="326" ht="18.75" customHeight="1" spans="1:9">
+    <row r="326" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A326" s="5">
         <v>339</v>
       </c>
@@ -13329,7 +13329,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="327" ht="18.75" customHeight="1" spans="1:9">
+    <row r="327" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A327" s="5">
         <v>341</v>
       </c>
@@ -13358,7 +13358,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="328" ht="18.75" customHeight="1" spans="1:9">
+    <row r="328" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A328" s="5">
         <v>342</v>
       </c>
@@ -13387,7 +13387,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="329" ht="18.75" customHeight="1" spans="1:9">
+    <row r="329" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A329" s="5">
         <v>343</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="330" ht="18.75" customHeight="1" spans="1:9">
+    <row r="330" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A330" s="5">
         <v>355</v>
       </c>
@@ -13445,7 +13445,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="331" ht="18.75" customHeight="1" spans="1:9">
+    <row r="331" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A331" s="5">
         <v>55</v>
       </c>
@@ -13474,7 +13474,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="332" ht="18.75" customHeight="1" spans="1:9">
+    <row r="332" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A332" s="5">
         <v>56</v>
       </c>
@@ -13503,7 +13503,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="333" ht="18.75" customHeight="1" spans="1:9">
+    <row r="333" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A333" s="5">
         <v>57</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="334" ht="18.75" customHeight="1" spans="1:9">
+    <row r="334" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A334" s="5">
         <v>59</v>
       </c>
@@ -13561,7 +13561,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="335" ht="18.75" customHeight="1" spans="1:9">
+    <row r="335" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A335" s="5">
         <v>60</v>
       </c>
@@ -13590,7 +13590,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="336" ht="18.75" customHeight="1" spans="1:9">
+    <row r="336" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A336" s="5">
         <v>61</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="337" ht="18.75" customHeight="1" spans="1:9">
+    <row r="337" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A337" s="5">
         <v>296</v>
       </c>
@@ -13648,7 +13648,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="338" ht="18.75" customHeight="1" spans="1:9">
+    <row r="338" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A338" s="5">
         <v>340</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="339" ht="18.75" customHeight="1" spans="1:9">
+    <row r="339" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A339" s="5">
         <v>344</v>
       </c>
@@ -13706,7 +13706,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="340" ht="18.75" customHeight="1" spans="1:9">
+    <row r="340" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A340" s="5">
         <v>346</v>
       </c>
@@ -13735,7 +13735,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="341" ht="18.75" customHeight="1" spans="1:9">
+    <row r="341" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A341" s="5">
         <v>347</v>
       </c>
@@ -13764,7 +13764,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="342" ht="18.75" customHeight="1" spans="1:9">
+    <row r="342" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A342" s="5">
         <v>348</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="343" ht="18.75" customHeight="1" spans="1:9">
+    <row r="343" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A343" s="5">
         <v>360</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="344" ht="18.75" customHeight="1" spans="1:9">
+    <row r="344" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A344" s="5">
         <v>14</v>
       </c>
@@ -13851,7 +13851,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="345" ht="18.75" customHeight="1" spans="1:9">
+    <row r="345" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A345" s="5">
         <v>18</v>
       </c>
@@ -13880,7 +13880,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="346" ht="18.75" customHeight="1" spans="1:9">
+    <row r="346" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A346" s="5">
         <v>29</v>
       </c>
@@ -13909,7 +13909,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="347" ht="18.75" customHeight="1" spans="1:9">
+    <row r="347" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A347" s="5">
         <v>30</v>
       </c>
@@ -13938,7 +13938,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="348" ht="18.75" customHeight="1" spans="1:9">
+    <row r="348" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A348" s="5">
         <v>21</v>
       </c>
@@ -13967,7 +13967,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="349" ht="18.75" customHeight="1" spans="1:9">
+    <row r="349" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A349" s="5">
         <v>39</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="350" ht="18.75" customHeight="1" spans="1:9">
+    <row r="350" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A350" s="5">
         <v>40</v>
       </c>
@@ -14025,7 +14025,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="351" ht="18.75" customHeight="1" spans="1:9">
+    <row r="351" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A351" s="5">
         <v>295</v>
       </c>
@@ -14054,7 +14054,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="352" ht="18.75" customHeight="1" spans="1:9">
+    <row r="352" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A352" s="5">
         <v>8</v>
       </c>
@@ -14083,7 +14083,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="353" ht="18.75" customHeight="1" spans="1:9">
+    <row r="353" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A353" s="5">
         <v>9</v>
       </c>
@@ -14112,7 +14112,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="354" ht="18.75" customHeight="1" spans="1:9">
+    <row r="354" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A354" s="5">
         <v>10</v>
       </c>
@@ -14141,7 +14141,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="355" ht="18.75" customHeight="1" spans="1:9">
+    <row r="355" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A355" s="5">
         <v>11</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="356" ht="18.75" customHeight="1" spans="1:9">
+    <row r="356" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A356" s="5">
         <v>12</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="357" ht="18.75" customHeight="1" spans="1:9">
+    <row r="357" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A357" s="5">
         <v>13</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="358" ht="18.75" customHeight="1" spans="1:9">
+    <row r="358" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A358" s="5">
         <v>15</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="359" ht="18.75" customHeight="1" spans="1:9">
+    <row r="359" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A359" s="5">
         <v>16</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="360" ht="18.75" customHeight="1" spans="1:9">
+    <row r="360" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A360" s="5">
         <v>17</v>
       </c>
@@ -14315,7 +14315,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="361" ht="18.75" customHeight="1" spans="1:9">
+    <row r="361" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A361" s="5">
         <v>19</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="362" ht="18.75" customHeight="1" spans="1:9">
+    <row r="362" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A362" s="5">
         <v>20</v>
       </c>
@@ -14373,7 +14373,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="363" ht="18.75" customHeight="1" spans="1:9">
+    <row r="363" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A363" s="5">
         <v>323</v>
       </c>
@@ -14402,7 +14402,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="364" ht="18.75" customHeight="1" spans="1:9">
+    <row r="364" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A364" s="5">
         <v>324</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="365" ht="18.75" customHeight="1" spans="1:9">
+    <row r="365" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A365" s="5">
         <v>325</v>
       </c>
@@ -14460,7 +14460,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="366" ht="18.75" customHeight="1" spans="1:9">
+    <row r="366" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A366" s="5">
         <v>326</v>
       </c>
@@ -14489,7 +14489,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="367" ht="18.75" customHeight="1" spans="1:9">
+    <row r="367" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A367" s="5">
         <v>327</v>
       </c>
@@ -14518,7 +14518,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="368" ht="18.75" customHeight="1" spans="1:9">
+    <row r="368" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A368" s="5">
         <v>328</v>
       </c>
@@ -14547,7 +14547,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="369" ht="18.75" customHeight="1" spans="1:9">
+    <row r="369" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A369" s="5">
         <v>329</v>
       </c>
@@ -14576,7 +14576,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="370" ht="18.75" customHeight="1" spans="1:9">
+    <row r="370" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A370" s="5">
         <v>330</v>
       </c>
@@ -14605,7 +14605,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="371" ht="18.75" customHeight="1" spans="1:9">
+    <row r="371" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A371" s="5">
         <v>331</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="372" ht="18.75" customHeight="1" spans="1:9">
+    <row r="372" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A372" s="5">
         <v>356</v>
       </c>
@@ -14663,7 +14663,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="373" ht="18.75" customHeight="1" spans="1:9">
+    <row r="373" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A373" s="5">
         <v>358</v>
       </c>
@@ -14692,7 +14692,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="374" ht="18.75" customHeight="1" spans="1:9">
+    <row r="374" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A374" s="5">
         <v>357</v>
       </c>
@@ -14721,7 +14721,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="375" ht="18.75" customHeight="1" spans="1:9">
+    <row r="375" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A375" s="5">
         <v>22</v>
       </c>
@@ -14750,7 +14750,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="376" ht="18.75" customHeight="1" spans="1:9">
+    <row r="376" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A376" s="5">
         <v>23</v>
       </c>
@@ -14779,7 +14779,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="377" ht="18.75" customHeight="1" spans="1:9">
+    <row r="377" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A377" s="5">
         <v>24</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="378" ht="18.75" customHeight="1" spans="1:9">
+    <row r="378" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A378" s="5">
         <v>25</v>
       </c>
@@ -14837,7 +14837,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="379" ht="18.75" customHeight="1" spans="1:9">
+    <row r="379" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A379" s="5">
         <v>26</v>
       </c>
@@ -14866,7 +14866,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="380" ht="18.75" customHeight="1" spans="1:9">
+    <row r="380" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A380" s="5">
         <v>27</v>
       </c>
@@ -14895,7 +14895,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="381" ht="18.75" customHeight="1" spans="1:9">
+    <row r="381" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A381" s="5">
         <v>28</v>
       </c>
@@ -14924,7 +14924,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="382" ht="18.75" customHeight="1" spans="1:9">
+    <row r="382" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A382" s="5">
         <v>31</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="383" ht="18.75" customHeight="1" spans="1:9">
+    <row r="383" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A383" s="5">
         <v>32</v>
       </c>
@@ -14982,7 +14982,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="384" ht="18.75" customHeight="1" spans="1:9">
+    <row r="384" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A384" s="5">
         <v>33</v>
       </c>
@@ -15011,7 +15011,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="385" ht="18.75" customHeight="1" spans="1:9">
+    <row r="385" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A385" s="5">
         <v>34</v>
       </c>
@@ -15040,7 +15040,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="386" ht="18.75" customHeight="1" spans="1:9">
+    <row r="386" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A386" s="5">
         <v>35</v>
       </c>
@@ -15069,7 +15069,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="387" ht="18.75" customHeight="1" spans="1:9">
+    <row r="387" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A387" s="5">
         <v>36</v>
       </c>
@@ -15098,7 +15098,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="388" ht="18.75" customHeight="1" spans="1:9">
+    <row r="388" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A388" s="5">
         <v>37</v>
       </c>
@@ -15127,7 +15127,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="389" ht="18.75" customHeight="1" spans="1:9">
+    <row r="389" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A389" s="5">
         <v>38</v>
       </c>
@@ -15156,7 +15156,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="390" ht="18.75" customHeight="1" spans="1:9">
+    <row r="390" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A390" s="5">
         <v>332</v>
       </c>
@@ -15185,7 +15185,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="391" ht="18.75" customHeight="1" spans="1:9">
+    <row r="391" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A391" s="5">
         <v>351</v>
       </c>
@@ -15214,7 +15214,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="392" ht="18.75" customHeight="1" spans="1:9">
+    <row r="392" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A392" s="5">
         <v>352</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="393" ht="18.75" customHeight="1" spans="1:9">
+    <row r="393" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A393" s="5">
         <v>353</v>
       </c>
@@ -15272,7 +15272,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="394" ht="18.75" customHeight="1" spans="1:9">
+    <row r="394" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A394" s="5">
         <v>354</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="395" ht="18.75" customHeight="1" spans="1:9">
+    <row r="395" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A395" s="5">
         <v>359</v>
       </c>
@@ -15330,7 +15330,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="396" ht="18.75" customHeight="1" spans="1:9">
+    <row r="396" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A396" s="5">
         <v>209</v>
       </c>
@@ -15359,7 +15359,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="397" ht="18.75" customHeight="1" spans="1:9">
+    <row r="397" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A397" s="5">
         <v>210</v>
       </c>
@@ -15388,7 +15388,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="398" ht="18.75" customHeight="1" spans="1:9">
+    <row r="398" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A398" s="5">
         <v>211</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="399" ht="18.75" customHeight="1" spans="1:9">
+    <row r="399" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A399" s="5">
         <v>212</v>
       </c>
@@ -15446,7 +15446,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="400" ht="18.75" customHeight="1" spans="1:9">
+    <row r="400" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A400" s="5">
         <v>213</v>
       </c>
@@ -15475,7 +15475,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="401" ht="18.75" customHeight="1" spans="1:9">
+    <row r="401" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A401" s="5">
         <v>214</v>
       </c>
@@ -15504,7 +15504,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="402" ht="18.75" customHeight="1" spans="1:9">
+    <row r="402" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A402" s="5">
         <v>215</v>
       </c>
@@ -15533,7 +15533,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="403" ht="18.75" customHeight="1" spans="1:9">
+    <row r="403" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A403" s="5">
         <v>216</v>
       </c>
@@ -15562,7 +15562,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="404" ht="18.75" customHeight="1" spans="1:9">
+    <row r="404" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A404" s="5">
         <v>217</v>
       </c>
@@ -15593,6 +15593,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I404" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="利润表"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/StocksIC/sort.xlsx
+++ b/StocksIC/sort.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7695"/>
+    <workbookView windowWidth="21600" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3233" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3233" uniqueCount="932">
   <si>
     <t>Index</t>
   </si>
@@ -1554,6 +1554,9 @@
   </si>
   <si>
     <t>扣除非经常性损益后的净利润</t>
+  </si>
+  <si>
+    <t>JLRL</t>
   </si>
   <si>
     <t>col207</t>
@@ -3944,7 +3947,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:9">
+    <row r="3" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -3973,7 +3976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:9">
+    <row r="4" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -4002,7 +4005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:9">
+    <row r="5" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -4031,7 +4034,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:9">
+    <row r="6" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -4060,7 +4063,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:9">
+    <row r="7" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -4089,7 +4092,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:9">
+    <row r="8" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -4118,7 +4121,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:9">
+    <row r="9" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -6061,7 +6064,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="76" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="76" ht="18.75" customHeight="1" spans="1:9">
       <c r="A76" s="5">
         <v>74</v>
       </c>
@@ -6090,7 +6093,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="77" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="77" ht="18.75" customHeight="1" spans="1:9">
       <c r="A77" s="5">
         <v>75</v>
       </c>
@@ -6119,7 +6122,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="78" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="78" ht="18.75" customHeight="1" spans="1:9">
       <c r="A78" s="5">
         <v>76</v>
       </c>
@@ -6148,7 +6151,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="79" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="79" ht="18.75" customHeight="1" spans="1:9">
       <c r="A79" s="5">
         <v>77</v>
       </c>
@@ -6177,7 +6180,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="80" ht="19" hidden="1" customHeight="1" spans="1:9">
+    <row r="80" ht="19" customHeight="1" spans="1:9">
       <c r="A80" s="5">
         <v>78</v>
       </c>
@@ -6206,7 +6209,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="81" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="81" ht="18.75" customHeight="1" spans="1:9">
       <c r="A81" s="5">
         <v>79</v>
       </c>
@@ -6235,7 +6238,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="82" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="82" ht="18.75" customHeight="1" spans="1:9">
       <c r="A82" s="5">
         <v>80</v>
       </c>
@@ -6264,7 +6267,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="83" ht="18.75" customHeight="1" spans="1:9">
       <c r="A83" s="5">
         <v>81</v>
       </c>
@@ -6293,7 +6296,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="84" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="84" ht="18.75" customHeight="1" spans="1:9">
       <c r="A84" s="5">
         <v>82</v>
       </c>
@@ -6322,7 +6325,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="85" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="85" ht="18.75" customHeight="1" spans="1:9">
       <c r="A85" s="5">
         <v>83</v>
       </c>
@@ -6351,7 +6354,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="86" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="86" ht="18.75" customHeight="1" spans="1:9">
       <c r="A86" s="5">
         <v>84</v>
       </c>
@@ -6380,7 +6383,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="87" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="87" ht="18.75" customHeight="1" spans="1:9">
       <c r="A87" s="5">
         <v>85</v>
       </c>
@@ -6409,7 +6412,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="88" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="88" ht="18.75" customHeight="1" spans="1:9">
       <c r="A88" s="5">
         <v>86</v>
       </c>
@@ -6438,7 +6441,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="89" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="89" ht="18.75" customHeight="1" spans="1:9">
       <c r="A89" s="5">
         <v>87</v>
       </c>
@@ -6467,7 +6470,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="90" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="90" ht="18.75" customHeight="1" spans="1:9">
       <c r="A90" s="5">
         <v>88</v>
       </c>
@@ -6496,7 +6499,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="91" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="91" ht="18.75" customHeight="1" spans="1:9">
       <c r="A91" s="5">
         <v>89</v>
       </c>
@@ -6525,7 +6528,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="92" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="92" ht="18.75" customHeight="1" spans="1:9">
       <c r="A92" s="5">
         <v>90</v>
       </c>
@@ -6554,7 +6557,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="93" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="93" ht="18.75" customHeight="1" spans="1:9">
       <c r="A93" s="5">
         <v>91</v>
       </c>
@@ -6583,7 +6586,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="94" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="94" ht="18.75" customHeight="1" spans="1:9">
       <c r="A94" s="5">
         <v>92</v>
       </c>
@@ -6612,7 +6615,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="95" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="95" ht="18.75" customHeight="1" spans="1:9">
       <c r="A95" s="5">
         <v>93</v>
       </c>
@@ -6641,7 +6644,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="96" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="96" ht="18.75" customHeight="1" spans="1:9">
       <c r="A96" s="5">
         <v>94</v>
       </c>
@@ -6670,7 +6673,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="97" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="97" ht="18.75" customHeight="1" spans="1:9">
       <c r="A97" s="5">
         <v>95</v>
       </c>
@@ -6699,7 +6702,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="98" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="98" ht="18.75" customHeight="1" spans="1:9">
       <c r="A98" s="5">
         <v>96</v>
       </c>
@@ -6728,7 +6731,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="99" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="99" ht="18.75" customHeight="1" spans="1:9">
       <c r="A99" s="5">
         <v>97</v>
       </c>
@@ -9425,7 +9428,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="192" ht="18.75" customHeight="1" spans="1:9">
+    <row r="192" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A192" s="5">
         <v>190</v>
       </c>
@@ -9860,7 +9863,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="207" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="207" ht="18.75" customHeight="1" spans="1:9">
       <c r="A207" s="5">
         <v>205</v>
       </c>
@@ -9889,62 +9892,62 @@
         <v>507</v>
       </c>
     </row>
-    <row r="208" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+    <row r="208" ht="18.75" customHeight="1" spans="1:9">
       <c r="A208" s="5">
         <v>206</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>477</v>
+        <v>187</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>478</v>
+        <v>188</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>477</v>
+        <v>223</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>478</v>
+        <v>224</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>478</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I208" s="2" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="209" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="209" ht="18.75" customHeight="1" spans="1:9">
       <c r="A209" s="5">
         <v>207</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>477</v>
+        <v>187</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>478</v>
+        <v>188</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>477</v>
+        <v>223</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>478</v>
+        <v>224</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>478</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I209" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="210" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -9970,10 +9973,10 @@
         <v>478</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I210" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="211" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -9981,28 +9984,28 @@
         <v>209</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C211" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D211" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D211" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E211" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F211" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F211" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="G211" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I211" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="212" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10010,28 +10013,28 @@
         <v>210</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C212" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D212" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D212" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E212" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F212" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F212" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="G212" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I212" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="213" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10039,28 +10042,28 @@
         <v>211</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C213" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D213" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D213" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E213" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F213" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="G213" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I213" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="214" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10068,28 +10071,28 @@
         <v>212</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C214" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D214" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D214" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E214" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F214" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F214" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="G214" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I214" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="215" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10097,28 +10100,28 @@
         <v>213</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C215" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D215" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D215" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E215" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F215" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F215" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="G215" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="216" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10126,28 +10129,28 @@
         <v>214</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C216" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D216" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D216" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E216" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F216" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F216" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="G216" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="217" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10155,28 +10158,28 @@
         <v>215</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C217" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D217" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D217" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E217" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F217" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F217" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="G217" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="218" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10184,28 +10187,28 @@
         <v>216</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C218" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D218" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D218" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E218" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F218" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F218" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="G218" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="219" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10213,39 +10216,39 @@
         <v>217</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C219" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D219" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D219" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E219" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F219" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F219" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="G219" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I219" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="220" ht="18.75" customHeight="1" spans="1:9">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="220" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A220" s="5">
         <v>218</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>13</v>
@@ -10260,10 +10263,10 @@
         <v>14</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I220" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="221" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10271,28 +10274,28 @@
         <v>219</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D221" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D221" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="E221" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F221" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="G221" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I221" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="222" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10300,28 +10303,28 @@
         <v>220</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C222" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D222" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="E222" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F222" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="G222" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I222" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="223" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10329,28 +10332,28 @@
         <v>221</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C223" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D223" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D223" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="E223" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F223" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F223" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="G223" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I223" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="224" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10358,28 +10361,28 @@
         <v>222</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C224" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D224" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D224" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="E224" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F224" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="G224" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I224" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="225" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10387,39 +10390,39 @@
         <v>223</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C225" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D225" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D225" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="E225" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F225" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F225" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="G225" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I225" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="226" ht="18.75" customHeight="1" spans="1:9">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="226" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A226" s="5">
         <v>224</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>13</v>
@@ -10434,10 +10437,10 @@
         <v>14</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I226" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="227" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10445,28 +10448,28 @@
         <v>225</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C227" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D227" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D227" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="E227" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F227" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="G227" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I227" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="228" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10474,28 +10477,28 @@
         <v>226</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D228" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D228" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="E228" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F228" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="G228" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I228" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="229" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10503,28 +10506,28 @@
         <v>227</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C229" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D229" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D229" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="E229" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F229" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F229" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="G229" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I229" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10532,28 +10535,28 @@
         <v>228</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C230" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D230" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="E230" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F230" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="G230" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I230" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="231" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10561,28 +10564,28 @@
         <v>229</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C231" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D231" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D231" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="E231" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F231" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="G231" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I231" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="232" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10590,28 +10593,28 @@
         <v>230</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D232" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="E232" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F232" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F232" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="G232" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I232" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="233" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10619,28 +10622,28 @@
         <v>231</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D233" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="E233" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F233" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F233" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="G233" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I233" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="234" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10648,28 +10651,28 @@
         <v>232</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D234" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="E234" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F234" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="G234" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I234" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="235" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10677,28 +10680,28 @@
         <v>233</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C235" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D235" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D235" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="E235" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F235" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="G235" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I235" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="236" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10706,28 +10709,28 @@
         <v>234</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C236" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D236" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D236" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="E236" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F236" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="G236" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I236" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="237" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10735,28 +10738,28 @@
         <v>235</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C237" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D237" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="E237" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F237" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="G237" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I237" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="238" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10764,28 +10767,28 @@
         <v>236</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C238" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D238" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D238" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="E238" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F238" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F238" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="G238" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I238" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="239" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10793,28 +10796,28 @@
         <v>237</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D239" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E239" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F239" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G239" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I239" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="240" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10822,28 +10825,28 @@
         <v>238</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C240" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D240" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D240" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E240" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F240" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G240" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I240" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="241" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10851,28 +10854,28 @@
         <v>239</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C241" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D241" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D241" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E241" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F241" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F241" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G241" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I241" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="242" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10880,28 +10883,28 @@
         <v>240</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C242" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D242" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D242" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E242" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F242" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F242" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G242" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I242" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="243" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10909,28 +10912,28 @@
         <v>241</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C243" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D243" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D243" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E243" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F243" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F243" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G243" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I243" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="244" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10938,28 +10941,28 @@
         <v>242</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C244" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D244" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D244" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E244" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F244" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F244" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G244" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I244" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="245" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10967,28 +10970,28 @@
         <v>243</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C245" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D245" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D245" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E245" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F245" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F245" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G245" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="I245" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="246" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -10996,28 +10999,28 @@
         <v>244</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C246" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D246" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D246" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E246" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F246" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F246" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G246" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I246" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="247" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11025,28 +11028,28 @@
         <v>245</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D247" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E247" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F247" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F247" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G247" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I247" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="248" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11054,28 +11057,28 @@
         <v>246</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C248" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D248" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E248" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F248" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G248" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I248" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="249" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11083,28 +11086,28 @@
         <v>247</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C249" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D249" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E249" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F249" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G249" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I249" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="250" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11112,28 +11115,28 @@
         <v>248</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C250" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D250" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D250" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E250" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F250" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G250" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I250" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="251" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11141,28 +11144,28 @@
         <v>249</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D251" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D251" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E251" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F251" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F251" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G251" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I251" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="252" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11170,28 +11173,28 @@
         <v>250</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C252" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D252" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D252" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E252" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F252" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F252" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G252" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I252" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="253" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11199,28 +11202,28 @@
         <v>251</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C253" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D253" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D253" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E253" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F253" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F253" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G253" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I253" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="254" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11228,28 +11231,28 @@
         <v>252</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C254" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D254" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E254" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F254" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G254" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I254" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="255" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11257,28 +11260,28 @@
         <v>253</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C255" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D255" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D255" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E255" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F255" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F255" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G255" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I255" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="256" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11286,28 +11289,28 @@
         <v>254</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C256" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D256" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D256" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E256" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F256" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F256" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G256" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I256" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="257" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11315,28 +11318,28 @@
         <v>255</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C257" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D257" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D257" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E257" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F257" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F257" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G257" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I257" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="258" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11344,28 +11347,28 @@
         <v>256</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C258" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D258" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D258" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E258" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F258" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F258" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G258" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I258" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="259" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11373,28 +11376,28 @@
         <v>257</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C259" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D259" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D259" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E259" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F259" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F259" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G259" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="I259" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="260" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11402,28 +11405,28 @@
         <v>258</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C260" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D260" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D260" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E260" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F260" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F260" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G260" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="I260" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="261" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11431,28 +11434,28 @@
         <v>259</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C261" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D261" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D261" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E261" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F261" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F261" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G261" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="I261" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="262" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11460,28 +11463,28 @@
         <v>260</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C262" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D262" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D262" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E262" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F262" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F262" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G262" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="I262" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="263" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11489,28 +11492,28 @@
         <v>261</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C263" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D263" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D263" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E263" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F263" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F263" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G263" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I263" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="264" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11518,28 +11521,28 @@
         <v>262</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C264" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D264" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D264" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E264" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F264" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F264" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G264" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I264" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="265" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11547,28 +11550,28 @@
         <v>263</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C265" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D265" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D265" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E265" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F265" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F265" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G265" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="I265" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="266" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11576,28 +11579,28 @@
         <v>264</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C266" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D266" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D266" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E266" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F266" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F266" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G266" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I266" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="267" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11605,28 +11608,28 @@
         <v>265</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C267" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D267" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D267" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E267" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F267" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F267" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G267" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I267" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="268" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11634,28 +11637,28 @@
         <v>266</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C268" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D268" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D268" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E268" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F268" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F268" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G268" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I268" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="269" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11681,13 +11684,13 @@
         <v>164</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I269" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="270" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="270" ht="18.75" customHeight="1" spans="1:9">
       <c r="A270" s="5">
         <v>268</v>
       </c>
@@ -11710,13 +11713,13 @@
         <v>64</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I270" s="2" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="271" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="271" ht="18.75" customHeight="1" spans="1:9">
       <c r="A271" s="5">
         <v>269</v>
       </c>
@@ -11727,22 +11730,22 @@
         <v>188</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>242</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I271" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="272" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11768,10 +11771,10 @@
         <v>64</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I272" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="273" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11779,28 +11782,28 @@
         <v>271</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C273" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D273" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D273" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E273" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F273" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G273" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="I273" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="274" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11808,28 +11811,28 @@
         <v>272</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C274" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D274" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D274" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E274" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F274" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F274" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G274" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I274" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="275" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11837,28 +11840,28 @@
         <v>273</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C275" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D275" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D275" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E275" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F275" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G275" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I275" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="276" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11866,31 +11869,31 @@
         <v>274</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C276" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D276" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D276" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E276" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F276" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F276" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G276" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="I276" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="277" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="277" ht="18.75" customHeight="1" spans="1:9">
       <c r="A277" s="5">
         <v>275</v>
       </c>
@@ -11901,22 +11904,22 @@
         <v>188</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>224</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I277" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="278" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11924,28 +11927,28 @@
         <v>276</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C278" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D278" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D278" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E278" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F278" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G278" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I278" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="279" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11953,28 +11956,28 @@
         <v>277</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C279" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D279" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D279" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E279" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F279" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F279" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G279" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I279" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="280" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -11982,28 +11985,28 @@
         <v>278</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C280" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D280" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D280" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E280" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F280" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F280" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G280" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I280" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="281" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12011,31 +12014,31 @@
         <v>279</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C281" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D281" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D281" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E281" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F281" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="G281" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I281" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="282" ht="18.75" customHeight="1" spans="1:9">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="282" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A282" s="5">
         <v>280</v>
       </c>
@@ -12058,21 +12061,21 @@
         <v>14</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="I282" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="283" ht="18.75" customHeight="1" spans="1:9">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="283" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A283" s="5">
         <v>281</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D283" t="s">
         <v>13</v>
@@ -12081,19 +12084,19 @@
         <v>14</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="I283" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="284" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="284" ht="18.75" customHeight="1" spans="1:9">
       <c r="A284" s="5">
         <v>282</v>
       </c>
@@ -12104,22 +12107,22 @@
         <v>188</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>224</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="285" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12127,28 +12130,28 @@
         <v>283</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C285" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D285" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E285" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F285" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F285" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G285" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="286" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12156,28 +12159,28 @@
         <v>284</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C286" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D286" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="D286" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="E286" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F286" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="G286" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I286" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="287" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12185,28 +12188,28 @@
         <v>285</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C287" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D287" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="D287" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="E287" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="F287" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F287" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="G287" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="I287" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="288" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12214,28 +12217,28 @@
         <v>286</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C288" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D288" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="D288" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="E288" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F288" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F288" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="G288" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I288" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="289" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12243,28 +12246,28 @@
         <v>287</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C289" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D289" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="D289" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="E289" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F289" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="G289" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I289" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="290" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12272,28 +12275,28 @@
         <v>288</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C290" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D290" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="D290" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="E290" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F290" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="G290" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I290" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="291" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12301,39 +12304,39 @@
         <v>289</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C291" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D291" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="D291" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="E291" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F291" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F291" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="G291" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="I291" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="292" ht="18.75" customHeight="1" spans="1:9">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="292" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A292" s="5">
         <v>290</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>13</v>
@@ -12342,16 +12345,16 @@
         <v>14</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I292" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="293" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12359,28 +12362,28 @@
         <v>291</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C293" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D293" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="D293" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="E293" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F293" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F293" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="G293" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I293" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="294" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12388,39 +12391,39 @@
         <v>292</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C294" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D294" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="D294" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="E294" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F294" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F294" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="G294" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I294" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="295" ht="18.75" customHeight="1" spans="1:9">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="295" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A295" s="5">
         <v>293</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>13</v>
@@ -12429,16 +12432,16 @@
         <v>14</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I295" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="296" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12458,16 +12461,16 @@
         <v>110</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I296" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="297" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12487,16 +12490,16 @@
         <v>33</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I297" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="298" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12522,10 +12525,10 @@
         <v>142</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I298" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="299" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12551,10 +12554,10 @@
         <v>164</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I299" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="300" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12580,13 +12583,13 @@
         <v>164</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="I300" s="2" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="301" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="301" ht="18.75" customHeight="1" spans="1:9">
       <c r="A301" s="5">
         <v>299</v>
       </c>
@@ -12609,13 +12612,13 @@
         <v>212</v>
       </c>
       <c r="H301" s="11" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="302" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="302" ht="18.75" customHeight="1" spans="1:9">
       <c r="A302" s="5">
         <v>300</v>
       </c>
@@ -12638,13 +12641,13 @@
         <v>212</v>
       </c>
       <c r="H302" s="11" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="303" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="303" ht="18.75" customHeight="1" spans="1:9">
       <c r="A303" s="5">
         <v>301</v>
       </c>
@@ -12667,13 +12670,13 @@
         <v>48</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="304" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="304" ht="18.75" customHeight="1" spans="1:9">
       <c r="A304" s="5">
         <v>302</v>
       </c>
@@ -12696,13 +12699,13 @@
         <v>252</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I304" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="305" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="305" ht="18.75" customHeight="1" spans="1:9">
       <c r="A305" s="5">
         <v>303</v>
       </c>
@@ -12725,13 +12728,13 @@
         <v>197</v>
       </c>
       <c r="H305" s="11" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I305" s="2" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="306" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="306" ht="18.75" customHeight="1" spans="1:9">
       <c r="A306" s="5">
         <v>304</v>
       </c>
@@ -12748,19 +12751,19 @@
         <v>195</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>210</v>
       </c>
       <c r="H306" s="11" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I306" s="2" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="307" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="307" ht="18.75" customHeight="1" spans="1:9">
       <c r="A307" s="5">
         <v>305</v>
       </c>
@@ -12777,16 +12780,16 @@
         <v>195</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>210</v>
       </c>
       <c r="H307" s="11" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="I307" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="308" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12806,19 +12809,19 @@
         <v>263</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>288</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="I308" s="8" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="309" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="309" ht="18.75" customHeight="1" spans="1:9">
       <c r="A309" s="5">
         <v>307</v>
       </c>
@@ -12829,25 +12832,25 @@
         <v>188</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>224</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="I309" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="310" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="310" ht="18.75" customHeight="1" spans="1:9">
       <c r="A310" s="5">
         <v>308</v>
       </c>
@@ -12858,22 +12861,22 @@
         <v>188</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>224</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="I310" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="311" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12899,21 +12902,21 @@
         <v>346</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I311" s="12" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="312" ht="18.75" customHeight="1" spans="1:9">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="312" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A312" s="5">
         <v>310</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>13</v>
@@ -12922,16 +12925,16 @@
         <v>14</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="I312" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="313" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12939,28 +12942,28 @@
         <v>311</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C313" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D313" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D313" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="E313" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F313" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F313" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="G313" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="I313" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="314" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -12986,10 +12989,10 @@
         <v>10</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I314" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="315" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13015,10 +13018,10 @@
         <v>10</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="I315" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="316" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13044,10 +13047,10 @@
         <v>10</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I316" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="317" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13067,16 +13070,16 @@
         <v>292</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>288</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I317" s="8" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="318" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13084,28 +13087,28 @@
         <v>316</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C318" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D318" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="D318" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="E318" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="F318" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F318" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="G318" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="I318" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="319" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13113,31 +13116,31 @@
         <v>317</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C319" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D319" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="D319" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="E319" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="F319" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F319" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="G319" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="I319" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="320" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="320" ht="18.75" customHeight="1" spans="1:9">
       <c r="A320" s="5">
         <v>318</v>
       </c>
@@ -13154,16 +13157,16 @@
         <v>224</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>242</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="I320" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="321" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13171,31 +13174,31 @@
         <v>319</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C321" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D321" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D321" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="E321" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F321" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F321" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="G321" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I321" s="2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="322" ht="18.75" customHeight="1" spans="1:9">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="322" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A322" s="5">
         <v>320</v>
       </c>
@@ -13218,13 +13221,13 @@
         <v>14</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="I322" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="323" ht="18.75" customHeight="1" spans="1:9">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="323" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A323" s="5">
         <v>321</v>
       </c>
@@ -13247,10 +13250,10 @@
         <v>14</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="I323" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="324" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13276,10 +13279,10 @@
         <v>164</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="I324" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="325" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13305,10 +13308,10 @@
         <v>35</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I325" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="326" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13334,10 +13337,10 @@
         <v>35</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I326" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="327" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13363,10 +13366,10 @@
         <v>35</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I327" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="328" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13392,10 +13395,10 @@
         <v>35</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I328" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="329" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13421,10 +13424,10 @@
         <v>35</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I329" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="330" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13450,10 +13453,10 @@
         <v>35</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="I330" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="331" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13479,10 +13482,10 @@
         <v>35</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="I331" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="332" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13508,10 +13511,10 @@
         <v>35</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I332" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="333" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13537,10 +13540,10 @@
         <v>35</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="I333" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="334" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13566,10 +13569,10 @@
         <v>68</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="I334" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="335" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13595,10 +13598,10 @@
         <v>112</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="I335" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="336" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13624,10 +13627,10 @@
         <v>112</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="I336" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="337" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13653,10 +13656,10 @@
         <v>112</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="I337" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="338" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13682,10 +13685,10 @@
         <v>112</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="I338" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="339" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13711,10 +13714,10 @@
         <v>112</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="I339" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="340" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13740,10 +13743,10 @@
         <v>112</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I340" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="341" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13769,10 +13772,10 @@
         <v>112</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="I341" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="342" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13798,10 +13801,10 @@
         <v>142</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="I342" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="343" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13827,10 +13830,10 @@
         <v>112</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="I343" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="344" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13856,10 +13859,10 @@
         <v>112</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="I344" s="6" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="345" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13885,10 +13888,10 @@
         <v>112</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="I345" s="6" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="346" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13914,10 +13917,10 @@
         <v>142</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I346" s="6" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="347" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13943,10 +13946,10 @@
         <v>48</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I347" s="9" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="348" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -13972,10 +13975,10 @@
         <v>48</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="I348" s="8" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="349" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14001,10 +14004,10 @@
         <v>48</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="I349" s="8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="350" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14030,10 +14033,10 @@
         <v>142</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="I350" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="351" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14059,10 +14062,10 @@
         <v>48</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I351" s="8" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="352" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14088,10 +14091,10 @@
         <v>48</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I352" s="8" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="353" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14117,10 +14120,10 @@
         <v>68</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="I353" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="354" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14146,10 +14149,10 @@
         <v>68</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I354" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="355" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14175,10 +14178,10 @@
         <v>68</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I355" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="356" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14204,10 +14207,10 @@
         <v>68</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="I356" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="357" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14233,10 +14236,10 @@
         <v>112</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="I357" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="358" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14262,10 +14265,10 @@
         <v>35</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I358" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="359" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14291,10 +14294,10 @@
         <v>68</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="I359" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="360" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14320,10 +14323,10 @@
         <v>35</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I360" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="361" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14349,10 +14352,10 @@
         <v>68</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="I361" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="362" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -14378,13 +14381,13 @@
         <v>142</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="I362" s="2" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="363" ht="18.75" customHeight="1" spans="1:9">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="363" ht="18.75" hidden="1" customHeight="1" spans="1:9">
       <c r="A363" s="5">
         <v>361</v>
       </c>
@@ -14407,13 +14410,13 @@
         <v>14</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="I363" s="2" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="364" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="364" ht="18.75" customHeight="1" spans="1:9">
       <c r="A364" s="5">
         <v>362</v>
       </c>
@@ -14436,13 +14439,13 @@
         <v>64</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="I364" s="2" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="365" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="365" ht="18.75" customHeight="1" spans="1:9">
       <c r="A365" s="5">
         <v>363</v>
       </c>
@@ -14465,13 +14468,13 @@
         <v>192</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="I365" s="2" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="366" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="366" ht="18.75" customHeight="1" spans="1:9">
       <c r="A366" s="5">
         <v>364</v>
       </c>
@@ -14482,25 +14485,25 @@
         <v>188</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="I366" s="2" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="367" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="367" ht="18.75" customHeight="1" spans="1:9">
       <c r="A367" s="5">
         <v>365</v>
       </c>
@@ -14511,25 +14514,25 @@
         <v>188</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I367" s="2" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="368" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="368" ht="18.75" customHeight="1" spans="1:9">
       <c r="A368" s="5">
         <v>366</v>
       </c>
@@ -14552,13 +14555,13 @@
         <v>192</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="I368" s="2" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="369" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="369" ht="18.75" customHeight="1" spans="1:9">
       <c r="A369" s="5">
         <v>367</v>
       </c>
@@ -14581,13 +14584,13 @@
         <v>192</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="I369" s="2" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="370" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="370" ht="18.75" customHeight="1" spans="1:9">
       <c r="A370" s="5">
         <v>368</v>
       </c>
@@ -14610,13 +14613,13 @@
         <v>192</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I370" s="2" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="371" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="371" ht="18.75" customHeight="1" spans="1:9">
       <c r="A371" s="5">
         <v>369</v>
       </c>
@@ -14633,19 +14636,19 @@
         <v>195</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>210</v>
       </c>
       <c r="H371" s="11" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="I371" s="2" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="372" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="372" ht="18.75" customHeight="1" spans="1:9">
       <c r="A372" s="5">
         <v>370</v>
       </c>
@@ -14668,13 +14671,13 @@
         <v>197</v>
       </c>
       <c r="H372" s="11" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="I372" s="2" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="373" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="373" ht="18.75" customHeight="1" spans="1:9">
       <c r="A373" s="5">
         <v>371</v>
       </c>
@@ -14697,13 +14700,13 @@
         <v>197</v>
       </c>
       <c r="H373" s="11" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="I373" s="2" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="374" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="374" ht="18.75" customHeight="1" spans="1:9">
       <c r="A374" s="5">
         <v>372</v>
       </c>
@@ -14726,13 +14729,13 @@
         <v>197</v>
       </c>
       <c r="H374" s="11" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="I374" s="2" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="375" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="375" ht="18.75" customHeight="1" spans="1:9">
       <c r="A375" s="5">
         <v>373</v>
       </c>
@@ -14755,13 +14758,13 @@
         <v>197</v>
       </c>
       <c r="H375" s="11" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="I375" s="2" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="376" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="376" ht="18.75" customHeight="1" spans="1:9">
       <c r="A376" s="5">
         <v>374</v>
       </c>
@@ -14784,13 +14787,13 @@
         <v>197</v>
       </c>
       <c r="H376" s="11" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="I376" s="2" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="377" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="377" ht="18.75" customHeight="1" spans="1:9">
       <c r="A377" s="5">
         <v>375</v>
       </c>
@@ -14813,13 +14816,13 @@
         <v>197</v>
       </c>
       <c r="H377" s="11" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="I377" s="2" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="378" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="378" ht="18.75" customHeight="1" spans="1:9">
       <c r="A378" s="5">
         <v>376</v>
       </c>
@@ -14830,10 +14833,10 @@
         <v>188</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F378" s="2" t="s">
         <v>48</v>
@@ -14842,13 +14845,13 @@
         <v>48</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="I378" s="7" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="379" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="379" ht="18.75" customHeight="1" spans="1:9">
       <c r="A379" s="5">
         <v>377</v>
       </c>
@@ -14871,13 +14874,13 @@
         <v>212</v>
       </c>
       <c r="H379" s="11" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="I379" s="2" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="380" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="380" ht="18.75" customHeight="1" spans="1:9">
       <c r="A380" s="5">
         <v>378</v>
       </c>
@@ -14900,13 +14903,13 @@
         <v>212</v>
       </c>
       <c r="H380" s="11" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="I380" s="2" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="381" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="381" ht="18.75" customHeight="1" spans="1:9">
       <c r="A381" s="5">
         <v>379</v>
       </c>
@@ -14929,13 +14932,13 @@
         <v>64</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="I381" s="2" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="382" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="382" ht="18.75" customHeight="1" spans="1:9">
       <c r="A382" s="5">
         <v>380</v>
       </c>
@@ -14958,13 +14961,13 @@
         <v>212</v>
       </c>
       <c r="H382" s="11" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="I382" s="2" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="383" ht="18.75" hidden="1" customHeight="1" spans="1:9">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="383" ht="18.75" customHeight="1" spans="1:9">
       <c r="A383" s="5">
         <v>381</v>
       </c>
@@ -14987,10 +14990,10 @@
         <v>212</v>
       </c>
       <c r="H383" s="11" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="I383" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="384" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15016,10 +15019,10 @@
         <v>48</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="I384" s="7" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="385" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15045,10 +15048,10 @@
         <v>264</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="I385" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="386" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15074,10 +15077,10 @@
         <v>264</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="I386" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="387" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15103,10 +15106,10 @@
         <v>264</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I387" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="388" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15132,10 +15135,10 @@
         <v>264</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I388" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="389" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15161,10 +15164,10 @@
         <v>264</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="I389" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="390" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15190,10 +15193,10 @@
         <v>264</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="I390" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="391" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15219,10 +15222,10 @@
         <v>264</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="I391" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="392" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15248,10 +15251,10 @@
         <v>264</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="I392" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="393" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15277,10 +15280,10 @@
         <v>264</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="I393" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="394" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15306,10 +15309,10 @@
         <v>264</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="I394" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="395" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15335,10 +15338,10 @@
         <v>275</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I395" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="396" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15364,10 +15367,10 @@
         <v>275</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="I396" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="397" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15393,10 +15396,10 @@
         <v>275</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="I397" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="398" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15422,10 +15425,10 @@
         <v>275</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="I398" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="399" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15451,10 +15454,10 @@
         <v>275</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="I399" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="400" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15480,10 +15483,10 @@
         <v>264</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I400" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="401" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15509,10 +15512,10 @@
         <v>275</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I401" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="402" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15538,10 +15541,10 @@
         <v>48</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="I402" s="7" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="403" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15567,10 +15570,10 @@
         <v>275</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I403" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="404" ht="18.75" hidden="1" customHeight="1" spans="1:9">
@@ -15596,20 +15599,20 @@
         <v>275</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="I404" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I404" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="3">
+    <filterColumn colId="2">
       <filters>
-        <filter val="MGZB"/>
+        <filter val="利润表"/>
       </filters>
     </filterColumn>
-    <sortState ref="A2:I404">
+    <sortState ref="A1:I404">
       <sortCondition ref="A2"/>
     </sortState>
     <extLst/>
